--- a/outputs/cadillac-repair-first-review/Cadillac-repair-first-fitment-review.xlsx
+++ b/outputs/cadillac-repair-first-review/Cadillac-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4c75906a19ae4675"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cadillac Review" sheetId="2" r:id="Rfce487dc96744e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R5e3c64f70e154c90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Rf5942f413e5741bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R88a610b7c86c48c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cadillac Review" sheetId="2" r:id="R3017249005564c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="Rea79c01b9ee44e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Re5f955506d5740a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -549,7 +549,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>299</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -563,7 +563,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -6337,26 +6337,28 @@
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
       <x:c r="H164" s="9" t="str">
-        <x:v>GM Genuine Parts catalog — Confirmed AFM Lifter Collapse Requires Generation-Specific Diagnosis</x:v>
+        <x:v>Amazon — Engine Valve Lifter 213-1738</x:v>
       </x:c>
       <x:c r="I164" s="9" t="str">
-        <x:v>https://parts.gmparts.com/</x:v>
+        <x:v>https://www.amazon.com/Clevite-77-213-1738-Roller-Lifter/dp/B000C07XZI?tag=au7o-20</x:v>
       </x:c>
       <x:c r="J164" s="9" t="str">
-        <x:v>2010-2020 Cadillac Escalade; select exact VIN, engine, trim, position and current supersession</x:v>
+        <x:v>2010-2020 Cadillac Escalade; only for the diagnosed Engine Valve Lifter branch, with exact engine/trim/position fitment rechecked before purchase</x:v>
       </x:c>
       <x:c r="K164" s="9" t="str">
-        <x:v>manufacturer VIN-select parts catalog</x:v>
-      </x:c>
-      <x:c r="L164" s="9" t="str"/>
+        <x:v>stored verified product link; exact conditional branch</x:v>
+      </x:c>
+      <x:c r="L164" s="9" t="str">
+        <x:v>Existing product page title/part number and stored ShowMeTheParts fitment evidence reviewed against the full How to Fix.</x:v>
+      </x:c>
       <x:c r="M164" s="9" t="str">
-        <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
+        <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase. Existing exact-part commerce link retained for that conditional branch.</x:v>
       </x:c>
       <x:c r="N164" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="165" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A165" s="40" t="str"/>
       <x:c r="B165" s="9" t="str"/>
       <x:c r="C165" s="9" t="str"/>
@@ -6365,720 +6367,702 @@
       <x:c r="F165" s="9" t="str"/>
       <x:c r="G165" s="9" t="str"/>
       <x:c r="H165" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
+        <x:v>GM Genuine Parts catalog — Confirmed AFM Lifter Collapse Requires Generation-Specific Diagnosis</x:v>
       </x:c>
       <x:c r="I165" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+        <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
       <x:c r="J165" s="9" t="str">
-        <x:v>2010-2020 Cadillac Escalade diagnosis, VIN/RPO confirmation and repair</x:v>
+        <x:v>2010-2020 Cadillac Escalade; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
       <x:c r="K165" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
+        <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
       <x:c r="L165" s="9" t="str"/>
       <x:c r="M165" s="9" t="str"/>
       <x:c r="N165" s="41" t="str"/>
     </x:row>
-    <x:row r="166" ht="844.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A166" s="40" t="n">
+    <x:row r="166" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A166" s="40" t="str"/>
+      <x:c r="B166" s="9" t="str"/>
+      <x:c r="C166" s="9" t="str"/>
+      <x:c r="D166" s="9" t="str"/>
+      <x:c r="E166" s="9" t="str"/>
+      <x:c r="F166" s="9" t="str"/>
+      <x:c r="G166" s="9" t="str"/>
+      <x:c r="H166" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I166" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J166" s="9" t="str">
+        <x:v>2010-2020 Cadillac Escalade diagnosis, VIN/RPO confirmation and repair</x:v>
+      </x:c>
+      <x:c r="K166" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L166" s="9" t="str"/>
+      <x:c r="M166" s="9" t="str"/>
+      <x:c r="N166" s="41" t="str"/>
+    </x:row>
+    <x:row r="167" ht="844.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A167" s="40" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B166" s="9" t="str">
+      <x:c r="B167" s="9" t="str">
         <x:v>cadillac-escalade-air-suspension-2007</x:v>
       </x:c>
-      <x:c r="C166" s="9" t="str">
+      <x:c r="C167" s="9" t="str">
         <x:v>2007-2014 | Cadillac | Escalade</x:v>
       </x:c>
-      <x:c r="D166" s="9" t="str">
+      <x:c r="D167" s="9" t="str">
         <x:v>Service Suspension or Low Ride Height Needs Level-Control Diagnosis</x:v>
       </x:c>
-      <x:c r="E166" s="9" t="str">
+      <x:c r="E167" s="9" t="str">
         <x:v>Confirm RPO Z55 or Z95, model year, DTCs, load condition and visible hose condition, then follow the matching PIT4954D branch. Apply the pressure-sensor wiring check only to 2009 and earlier vehicles; use the moisture or inlet-hose path only when its stated condition is present. Do not treat a missing key-up compressor run by itself as a failure: startup operation occurs only below 10 psi, typically after a long park or when a small leak already exists. GM warns against replacing the complete compressor for these conditions.</x:v>
       </x:c>
-      <x:c r="F166" s="9" t="str">
+      <x:c r="F167" s="9" t="str">
         <x:v>Confirm RPO Z55 or Z95, model year, DTCs, load condition and visible hose condition, then follow the matching PIT4954D branch. Apply the pressure-sensor wiring check only to 2009 and earlier vehicles; use the moisture or inlet-hose path only when its stated condition is present. Do not treat a missing key-up compressor run by itself as a failure: startup operation occurs only below 10 psi, typically after a long park or when a small leak already exists. GM warns against replacing the complete compressor for these conditions.</x:v>
       </x:c>
-      <x:c r="G166" s="9" t="str">
+      <x:c r="G167" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H166" s="9" t="str">
+      <x:c r="H167" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Service Suspension or Low Ride Height Needs Level-Control Diagnosis</x:v>
       </x:c>
-      <x:c r="I166" s="9" t="str">
+      <x:c r="I167" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J166" s="9" t="str">
+      <x:c r="J167" s="9" t="str">
         <x:v>2007-2014 Cadillac Escalade; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K166" s="9" t="str">
+      <x:c r="K167" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L166" s="9" t="str"/>
-      <x:c r="M166" s="9" t="str">
+      <x:c r="L167" s="9" t="str"/>
+      <x:c r="M167" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N166" s="41" t="str">
+      <x:c r="N167" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A167" s="40" t="str"/>
-      <x:c r="B167" s="9" t="str"/>
-      <x:c r="C167" s="9" t="str"/>
-      <x:c r="D167" s="9" t="str"/>
-      <x:c r="E167" s="9" t="str"/>
-      <x:c r="F167" s="9" t="str"/>
-      <x:c r="G167" s="9" t="str"/>
-      <x:c r="H167" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I167" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J167" s="9" t="str">
+    <x:row r="168" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A168" s="40" t="str"/>
+      <x:c r="B168" s="9" t="str"/>
+      <x:c r="C168" s="9" t="str"/>
+      <x:c r="D168" s="9" t="str"/>
+      <x:c r="E168" s="9" t="str"/>
+      <x:c r="F168" s="9" t="str"/>
+      <x:c r="G168" s="9" t="str"/>
+      <x:c r="H168" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I168" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J168" s="9" t="str">
         <x:v>2007-2014 Cadillac Escalade diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K167" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L167" s="9" t="str"/>
-      <x:c r="M167" s="9" t="str"/>
-      <x:c r="N167" s="41" t="str"/>
-    </x:row>
-    <x:row r="168" ht="712.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A168" s="40" t="n">
+      <x:c r="K168" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L168" s="9" t="str"/>
+      <x:c r="M168" s="9" t="str"/>
+      <x:c r="N168" s="41" t="str"/>
+    </x:row>
+    <x:row r="169" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A169" s="40" t="n">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B168" s="9" t="str">
+      <x:c r="B169" s="9" t="str">
         <x:v>cadillac-escalade-brake-lines-2007</x:v>
       </x:c>
-      <x:c r="C168" s="9" t="str">
+      <x:c r="C169" s="9" t="str">
         <x:v>2007-2014 | Cadillac | Escalade</x:v>
       </x:c>
-      <x:c r="D168" s="9" t="str">
+      <x:c r="D169" s="9" t="str">
         <x:v>Brake Line Corrosion and Failure (Rust Belt)</x:v>
       </x:c>
-      <x:c r="E168" s="9" t="str">
+      <x:c r="E169" s="9" t="str">
         <x:v>Inspect all brake lines thoroughly, particularly along the frame rail and near the rear axle. Replace any corroded lines immediately. Dorman offers pre-bent stainless steel replacement brake line kits that are corrosion-resistant and direct-fit. The entire vehicle brake line set should be replaced if significant corrosion is found - partial replacement leaves other corroded lines ready to fail. This is a safety-critical repair that should not be delayed.</x:v>
       </x:c>
-      <x:c r="F168" s="9" t="str">
+      <x:c r="F169" s="9" t="str">
         <x:v>Inspect all brake lines thoroughly, particularly along the frame rail and near the rear axle. Replace any corroded lines immediately. Dorman offers pre-bent stainless steel replacement brake line kits that are corrosion-resistant and direct-fit. The entire vehicle brake line set should be replaced if significant corrosion is found - partial replacement leaves other corroded lines ready to fail. This is a safety-critical repair that should not be delayed.</x:v>
       </x:c>
-      <x:c r="G168" s="9" t="str">
+      <x:c r="G169" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H168" s="9" t="str">
+      <x:c r="H169" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Brake Line Corrosion and Failure</x:v>
       </x:c>
-      <x:c r="I168" s="9" t="str">
+      <x:c r="I169" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J168" s="9" t="str">
+      <x:c r="J169" s="9" t="str">
         <x:v>2007-2014 Cadillac Escalade; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K168" s="9" t="str">
+      <x:c r="K169" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L168" s="9" t="str"/>
-      <x:c r="M168" s="9" t="str">
+      <x:c r="L169" s="9" t="str"/>
+      <x:c r="M169" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N168" s="41" t="str">
+      <x:c r="N169" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A169" s="40" t="str"/>
-      <x:c r="B169" s="9" t="str"/>
-      <x:c r="C169" s="9" t="str"/>
-      <x:c r="D169" s="9" t="str"/>
-      <x:c r="E169" s="9" t="str"/>
-      <x:c r="F169" s="9" t="str"/>
-      <x:c r="G169" s="9" t="str"/>
-      <x:c r="H169" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I169" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J169" s="9" t="str">
+    <x:row r="170" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A170" s="40" t="str"/>
+      <x:c r="B170" s="9" t="str"/>
+      <x:c r="C170" s="9" t="str"/>
+      <x:c r="D170" s="9" t="str"/>
+      <x:c r="E170" s="9" t="str"/>
+      <x:c r="F170" s="9" t="str"/>
+      <x:c r="G170" s="9" t="str"/>
+      <x:c r="H170" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I170" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J170" s="9" t="str">
         <x:v>2007-2014 Cadillac Escalade diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K169" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L169" s="9" t="str"/>
-      <x:c r="M169" s="9" t="str"/>
-      <x:c r="N169" s="41" t="str"/>
-    </x:row>
-    <x:row r="170" ht="831.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A170" s="40" t="n">
+      <x:c r="K170" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L170" s="9" t="str"/>
+      <x:c r="M170" s="9" t="str"/>
+      <x:c r="N170" s="41" t="str"/>
+    </x:row>
+    <x:row r="171" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A171" s="40" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B170" s="9" t="str">
+      <x:c r="B171" s="9" t="str">
         <x:v>cadillac-escalade-esv-air-ride-2007</x:v>
       </x:c>
-      <x:c r="C170" s="9" t="str">
+      <x:c r="C171" s="9" t="str">
         <x:v>2007-2013 | Cadillac | Escalade ESV</x:v>
       </x:c>
-      <x:c r="D170" s="9" t="str">
+      <x:c r="D171" s="9" t="str">
         <x:v>Rear Level-Control Message or Low Ride Height Needs Circuit Diagnosis</x:v>
       </x:c>
-      <x:c r="E170" s="9" t="str">
+      <x:c r="E171" s="9" t="str">
         <x:v>Confirm RPO Z55 or Z95, model year, DTCs, load condition and visible hose condition, then follow the matching PIT4954C branch. Apply the pressure-sensor wiring check only to 2007-2009 vehicles; use the moisture or inlet-hose path only when its stated condition is present. Do not treat a missing key-up compressor run by itself as a failure: startup operation occurs only below 10 psi, typically after a long park or when a small leak already exists. GM warns against replacing the complete compressor for these conditions.</x:v>
       </x:c>
-      <x:c r="F170" s="9" t="str">
+      <x:c r="F171" s="9" t="str">
         <x:v>Confirm RPO Z55 or Z95, model year, DTCs, load condition and visible hose condition, then follow the matching PIT4954C branch. Apply the pressure-sensor wiring check only to 2007-2009 vehicles; use the moisture or inlet-hose path only when its stated condition is present. Do not treat a missing key-up compressor run by itself as a failure: startup operation occurs only below 10 psi, typically after a long park or when a small leak already exists. GM warns against replacing the complete compressor for these conditions.</x:v>
       </x:c>
-      <x:c r="G170" s="9" t="str">
+      <x:c r="G171" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H170" s="9" t="str">
+      <x:c r="H171" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Rear Level-Control Message or Low Ride Height Needs Circuit Diagnosis</x:v>
       </x:c>
-      <x:c r="I170" s="9" t="str">
+      <x:c r="I171" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J170" s="9" t="str">
+      <x:c r="J171" s="9" t="str">
         <x:v>2007-2013 Cadillac Escalade ESV; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K170" s="9" t="str">
+      <x:c r="K171" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L170" s="9" t="str"/>
-      <x:c r="M170" s="9" t="str">
+      <x:c r="L171" s="9" t="str"/>
+      <x:c r="M171" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N170" s="41" t="str">
+      <x:c r="N171" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A171" s="40" t="str"/>
-      <x:c r="B171" s="9" t="str"/>
-      <x:c r="C171" s="9" t="str"/>
-      <x:c r="D171" s="9" t="str"/>
-      <x:c r="E171" s="9" t="str"/>
-      <x:c r="F171" s="9" t="str"/>
-      <x:c r="G171" s="9" t="str"/>
-      <x:c r="H171" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I171" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J171" s="9" t="str">
+    <x:row r="172" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A172" s="40" t="str"/>
+      <x:c r="B172" s="9" t="str"/>
+      <x:c r="C172" s="9" t="str"/>
+      <x:c r="D172" s="9" t="str"/>
+      <x:c r="E172" s="9" t="str"/>
+      <x:c r="F172" s="9" t="str"/>
+      <x:c r="G172" s="9" t="str"/>
+      <x:c r="H172" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I172" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J172" s="9" t="str">
         <x:v>2007-2013 Cadillac Escalade ESV diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K171" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L171" s="9" t="str"/>
-      <x:c r="M171" s="9" t="str"/>
-      <x:c r="N171" s="41" t="str"/>
-    </x:row>
-    <x:row r="172" ht="660" hidden="0" customHeight="1">
-      <x:c r="A172" s="40" t="n">
+      <x:c r="K172" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L172" s="9" t="str"/>
+      <x:c r="M172" s="9" t="str"/>
+      <x:c r="N172" s="41" t="str"/>
+    </x:row>
+    <x:row r="173" ht="660" hidden="0" customHeight="1">
+      <x:c r="A173" s="40" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B172" s="9" t="str">
+      <x:c r="B173" s="9" t="str">
         <x:v>cadillac-escalade-esv-air-suspension-2002</x:v>
       </x:c>
-      <x:c r="C172" s="9" t="str">
+      <x:c r="C173" s="9" t="str">
         <x:v>2003-2006 | Cadillac | Escalade ESV</x:v>
       </x:c>
-      <x:c r="D172" s="9" t="str">
+      <x:c r="D173" s="9" t="str">
         <x:v>Early Escalade ESV Level-Control Faults Need Sensor and Inlet Diagnosis</x:v>
       </x:c>
-      <x:c r="E172" s="9" t="str">
+      <x:c r="E173" s="9" t="str">
         <x:v>Confirm the model year, suspension RPO, DTCs, load condition and visible hose condition, then follow only the matching PIT4954C branch. Do not treat a missing key-up compressor run by itself as a failure: startup operation occurs only below 10 psi, typically after a long park or when a small leak already exists. Do not replace the complete compressor or convert the suspension solely from this symptom card.</x:v>
       </x:c>
-      <x:c r="F172" s="9" t="str">
+      <x:c r="F173" s="9" t="str">
         <x:v>Confirm the model year, suspension RPO, DTCs, load condition and visible hose condition, then follow only the matching PIT4954C branch. Do not treat a missing key-up compressor run by itself as a failure: startup operation occurs only below 10 psi, typically after a long park or when a small leak already exists. Do not replace the complete compressor or convert the suspension solely from this symptom card.</x:v>
       </x:c>
-      <x:c r="G172" s="9" t="str">
+      <x:c r="G173" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H172" s="9" t="str">
+      <x:c r="H173" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Early Escalade ESV Level-Control Faults Need Sensor and Inlet Diagnosis</x:v>
       </x:c>
-      <x:c r="I172" s="9" t="str">
+      <x:c r="I173" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J172" s="9" t="str">
+      <x:c r="J173" s="9" t="str">
         <x:v>2003-2006 Cadillac Escalade ESV; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K172" s="9" t="str">
+      <x:c r="K173" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L172" s="9" t="str"/>
-      <x:c r="M172" s="9" t="str">
+      <x:c r="L173" s="9" t="str"/>
+      <x:c r="M173" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N172" s="41" t="str">
+      <x:c r="N173" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A173" s="40" t="str"/>
-      <x:c r="B173" s="9" t="str"/>
-      <x:c r="C173" s="9" t="str"/>
-      <x:c r="D173" s="9" t="str"/>
-      <x:c r="E173" s="9" t="str"/>
-      <x:c r="F173" s="9" t="str"/>
-      <x:c r="G173" s="9" t="str"/>
-      <x:c r="H173" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I173" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J173" s="9" t="str">
+    <x:row r="174" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A174" s="40" t="str"/>
+      <x:c r="B174" s="9" t="str"/>
+      <x:c r="C174" s="9" t="str"/>
+      <x:c r="D174" s="9" t="str"/>
+      <x:c r="E174" s="9" t="str"/>
+      <x:c r="F174" s="9" t="str"/>
+      <x:c r="G174" s="9" t="str"/>
+      <x:c r="H174" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I174" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J174" s="9" t="str">
         <x:v>2003-2006 Cadillac Escalade ESV diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K173" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L173" s="9" t="str"/>
-      <x:c r="M173" s="9" t="str"/>
-      <x:c r="N173" s="41" t="str"/>
-    </x:row>
-    <x:row r="174" ht="554.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A174" s="40" t="n">
+      <x:c r="K174" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L174" s="9" t="str"/>
+      <x:c r="M174" s="9" t="str"/>
+      <x:c r="N174" s="41" t="str"/>
+    </x:row>
+    <x:row r="175" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A175" s="40" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B174" s="9" t="str">
+      <x:c r="B175" s="9" t="str">
         <x:v>cadillac-escalade-esv-liftgate-struts-2007</x:v>
       </x:c>
-      <x:c r="C174" s="9" t="str">
+      <x:c r="C175" s="9" t="str">
         <x:v>2007-2014 | Cadillac | Escalade ESV</x:v>
       </x:c>
-      <x:c r="D174" s="9" t="str">
+      <x:c r="D175" s="9" t="str">
         <x:v>Power Liftgate Strut Failure and Liftgate Falling</x:v>
       </x:c>
-      <x:c r="E174" s="9" t="str">
+      <x:c r="E175" s="9" t="str">
         <x:v>Replace both liftgate gas struts together — they are inexpensive ($30-60/pair) and easy to replace with a flathead screwdriver to pop the ball studs. If the power liftgate motor has failed, the motor assembly (GM 25965765) requires interior trim panel removal but is a 1-hour DIY job. Lubricate latch mechanism with white lithium grease annually.</x:v>
       </x:c>
-      <x:c r="F174" s="9" t="str">
+      <x:c r="F175" s="9" t="str">
         <x:v>Replace both liftgate gas struts together — they are inexpensive ($30-60/pair) and easy to replace with a flathead screwdriver to pop the ball studs. If the power liftgate motor has failed, the motor assembly (GM 25965765) requires interior trim panel removal but is a 1-hour DIY job. Lubricate latch mechanism with white lithium grease annually.</x:v>
       </x:c>
-      <x:c r="G174" s="9" t="str">
+      <x:c r="G175" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H174" s="9" t="str">
+      <x:c r="H175" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Power Liftgate Strut Failure and Liftgate Falling</x:v>
       </x:c>
-      <x:c r="I174" s="9" t="str">
+      <x:c r="I175" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J174" s="9" t="str">
+      <x:c r="J175" s="9" t="str">
         <x:v>2007-2014 Cadillac Escalade ESV; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K174" s="9" t="str">
+      <x:c r="K175" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L174" s="9" t="str"/>
-      <x:c r="M174" s="9" t="str">
+      <x:c r="L175" s="9" t="str"/>
+      <x:c r="M175" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N174" s="41" t="str">
+      <x:c r="N175" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A175" s="40" t="str"/>
-      <x:c r="B175" s="9" t="str"/>
-      <x:c r="C175" s="9" t="str"/>
-      <x:c r="D175" s="9" t="str"/>
-      <x:c r="E175" s="9" t="str"/>
-      <x:c r="F175" s="9" t="str"/>
-      <x:c r="G175" s="9" t="str"/>
-      <x:c r="H175" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I175" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J175" s="9" t="str">
+    <x:row r="176" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A176" s="40" t="str"/>
+      <x:c r="B176" s="9" t="str"/>
+      <x:c r="C176" s="9" t="str"/>
+      <x:c r="D176" s="9" t="str"/>
+      <x:c r="E176" s="9" t="str"/>
+      <x:c r="F176" s="9" t="str"/>
+      <x:c r="G176" s="9" t="str"/>
+      <x:c r="H176" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I176" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J176" s="9" t="str">
         <x:v>2007-2014 Cadillac Escalade ESV diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K175" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L175" s="9" t="str"/>
-      <x:c r="M175" s="9" t="str"/>
-      <x:c r="N175" s="41" t="str"/>
-    </x:row>
-    <x:row r="176" ht="409.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A176" s="40" t="n">
+      <x:c r="K176" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L176" s="9" t="str"/>
+      <x:c r="M176" s="9" t="str"/>
+      <x:c r="N176" s="41" t="str"/>
+    </x:row>
+    <x:row r="177" ht="409.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A177" s="40" t="n">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B176" s="9" t="str">
+      <x:c r="B177" s="9" t="str">
         <x:v>cadillac-escalade-esv-transfer-case-2002</x:v>
       </x:c>
-      <x:c r="C176" s="9" t="str">
+      <x:c r="C177" s="9" t="str">
         <x:v>2002-2020 | Cadillac | Escalade ESV</x:v>
       </x:c>
-      <x:c r="D176" s="9" t="str">
+      <x:c r="D177" s="9" t="str">
         <x:v>Transfer Case Encoder Motor and Position Sensor Failure</x:v>
       </x:c>
-      <x:c r="E176" s="9" t="str">
+      <x:c r="E177" s="9" t="str">
         <x:v>Replace the encoder motor on the transfer case. The motor is externally mounted and accessible. After replacement, a transfer case relearn procedure must be performed with a scan tool. Check and top off the transfer case fluid with the correct Auto-Trak II fluid.</x:v>
       </x:c>
-      <x:c r="F176" s="9" t="str">
+      <x:c r="F177" s="9" t="str">
         <x:v>Replace the encoder motor on the transfer case. The motor is externally mounted and accessible. After replacement, a transfer case relearn procedure must be performed with a scan tool. Check and top off the transfer case fluid with the correct Auto-Trak II fluid.</x:v>
       </x:c>
-      <x:c r="G176" s="9" t="str">
+      <x:c r="G177" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H176" s="9" t="str">
+      <x:c r="H177" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Transfer Case Encoder Motor and Position Sensor Failure</x:v>
       </x:c>
-      <x:c r="I176" s="9" t="str">
+      <x:c r="I177" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J176" s="9" t="str">
+      <x:c r="J177" s="9" t="str">
         <x:v>2002-2020 Cadillac Escalade ESV; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K176" s="9" t="str">
+      <x:c r="K177" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L176" s="9" t="str"/>
-      <x:c r="M176" s="9" t="str">
+      <x:c r="L177" s="9" t="str"/>
+      <x:c r="M177" s="9" t="str">
         <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
       </x:c>
-      <x:c r="N176" s="41" t="str">
+      <x:c r="N177" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A177" s="40" t="str"/>
-      <x:c r="B177" s="9" t="str"/>
-      <x:c r="C177" s="9" t="str"/>
-      <x:c r="D177" s="9" t="str"/>
-      <x:c r="E177" s="9" t="str"/>
-      <x:c r="F177" s="9" t="str"/>
-      <x:c r="G177" s="9" t="str"/>
-      <x:c r="H177" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I177" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J177" s="9" t="str">
+    <x:row r="178" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A178" s="40" t="str"/>
+      <x:c r="B178" s="9" t="str"/>
+      <x:c r="C178" s="9" t="str"/>
+      <x:c r="D178" s="9" t="str"/>
+      <x:c r="E178" s="9" t="str"/>
+      <x:c r="F178" s="9" t="str"/>
+      <x:c r="G178" s="9" t="str"/>
+      <x:c r="H178" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I178" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J178" s="9" t="str">
         <x:v>2002-2020 Cadillac Escalade ESV diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K177" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L177" s="9" t="str"/>
-      <x:c r="M177" s="9" t="str"/>
-      <x:c r="N177" s="41" t="str"/>
-    </x:row>
-    <x:row r="178" ht="792" hidden="0" customHeight="1">
-      <x:c r="A178" s="40" t="n">
+      <x:c r="K178" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L178" s="9" t="str"/>
+      <x:c r="M178" s="9" t="str"/>
+      <x:c r="N178" s="41" t="str"/>
+    </x:row>
+    <x:row r="179" ht="792" hidden="0" customHeight="1">
+      <x:c r="A179" s="40" t="n">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B178" s="9" t="str">
+      <x:c r="B179" s="9" t="str">
         <x:v>cadillac-escalade-instrument-cluster-2003</x:v>
       </x:c>
-      <x:c r="C178" s="9" t="str">
+      <x:c r="C179" s="9" t="str">
         <x:v>2003-2006 | Cadillac | Escalade</x:v>
       </x:c>
-      <x:c r="D178" s="9" t="str">
+      <x:c r="D179" s="9" t="str">
         <x:v>Instrument Cluster Gauge Failure (Stepper Motors)</x:v>
       </x:c>
-      <x:c r="E178" s="9" t="str">
+      <x:c r="E179" s="9" t="str">
         <x:v>Replace the stepper motors in the instrument cluster. This can be done by sending the cluster to a rebuild service (many online), doing it yourself with a stepper motor kit ($20-40 for motors), or buying a Dorman remanufactured cluster. The stepper motor replacement is a common DIY repair requiring basic soldering skills. Professional cluster rebuild services cost $150-250 and include all motors plus LED backlighting upgrade. Dorman offers complete remanufactured clusters.</x:v>
       </x:c>
-      <x:c r="F178" s="9" t="str">
+      <x:c r="F179" s="9" t="str">
         <x:v>Replace the stepper motors in the instrument cluster. This can be done by sending the cluster to a rebuild service (many online), doing it yourself with a stepper motor kit ($20-40 for motors), or buying a Dorman remanufactured cluster. The stepper motor replacement is a common DIY repair requiring basic soldering skills. Professional cluster rebuild services cost $150-250 and include all motors plus LED backlighting upgrade. Dorman offers complete remanufactured clusters.</x:v>
       </x:c>
-      <x:c r="G178" s="9" t="str">
+      <x:c r="G179" s="9" t="str">
         <x:v>SPECIALIST / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H178" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I178" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J178" s="9" t="str">
+      <x:c r="H179" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I179" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J179" s="9" t="str">
         <x:v>2003-2006 Cadillac Escalade diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K178" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L178" s="9" t="str"/>
-      <x:c r="M178" s="9" t="str">
-        <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
-      </x:c>
-      <x:c r="N178" s="41" t="str">
-        <x:v>Use a qualified specialist or manufacturer service route; no generic kit or one-size-fits-all part.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A179" s="40" t="n">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B179" s="9" t="str">
-        <x:v>cadillac-escalade-oil-consumption-2015</x:v>
-      </x:c>
-      <x:c r="C179" s="9" t="str">
-        <x:v>2015-2016 | Cadillac | Escalade | 6.2L L86 V8</x:v>
-      </x:c>
-      <x:c r="D179" s="9" t="str">
-        <x:v>L86 Oil Use Needs a Measured Consumption and PCV-Path Diagnosis</x:v>
-      </x:c>
-      <x:c r="E179" s="9" t="str">
-        <x:v>Check oil consistently after at least 15 minutes, document oil added and mileage, and inspect external leaks and PCV paths. Apply the piston/ring or LOMA/VLOM branch only when the bulletin criteria and build date match. Do not infer AFM causation, use a delete device, or order parts from this card.</x:v>
-      </x:c>
-      <x:c r="F179" s="9" t="str">
-        <x:v>Check oil consistently after at least 15 minutes, document oil added and mileage, and inspect external leaks and PCV paths. Apply the piston/ring or LOMA/VLOM branch only when the bulletin criteria and build date match. Do not infer AFM causation, use a delete device, or order parts from this card.</x:v>
-      </x:c>
-      <x:c r="G179" s="9" t="str">
-        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
-      </x:c>
-      <x:c r="H179" s="9" t="str">
-        <x:v>GM Genuine Parts catalog — L86 Oil Use Needs a Measured Consumption and PCV-Path Diagnosis</x:v>
-      </x:c>
-      <x:c r="I179" s="9" t="str">
-        <x:v>https://parts.gmparts.com/</x:v>
-      </x:c>
-      <x:c r="J179" s="9" t="str">
-        <x:v>2015-2016 Cadillac Escalade; select exact VIN, engine, trim, position and current supersession</x:v>
-      </x:c>
       <x:c r="K179" s="9" t="str">
-        <x:v>manufacturer VIN-select parts catalog</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L179" s="9" t="str"/>
       <x:c r="M179" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
       <x:c r="N179" s="41" t="str">
+        <x:v>Use a qualified specialist or manufacturer service route; no generic kit or one-size-fits-all part.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A180" s="40" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B180" s="9" t="str">
+        <x:v>cadillac-escalade-oil-consumption-2015</x:v>
+      </x:c>
+      <x:c r="C180" s="9" t="str">
+        <x:v>2015-2016 | Cadillac | Escalade | 6.2L L86 V8</x:v>
+      </x:c>
+      <x:c r="D180" s="9" t="str">
+        <x:v>L86 Oil Use Needs a Measured Consumption and PCV-Path Diagnosis</x:v>
+      </x:c>
+      <x:c r="E180" s="9" t="str">
+        <x:v>Check oil consistently after at least 15 minutes, document oil added and mileage, and inspect external leaks and PCV paths. Apply the piston/ring or LOMA/VLOM branch only when the bulletin criteria and build date match. Do not infer AFM causation, use a delete device, or order parts from this card.</x:v>
+      </x:c>
+      <x:c r="F180" s="9" t="str">
+        <x:v>Check oil consistently after at least 15 minutes, document oil added and mileage, and inspect external leaks and PCV paths. Apply the piston/ring or LOMA/VLOM branch only when the bulletin criteria and build date match. Do not infer AFM causation, use a delete device, or order parts from this card.</x:v>
+      </x:c>
+      <x:c r="G180" s="9" t="str">
+        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H180" s="9" t="str">
+        <x:v>GM Genuine Parts catalog — L86 Oil Use Needs a Measured Consumption and PCV-Path Diagnosis</x:v>
+      </x:c>
+      <x:c r="I180" s="9" t="str">
+        <x:v>https://parts.gmparts.com/</x:v>
+      </x:c>
+      <x:c r="J180" s="9" t="str">
+        <x:v>2015-2016 Cadillac Escalade; select exact VIN, engine, trim, position and current supersession</x:v>
+      </x:c>
+      <x:c r="K180" s="9" t="str">
+        <x:v>manufacturer VIN-select parts catalog</x:v>
+      </x:c>
+      <x:c r="L180" s="9" t="str"/>
+      <x:c r="M180" s="9" t="str">
+        <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
+      </x:c>
+      <x:c r="N180" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A180" s="40" t="str"/>
-      <x:c r="B180" s="9" t="str"/>
-      <x:c r="C180" s="9" t="str"/>
-      <x:c r="D180" s="9" t="str"/>
-      <x:c r="E180" s="9" t="str"/>
-      <x:c r="F180" s="9" t="str"/>
-      <x:c r="G180" s="9" t="str"/>
-      <x:c r="H180" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I180" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J180" s="9" t="str">
+    <x:row r="181" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A181" s="40" t="str"/>
+      <x:c r="B181" s="9" t="str"/>
+      <x:c r="C181" s="9" t="str"/>
+      <x:c r="D181" s="9" t="str"/>
+      <x:c r="E181" s="9" t="str"/>
+      <x:c r="F181" s="9" t="str"/>
+      <x:c r="G181" s="9" t="str"/>
+      <x:c r="H181" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I181" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J181" s="9" t="str">
         <x:v>2015-2016 Cadillac Escalade diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K180" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L180" s="9" t="str"/>
-      <x:c r="M180" s="9" t="str"/>
-      <x:c r="N180" s="41" t="str"/>
-    </x:row>
-    <x:row r="181" ht="712.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A181" s="40" t="n">
+      <x:c r="K181" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L181" s="9" t="str"/>
+      <x:c r="M181" s="9" t="str"/>
+      <x:c r="N181" s="41" t="str"/>
+    </x:row>
+    <x:row r="182" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A182" s="40" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B181" s="9" t="str">
+      <x:c r="B182" s="9" t="str">
         <x:v>cadillac-escalade-transfer-case-2007</x:v>
       </x:c>
-      <x:c r="C181" s="9" t="str">
+      <x:c r="C182" s="9" t="str">
         <x:v>2007-2020 | Cadillac | Escalade</x:v>
       </x:c>
-      <x:c r="D181" s="9" t="str">
+      <x:c r="D182" s="9" t="str">
         <x:v>Transfer Case Encoder Motor and Chain Failure</x:v>
       </x:c>
-      <x:c r="E181" s="9" t="str">
+      <x:c r="E182" s="9" t="str">
         <x:v>Diagnose the specific failure. The encoder motor (shift motor) is the most common failure and can be replaced independently for $300-600. Internal chain stretch requires transfer case rebuild or replacement. Regular transfer case fluid changes every 50,000 miles with Auto-Trak II fluid (NP149) or Dexron VI (NP246) can prevent premature wear. Some owners upgrade to a Merchant Automotive encoder motor for improved longevity.</x:v>
       </x:c>
-      <x:c r="F181" s="9" t="str">
+      <x:c r="F182" s="9" t="str">
         <x:v>Diagnose the specific failure. The encoder motor (shift motor) is the most common failure and can be replaced independently for $300-600. Internal chain stretch requires transfer case rebuild or replacement. Regular transfer case fluid changes every 50,000 miles with Auto-Trak II fluid (NP149) or Dexron VI (NP246) can prevent premature wear. Some owners upgrade to a Merchant Automotive encoder motor for improved longevity.</x:v>
       </x:c>
-      <x:c r="G181" s="9" t="str">
+      <x:c r="G182" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H181" s="9" t="str">
+      <x:c r="H182" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Transfer Case Encoder Motor and Chain Failure</x:v>
       </x:c>
-      <x:c r="I181" s="9" t="str">
+      <x:c r="I182" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J181" s="9" t="str">
+      <x:c r="J182" s="9" t="str">
         <x:v>2007-2020 Cadillac Escalade; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K181" s="9" t="str">
+      <x:c r="K182" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L181" s="9" t="str"/>
-      <x:c r="M181" s="9" t="str">
+      <x:c r="L182" s="9" t="str"/>
+      <x:c r="M182" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N181" s="41" t="str">
+      <x:c r="N182" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A182" s="40" t="str"/>
-      <x:c r="B182" s="9" t="str"/>
-      <x:c r="C182" s="9" t="str"/>
-      <x:c r="D182" s="9" t="str"/>
-      <x:c r="E182" s="9" t="str"/>
-      <x:c r="F182" s="9" t="str"/>
-      <x:c r="G182" s="9" t="str"/>
-      <x:c r="H182" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I182" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J182" s="9" t="str">
+    <x:row r="183" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A183" s="40" t="str"/>
+      <x:c r="B183" s="9" t="str"/>
+      <x:c r="C183" s="9" t="str"/>
+      <x:c r="D183" s="9" t="str"/>
+      <x:c r="E183" s="9" t="str"/>
+      <x:c r="F183" s="9" t="str"/>
+      <x:c r="G183" s="9" t="str"/>
+      <x:c r="H183" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I183" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J183" s="9" t="str">
         <x:v>2007-2020 Cadillac Escalade diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K182" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L182" s="9" t="str"/>
-      <x:c r="M182" s="9" t="str"/>
-      <x:c r="N182" s="41" t="str"/>
-    </x:row>
-    <x:row r="183" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A183" s="40" t="n">
+      <x:c r="K183" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L183" s="9" t="str"/>
+      <x:c r="M183" s="9" t="str"/>
+      <x:c r="N183" s="41" t="str"/>
+    </x:row>
+    <x:row r="184" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A184" s="40" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B183" s="9" t="str">
+      <x:c r="B184" s="9" t="str">
         <x:v>cadillac-escalade-transmission-shudder-2015</x:v>
       </x:c>
-      <x:c r="C183" s="9" t="str">
+      <x:c r="C184" s="9" t="str">
         <x:v>2015-2017 | Cadillac | Escalade | 6.2L L86 V8</x:v>
       </x:c>
-      <x:c r="D183" s="9" t="str">
+      <x:c r="D184" s="9" t="str">
         <x:v>8L90 Light-Throttle Shudder Has a Specific Fluid-Exchange Procedure</x:v>
       </x:c>
-      <x:c r="E183" s="9" t="str">
+      <x:c r="E184" s="9" t="str">
         <x:v>Confirm the exact L86/M5U configuration and symptom with scan and vibration data. The bulletin directs a one-time 20-quart Mobil 1 Synthetic LV ATF HP exchange and allows up to 200 miles or two cold-to-operating-temperature cycles. A returning concern requires normal diagnosis rather than automatic converter replacement.</x:v>
       </x:c>
-      <x:c r="F183" s="9" t="str">
+      <x:c r="F184" s="9" t="str">
         <x:v>Confirm the exact L86/M5U configuration and symptom with scan and vibration data. The bulletin directs a one-time 20-quart Mobil 1 Synthetic LV ATF HP exchange and allows up to 200 miles or two cold-to-operating-temperature cycles. A returning concern requires normal diagnosis rather than automatic converter replacement.</x:v>
       </x:c>
-      <x:c r="G183" s="9" t="str">
+      <x:c r="G184" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H183" s="9" t="str">
+      <x:c r="H184" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 8L90 Light-Throttle Shudder Has a Specific Fluid-Exchange Procedure</x:v>
       </x:c>
-      <x:c r="I183" s="9" t="str">
+      <x:c r="I184" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J183" s="9" t="str">
+      <x:c r="J184" s="9" t="str">
         <x:v>2015-2017 Cadillac Escalade; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K183" s="9" t="str">
+      <x:c r="K184" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L183" s="9" t="str"/>
-      <x:c r="M183" s="9" t="str">
+      <x:c r="L184" s="9" t="str"/>
+      <x:c r="M184" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N183" s="41" t="str">
+      <x:c r="N184" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A184" s="40" t="str"/>
-      <x:c r="B184" s="9" t="str"/>
-      <x:c r="C184" s="9" t="str"/>
-      <x:c r="D184" s="9" t="str"/>
-      <x:c r="E184" s="9" t="str"/>
-      <x:c r="F184" s="9" t="str"/>
-      <x:c r="G184" s="9" t="str"/>
-      <x:c r="H184" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I184" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J184" s="9" t="str">
+    <x:row r="185" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A185" s="40" t="str"/>
+      <x:c r="B185" s="9" t="str"/>
+      <x:c r="C185" s="9" t="str"/>
+      <x:c r="D185" s="9" t="str"/>
+      <x:c r="E185" s="9" t="str"/>
+      <x:c r="F185" s="9" t="str"/>
+      <x:c r="G185" s="9" t="str"/>
+      <x:c r="H185" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I185" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J185" s="9" t="str">
         <x:v>2015-2017 Cadillac Escalade diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K184" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L184" s="9" t="str"/>
-      <x:c r="M184" s="9" t="str"/>
-      <x:c r="N184" s="41" t="str"/>
-    </x:row>
-    <x:row r="185" ht="514.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A185" s="40" t="n">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B185" s="9" t="str">
-        <x:v>cadillac-escaladeesv-10-speed-10l8010l90-harsh-shifting-2021</x:v>
-      </x:c>
-      <x:c r="C185" s="9" t="str">
-        <x:v>2021-2025 | Cadillac | Escalade ESV | 6.2L L87 V8, 3.0L LM2 diesel, 6.2L LT4 V8</x:v>
-      </x:c>
-      <x:c r="D185" s="9" t="str">
-        <x:v>10-Speed Harsh Shift, Shudder or Flare Can Come From a Twisted Cooler Line</x:v>
-      </x:c>
-      <x:c r="E185" s="9" t="str">
-        <x:v>Verify the exact engine/transmission branch and DTCs, inspect the cooler lines for a twist or misshapen section, correct the routing or replace a confirmed damaged line, set fluid level and evaluate the thermal bypass valve as directed. Continue normal diagnosis if the concern remains; do not order transmission parts from this card.</x:v>
-      </x:c>
-      <x:c r="F185" s="9" t="str">
-        <x:v>Verify the exact engine/transmission branch and DTCs, inspect the cooler lines for a twist or misshapen section, correct the routing or replace a confirmed damaged line, set fluid level and evaluate the thermal bypass valve as directed. Continue normal diagnosis if the concern remains; do not order transmission parts from this card.</x:v>
-      </x:c>
-      <x:c r="G185" s="9" t="str">
-        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
-      </x:c>
-      <x:c r="H185" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I185" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J185" s="9" t="str">
-        <x:v>2021-2025 Cadillac Escalade ESV instruction-specific diagnosis</x:v>
-      </x:c>
       <x:c r="K185" s="9" t="str">
         <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L185" s="9" t="str"/>
-      <x:c r="M185" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
-      </x:c>
-      <x:c r="N185" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
+      <x:c r="M185" s="9" t="str"/>
+      <x:c r="N185" s="41" t="str"/>
     </x:row>
     <x:row r="186" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A186" s="40" t="n">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B186" s="9" t="str">
-        <x:v>cadillac-escaladeesv-62l-l87-connecting-rodbearing-2021</x:v>
+        <x:v>cadillac-escaladeesv-10-speed-10l8010l90-harsh-shifting-2021</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
-        <x:v>2021-2024 | Cadillac | Escalade ESV | 6.2L L87 V8</x:v>
+        <x:v>2021-2025 | Cadillac | Escalade ESV | 6.2L L87 V8, 3.0L LM2 diesel, 6.2L LT4 V8</x:v>
       </x:c>
       <x:c r="D186" s="9" t="str">
-        <x:v>L87 Connecting-Rod or Crankshaft Defect Can Cause Engine Failure (Recall 25V274)</x:v>
+        <x:v>10-Speed Harsh Shift, Shudder or Flare Can Come From a Twisted Cooler Line</x:v>
       </x:c>
       <x:c r="E186" s="9" t="str">
-        <x:v>Check the VIN and current recall assignment with Cadillac. GM routes involved vehicles through VIN-specific inspection and remedy instructions and replaces the engine when required at no charge. If abnormal engine noise, warning messages or loss of power occurs, stop safely and arrange dealer service or towing.</x:v>
+        <x:v>Verify the exact engine/transmission branch and DTCs, inspect the cooler lines for a twist or misshapen section, correct the routing or replace a confirmed damaged line, set fluid level and evaluate the thermal bypass valve as directed. Continue normal diagnosis if the concern remains; do not order transmission parts from this card.</x:v>
       </x:c>
       <x:c r="F186" s="9" t="str">
-        <x:v>Check the VIN and current recall assignment with Cadillac. GM routes involved vehicles through VIN-specific inspection and remedy instructions and replaces the engine when required at no charge. If abnormal engine noise, warning messages or loss of power occurs, stop safely and arrange dealer service or towing.</x:v>
+        <x:v>Verify the exact engine/transmission branch and DTCs, inspect the cooler lines for a twist or misshapen section, correct the routing or replace a confirmed damaged line, set fluid level and evaluate the thermal bypass valve as directed. Continue normal diagnosis if the concern remains; do not order transmission parts from this card.</x:v>
       </x:c>
       <x:c r="G186" s="9" t="str">
-        <x:v>RECALL ROUTES ONLY</x:v>
+        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
       <x:c r="H186" s="9" t="str">
         <x:v>Cadillac certified-service locator</x:v>
@@ -7087,378 +7071,378 @@
         <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
       </x:c>
       <x:c r="J186" s="9" t="str">
-        <x:v>2021-2024 Cadillac Escalade ESV VIN/campaign completion and free remedy</x:v>
+        <x:v>2021-2025 Cadillac Escalade ESV instruction-specific diagnosis</x:v>
       </x:c>
       <x:c r="K186" s="9" t="str">
-        <x:v>authorized recall service</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L186" s="9" t="str"/>
       <x:c r="M186" s="9" t="str">
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+      </x:c>
+      <x:c r="N186" s="41" t="str">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="514.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A187" s="40" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B187" s="9" t="str">
+        <x:v>cadillac-escaladeesv-62l-l87-connecting-rodbearing-2021</x:v>
+      </x:c>
+      <x:c r="C187" s="9" t="str">
+        <x:v>2021-2024 | Cadillac | Escalade ESV | 6.2L L87 V8</x:v>
+      </x:c>
+      <x:c r="D187" s="9" t="str">
+        <x:v>L87 Connecting-Rod or Crankshaft Defect Can Cause Engine Failure (Recall 25V274)</x:v>
+      </x:c>
+      <x:c r="E187" s="9" t="str">
+        <x:v>Check the VIN and current recall assignment with Cadillac. GM routes involved vehicles through VIN-specific inspection and remedy instructions and replaces the engine when required at no charge. If abnormal engine noise, warning messages or loss of power occurs, stop safely and arrange dealer service or towing.</x:v>
+      </x:c>
+      <x:c r="F187" s="9" t="str">
+        <x:v>Check the VIN and current recall assignment with Cadillac. GM routes involved vehicles through VIN-specific inspection and remedy instructions and replaces the engine when required at no charge. If abnormal engine noise, warning messages or loss of power occurs, stop safely and arrange dealer service or towing.</x:v>
+      </x:c>
+      <x:c r="G187" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H187" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I187" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J187" s="9" t="str">
+        <x:v>2021-2024 Cadillac Escalade ESV VIN/campaign completion and free remedy</x:v>
+      </x:c>
+      <x:c r="K187" s="9" t="str">
+        <x:v>authorized recall service</x:v>
+      </x:c>
+      <x:c r="L187" s="9" t="str"/>
+      <x:c r="M187" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N186" s="41" t="str">
+      <x:c r="N187" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="66" hidden="0" customHeight="1">
-      <x:c r="A187" s="40" t="str"/>
-      <x:c r="B187" s="9" t="str"/>
-      <x:c r="C187" s="9" t="str"/>
-      <x:c r="D187" s="9" t="str"/>
-      <x:c r="E187" s="9" t="str"/>
-      <x:c r="F187" s="9" t="str"/>
-      <x:c r="G187" s="9" t="str"/>
-      <x:c r="H187" s="9" t="str">
+    <x:row r="188" ht="66" hidden="0" customHeight="1">
+      <x:c r="A188" s="40" t="str"/>
+      <x:c r="B188" s="9" t="str"/>
+      <x:c r="C188" s="9" t="str"/>
+      <x:c r="D188" s="9" t="str"/>
+      <x:c r="E188" s="9" t="str"/>
+      <x:c r="F188" s="9" t="str"/>
+      <x:c r="G188" s="9" t="str"/>
+      <x:c r="H188" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I187" s="9" t="str">
+      <x:c r="I188" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J187" s="9" t="str">
+      <x:c r="J188" s="9" t="str">
         <x:v>2021-2024 Cadillac Escalade ESV VIN history</x:v>
       </x:c>
-      <x:c r="K187" s="9" t="str">
+      <x:c r="K188" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L187" s="9" t="str"/>
-      <x:c r="M187" s="9" t="str"/>
-      <x:c r="N187" s="41" t="str"/>
-    </x:row>
-    <x:row r="188" ht="831.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A188" s="40" t="n">
+      <x:c r="L188" s="9" t="str"/>
+      <x:c r="M188" s="9" t="str"/>
+      <x:c r="N188" s="41" t="str"/>
+    </x:row>
+    <x:row r="189" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A189" s="40" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B188" s="9" t="str">
+      <x:c r="B189" s="9" t="str">
         <x:v>cadillac-escaladeesv-intermittent-no-start-battery-drain-2021</x:v>
       </x:c>
-      <x:c r="C188" s="9" t="str">
+      <x:c r="C189" s="9" t="str">
         <x:v>2021-2025 | Cadillac | Escalade ESV</x:v>
       </x:c>
-      <x:c r="D188" s="9" t="str">
+      <x:c r="D189" s="9" t="str">
         <x:v>Dead Battery or No-Crank Can Come From the Alarm Glass-Breakage Loop</x:v>
       </x:c>
-      <x:c r="E188" s="9" t="str">
+      <x:c r="E189" s="9" t="str">
         <x:v>Have a qualified technician confirm the theft-alarm RPO and reproduce the draw with the vehicle closed and locked when needed. PIT5993D requires de-energizing and isolating the specified battery and BCM connections, checking BCM X7 terminal 27 tension with the specified test probe, and measuring the glass-breakage loop at the prescribed BCM ground terminals; the complete loop should be under 20 ohms. Repair confirmed high resistance, then test the battery. Do not order one from this card.</x:v>
       </x:c>
-      <x:c r="F188" s="9" t="str">
+      <x:c r="F189" s="9" t="str">
         <x:v>Have a qualified technician confirm the theft-alarm RPO and reproduce the draw with the vehicle closed and locked when needed. PIT5993D requires de-energizing and isolating the specified battery and BCM connections, checking BCM X7 terminal 27 tension with the specified test probe, and measuring the glass-breakage loop at the prescribed BCM ground terminals; the complete loop should be under 20 ohms. Repair confirmed high resistance, then test the battery. Do not order one from this card.</x:v>
       </x:c>
-      <x:c r="G188" s="9" t="str">
+      <x:c r="G189" s="9" t="str">
         <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
-      <x:c r="H188" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I188" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J188" s="9" t="str">
+      <x:c r="H189" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I189" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J189" s="9" t="str">
         <x:v>2021-2025 Cadillac Escalade ESV instruction-specific diagnosis</x:v>
       </x:c>
-      <x:c r="K188" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L188" s="9" t="str"/>
-      <x:c r="M188" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
-      </x:c>
-      <x:c r="N188" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" ht="356.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A189" s="40" t="n">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B189" s="9" t="str">
-        <x:v>cadillac-escaladeesv-oled-curved-display-blackout-2021</x:v>
-      </x:c>
-      <x:c r="C189" s="9" t="str">
-        <x:v>2021-2021 | Cadillac | Escalade ESV</x:v>
-      </x:c>
-      <x:c r="D189" s="9" t="str">
-        <x:v>Black Radio Screen With U023C and B1A62-86 Needs VPM Recovery</x:v>
-      </x:c>
-      <x:c r="E189" s="9" t="str">
-        <x:v>Confirm the exact display pattern, RPO and DTCs. The GM procedure removes VPM fuse F28 for one minute, reinstalls it and has the dealer reprogram the K157 Video Processing Module. Do not replace the OLED display from this card.</x:v>
-      </x:c>
-      <x:c r="F189" s="9" t="str">
-        <x:v>Confirm the exact display pattern, RPO and DTCs. The GM procedure removes VPM fuse F28 for one minute, reinstalls it and has the dealer reprogram the K157 Video Processing Module. Do not replace the OLED display from this card.</x:v>
-      </x:c>
-      <x:c r="G189" s="9" t="str">
-        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
-      </x:c>
-      <x:c r="H189" s="9" t="str">
-        <x:v>GM Genuine Parts catalog — Black Radio Screen With U023C and B1A62-86 Needs VPM Recovery</x:v>
-      </x:c>
-      <x:c r="I189" s="9" t="str">
-        <x:v>https://parts.gmparts.com/</x:v>
-      </x:c>
-      <x:c r="J189" s="9" t="str">
-        <x:v>2021-2021 Cadillac Escalade ESV; select exact VIN, engine, trim, position and current supersession</x:v>
-      </x:c>
       <x:c r="K189" s="9" t="str">
-        <x:v>manufacturer VIN-select parts catalog</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L189" s="9" t="str"/>
       <x:c r="M189" s="9" t="str">
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+      </x:c>
+      <x:c r="N189" s="41" t="str">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="356.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A190" s="40" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B190" s="9" t="str">
+        <x:v>cadillac-escaladeesv-oled-curved-display-blackout-2021</x:v>
+      </x:c>
+      <x:c r="C190" s="9" t="str">
+        <x:v>2021-2021 | Cadillac | Escalade ESV</x:v>
+      </x:c>
+      <x:c r="D190" s="9" t="str">
+        <x:v>Black Radio Screen With U023C and B1A62-86 Needs VPM Recovery</x:v>
+      </x:c>
+      <x:c r="E190" s="9" t="str">
+        <x:v>Confirm the exact display pattern, RPO and DTCs. The GM procedure removes VPM fuse F28 for one minute, reinstalls it and has the dealer reprogram the K157 Video Processing Module. Do not replace the OLED display from this card.</x:v>
+      </x:c>
+      <x:c r="F190" s="9" t="str">
+        <x:v>Confirm the exact display pattern, RPO and DTCs. The GM procedure removes VPM fuse F28 for one minute, reinstalls it and has the dealer reprogram the K157 Video Processing Module. Do not replace the OLED display from this card.</x:v>
+      </x:c>
+      <x:c r="G190" s="9" t="str">
+        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H190" s="9" t="str">
+        <x:v>GM Genuine Parts catalog — Black Radio Screen With U023C and B1A62-86 Needs VPM Recovery</x:v>
+      </x:c>
+      <x:c r="I190" s="9" t="str">
+        <x:v>https://parts.gmparts.com/</x:v>
+      </x:c>
+      <x:c r="J190" s="9" t="str">
+        <x:v>2021-2021 Cadillac Escalade ESV; select exact VIN, engine, trim, position and current supersession</x:v>
+      </x:c>
+      <x:c r="K190" s="9" t="str">
+        <x:v>manufacturer VIN-select parts catalog</x:v>
+      </x:c>
+      <x:c r="L190" s="9" t="str"/>
+      <x:c r="M190" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N189" s="41" t="str">
+      <x:c r="N190" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A190" s="40" t="str"/>
-      <x:c r="B190" s="9" t="str"/>
-      <x:c r="C190" s="9" t="str"/>
-      <x:c r="D190" s="9" t="str"/>
-      <x:c r="E190" s="9" t="str"/>
-      <x:c r="F190" s="9" t="str"/>
-      <x:c r="G190" s="9" t="str"/>
-      <x:c r="H190" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I190" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J190" s="9" t="str">
+    <x:row r="191" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A191" s="40" t="str"/>
+      <x:c r="B191" s="9" t="str"/>
+      <x:c r="C191" s="9" t="str"/>
+      <x:c r="D191" s="9" t="str"/>
+      <x:c r="E191" s="9" t="str"/>
+      <x:c r="F191" s="9" t="str"/>
+      <x:c r="G191" s="9" t="str"/>
+      <x:c r="H191" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I191" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J191" s="9" t="str">
         <x:v>2021-2021 Cadillac Escalade ESV diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K190" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L190" s="9" t="str"/>
-      <x:c r="M190" s="9" t="str"/>
-      <x:c r="N190" s="41" t="str"/>
-    </x:row>
-    <x:row r="191" ht="422.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A191" s="40" t="n">
+      <x:c r="K191" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L191" s="9" t="str"/>
+      <x:c r="M191" s="9" t="str"/>
+      <x:c r="N191" s="41" t="str"/>
+    </x:row>
+    <x:row r="192" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A192" s="40" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B191" s="9" t="str">
+      <x:c r="B192" s="9" t="str">
         <x:v>cadillac-escaladeesv-super-cruise-and-driver-2021</x:v>
       </x:c>
-      <x:c r="C191" s="9" t="str">
+      <x:c r="C192" s="9" t="str">
         <x:v>2021-2024 | Cadillac | Escalade ESV</x:v>
       </x:c>
-      <x:c r="D191" s="9" t="str">
+      <x:c r="D192" s="9" t="str">
         <x:v>Startup Super Cruise Unavailable With U1624 Has a Module-Reset Path</x:v>
       </x:c>
-      <x:c r="E191" s="9" t="str">
+      <x:c r="E192" s="9" t="str">
         <x:v>Confirm RPO UKL and U1624 in K124. Follow the GM procedure to reset K73 by removing its fuse for at least one minute. If the code does not move to history, continue Service Information diagnosis. Do not replace modules or order driver-assistance parts from this card.</x:v>
       </x:c>
-      <x:c r="F191" s="9" t="str">
+      <x:c r="F192" s="9" t="str">
         <x:v>Confirm RPO UKL and U1624 in K124. Follow the GM procedure to reset K73 by removing its fuse for at least one minute. If the code does not move to history, continue Service Information diagnosis. Do not replace modules or order driver-assistance parts from this card.</x:v>
       </x:c>
-      <x:c r="G191" s="9" t="str">
+      <x:c r="G192" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H191" s="9" t="str">
+      <x:c r="H192" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Startup Super Cruise Unavailable With U1624 Has a Module-Reset Path</x:v>
       </x:c>
-      <x:c r="I191" s="9" t="str">
+      <x:c r="I192" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J191" s="9" t="str">
+      <x:c r="J192" s="9" t="str">
         <x:v>2021-2024 Cadillac Escalade ESV; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K191" s="9" t="str">
+      <x:c r="K192" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L191" s="9" t="str"/>
-      <x:c r="M191" s="9" t="str">
+      <x:c r="L192" s="9" t="str"/>
+      <x:c r="M192" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N191" s="41" t="str">
+      <x:c r="N192" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A192" s="40" t="str"/>
-      <x:c r="B192" s="9" t="str"/>
-      <x:c r="C192" s="9" t="str"/>
-      <x:c r="D192" s="9" t="str"/>
-      <x:c r="E192" s="9" t="str"/>
-      <x:c r="F192" s="9" t="str"/>
-      <x:c r="G192" s="9" t="str"/>
-      <x:c r="H192" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I192" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J192" s="9" t="str">
+    <x:row r="193" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A193" s="40" t="str"/>
+      <x:c r="B193" s="9" t="str"/>
+      <x:c r="C193" s="9" t="str"/>
+      <x:c r="D193" s="9" t="str"/>
+      <x:c r="E193" s="9" t="str"/>
+      <x:c r="F193" s="9" t="str"/>
+      <x:c r="G193" s="9" t="str"/>
+      <x:c r="H193" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I193" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J193" s="9" t="str">
         <x:v>2021-2024 Cadillac Escalade ESV diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K192" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L192" s="9" t="str"/>
-      <x:c r="M192" s="9" t="str"/>
-      <x:c r="N192" s="41" t="str"/>
-    </x:row>
-    <x:row r="193" ht="1438.800048828125" hidden="0" customHeight="1">
-      <x:c r="A193" s="40" t="n">
+      <x:c r="K193" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L193" s="9" t="str"/>
+      <x:c r="M193" s="9" t="str"/>
+      <x:c r="N193" s="41" t="str"/>
+    </x:row>
+    <x:row r="194" ht="1438.800048828125" hidden="0" customHeight="1">
+      <x:c r="A194" s="40" t="n">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B193" s="9" t="str">
+      <x:c r="B194" s="9" t="str">
         <x:v>cadillac-fleetwood-cooling-system-1993</x:v>
       </x:c>
-      <x:c r="C193" s="9" t="str">
+      <x:c r="C194" s="9" t="str">
         <x:v>1990-1996 | Cadillac | Fleetwood</x:v>
       </x:c>
-      <x:c r="D193" s="9" t="str">
+      <x:c r="D194" s="9" t="str">
         <x:v>Cooling System and Heater Core Failure</x:v>
       </x:c>
-      <x:c r="E193" s="9" t="str">
+      <x:c r="E194" s="9" t="str">
         <x:v>Pressure-test the cooling system cold and hot, inspect the water pump weep hole, radiator tanks/core, hoses, and heater core area for leaks, and confirm heater core failure if the cabin has a sweet odor, fogged windshield, or damp passenger-side carpet. Replace the failed component(s): water pump and thermostat on the 5.7L TBI/LT1 as needed, radiator if the core or end tanks are deteriorated, and the heater core if leaking; on these Fleetwoods, heater core service typically requires major dash/HVAC case disassembly, so labor is high. After repairs, flush the system, refill with the correct 50/50 coolant mix, bleed air, verify fan operation and operating temperature, and replace aged hoses, belt, and radiator cap if original. Typical costs are about $400-$900 for a water pump job, $500-$1,000 for a radiator, and roughly $1,000-$1,800 for a heater core due to labor intensity.</x:v>
       </x:c>
-      <x:c r="F193" s="9" t="str">
+      <x:c r="F194" s="9" t="str">
         <x:v>Pressure-test the cooling system cold and hot, inspect the water pump weep hole, radiator tanks/core, hoses, and heater core area for leaks, and confirm heater core failure if the cabin has a sweet odor, fogged windshield, or damp passenger-side carpet. Replace the failed component(s): water pump and thermostat on the 5.7L TBI/LT1 as needed, radiator if the core or end tanks are deteriorated, and the heater core if leaking; on these Fleetwoods, heater core service typically requires major dash/HVAC case disassembly, so labor is high. After repairs, flush the system, refill with the correct 50/50 coolant mix, bleed air, verify fan operation and operating temperature, and replace aged hoses, belt, and radiator cap if original. Typical costs are about $400-$900 for a water pump job, $500-$1,000 for a radiator, and roughly $1,000-$1,800 for a heater core due to labor intensity.</x:v>
       </x:c>
-      <x:c r="G193" s="9" t="str">
+      <x:c r="G194" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H193" s="9" t="str">
+      <x:c r="H194" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Cooling System and Heater Core Failure</x:v>
       </x:c>
-      <x:c r="I193" s="9" t="str">
+      <x:c r="I194" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J193" s="9" t="str">
+      <x:c r="J194" s="9" t="str">
         <x:v>1990-1996 Cadillac Fleetwood; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K193" s="9" t="str">
+      <x:c r="K194" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L193" s="9" t="str"/>
-      <x:c r="M193" s="9" t="str">
+      <x:c r="L194" s="9" t="str"/>
+      <x:c r="M194" s="9" t="str">
         <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
       </x:c>
-      <x:c r="N193" s="41" t="str">
+      <x:c r="N194" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A194" s="40" t="str"/>
-      <x:c r="B194" s="9" t="str"/>
-      <x:c r="C194" s="9" t="str"/>
-      <x:c r="D194" s="9" t="str"/>
-      <x:c r="E194" s="9" t="str"/>
-      <x:c r="F194" s="9" t="str"/>
-      <x:c r="G194" s="9" t="str"/>
-      <x:c r="H194" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I194" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J194" s="9" t="str">
+    <x:row r="195" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A195" s="40" t="str"/>
+      <x:c r="B195" s="9" t="str"/>
+      <x:c r="C195" s="9" t="str"/>
+      <x:c r="D195" s="9" t="str"/>
+      <x:c r="E195" s="9" t="str"/>
+      <x:c r="F195" s="9" t="str"/>
+      <x:c r="G195" s="9" t="str"/>
+      <x:c r="H195" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I195" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J195" s="9" t="str">
         <x:v>1990-1996 Cadillac Fleetwood diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K194" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L194" s="9" t="str"/>
-      <x:c r="M194" s="9" t="str"/>
-      <x:c r="N194" s="41" t="str"/>
-    </x:row>
-    <x:row r="195" ht="145.1999969482422" hidden="0" customHeight="1">
-      <x:c r="A195" s="40" t="n">
+      <x:c r="K195" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L195" s="9" t="str"/>
+      <x:c r="M195" s="9" t="str"/>
+      <x:c r="N195" s="41" t="str"/>
+    </x:row>
+    <x:row r="196" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A196" s="40" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B195" s="9" t="str">
+      <x:c r="B196" s="9" t="str">
         <x:v>cadillac-fleetwood-lt1-optispark-1994</x:v>
       </x:c>
-      <x:c r="C195" s="9" t="str">
+      <x:c r="C196" s="9" t="str">
         <x:v>1994-1996 | Cadillac | Fleetwood | LT1</x:v>
       </x:c>
-      <x:c r="D195" s="9" t="str">
+      <x:c r="D196" s="9" t="str">
         <x:v>LT1 5.7L Optispark Distributor Failure (1994-1996)</x:v>
       </x:c>
-      <x:c r="E195" s="9" t="str"/>
-      <x:c r="F195" s="9" t="str">
+      <x:c r="E196" s="9" t="str"/>
+      <x:c r="F196" s="9" t="str">
         <x:v>Source How to Fix is blank; no repair item or destination inferred.</x:v>
       </x:c>
-      <x:c r="G195" s="9" t="str">
+      <x:c r="G196" s="9" t="str">
         <x:v>SOURCE HOW-TO-FIX REQUIRED — NO INFERRED LINK</x:v>
       </x:c>
-      <x:c r="H195" s="9" t="str"/>
-      <x:c r="I195" s="9" t="str"/>
-      <x:c r="J195" s="9" t="str"/>
-      <x:c r="K195" s="9" t="str"/>
-      <x:c r="L195" s="9" t="str"/>
-      <x:c r="M195" s="9" t="str">
-        <x:v>The published issue has no repair instructions to ground a safe part or service destination.</x:v>
-      </x:c>
-      <x:c r="N195" s="41" t="str">
-        <x:v>Add and review a complete How to Fix before linking any product, scanner or service.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" ht="435.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A196" s="40" t="n">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="B196" s="9" t="str">
-        <x:v>cadillac-fleetwood-rear-air-spring-1993</x:v>
-      </x:c>
-      <x:c r="C196" s="9" t="str">
-        <x:v>1994-1994 | Cadillac | Fleetwood</x:v>
-      </x:c>
-      <x:c r="D196" s="9" t="str">
-        <x:v>A Seven-Minute Level Ride Warning Calls for Electronic Level-Control Service</x:v>
-      </x:c>
-      <x:c r="E196" s="9" t="str">
-        <x:v>If the warning remains on for seven minutes, have the 1994 Fleetwood Electronic Level Control system diagnosed. Inspect system operation and current service information before replacing a component. Do not order an air spring, compressor or conversion kit from this card.</x:v>
-      </x:c>
-      <x:c r="F196" s="9" t="str">
-        <x:v>If the warning remains on for seven minutes, have the 1994 Fleetwood Electronic Level Control system diagnosed. Inspect system operation and current service information before replacing a component. Do not order an air spring, compressor or conversion kit from this card.</x:v>
-      </x:c>
-      <x:c r="G196" s="9" t="str">
-        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
-      </x:c>
-      <x:c r="H196" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I196" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J196" s="9" t="str">
-        <x:v>1994-1994 Cadillac Fleetwood instruction-specific diagnosis</x:v>
-      </x:c>
-      <x:c r="K196" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
+      <x:c r="H196" s="9" t="str"/>
+      <x:c r="I196" s="9" t="str"/>
+      <x:c r="J196" s="9" t="str"/>
+      <x:c r="K196" s="9" t="str"/>
       <x:c r="L196" s="9" t="str"/>
       <x:c r="M196" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+        <x:v>The published issue has no repair instructions to ground a safe part or service destination.</x:v>
       </x:c>
       <x:c r="N196" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" ht="620.4000244140625" hidden="0" customHeight="1">
+        <x:v>Add and review a complete How to Fix before linking any product, scanner or service.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A197" s="40" t="n">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B197" s="9" t="str">
-        <x:v>cadillac-lyriq-12v-battery-drain-2023</x:v>
+        <x:v>cadillac-fleetwood-rear-air-spring-1993</x:v>
       </x:c>
       <x:c r="C197" s="9" t="str">
-        <x:v>2023-2024 | Cadillac | Lyriq</x:v>
+        <x:v>1994-1994 | Cadillac | Fleetwood</x:v>
       </x:c>
       <x:c r="D197" s="9" t="str">
-        <x:v>Dead 12V Battery from Gateway or BECM Software Conditions</x:v>
+        <x:v>A Seven-Minute Level Ride Warning Calls for Electronic Level-Control Service</x:v>
       </x:c>
       <x:c r="E197" s="9" t="str">
-        <x:v>Have an EV-qualified Cadillac technician reproduce the draw and scan every module. For the 2023 gateway condition, cycle the specified fuse and verify or update the gateway software. Apply PIP6021 only when all listed DTCs are present; otherwise continue normal service-information diagnosis. Accept applicable future OTA updates. Do not disconnect the 12V or high-voltage system from this card.</x:v>
+        <x:v>If the warning remains on for seven minutes, have the 1994 Fleetwood Electronic Level Control system diagnosed. Inspect system operation and current service information before replacing a component. Do not order an air spring, compressor or conversion kit from this card.</x:v>
       </x:c>
       <x:c r="F197" s="9" t="str">
-        <x:v>Have an EV-qualified Cadillac technician reproduce the draw and scan every module. For the 2023 gateway condition, cycle the specified fuse and verify or update the gateway software. Apply PIP6021 only when all listed DTCs are present; otherwise continue normal service-information diagnosis. Accept applicable future OTA updates. Do not disconnect the 12V or high-voltage system from this card.</x:v>
+        <x:v>If the warning remains on for seven minutes, have the 1994 Fleetwood Electronic Level Control system diagnosed. Inspect system operation and current service information before replacing a component. Do not order an air spring, compressor or conversion kit from this card.</x:v>
       </x:c>
       <x:c r="G197" s="9" t="str">
-        <x:v>HIGH-VOLTAGE / EV-QUALIFIED SERVICE</x:v>
+        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
       <x:c r="H197" s="9" t="str">
         <x:v>Cadillac certified-service locator</x:v>
@@ -7467,40 +7451,40 @@
         <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
       </x:c>
       <x:c r="J197" s="9" t="str">
-        <x:v>2023-2024 Cadillac Lyriq EV-qualified diagnosis</x:v>
+        <x:v>1994-1994 Cadillac Fleetwood instruction-specific diagnosis</x:v>
       </x:c>
       <x:c r="K197" s="9" t="str">
-        <x:v>authorized EV service</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L197" s="9" t="str"/>
       <x:c r="M197" s="9" t="str">
-        <x:v>High-voltage diagnosis and remedy require qualified procedures and vehicle-specific data.</x:v>
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
       </x:c>
       <x:c r="N197" s="41" t="str">
-        <x:v>No consumer HV part, battery or generic scanner link.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" ht="409.20001220703125" hidden="0" customHeight="1">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A198" s="40" t="n">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B198" s="9" t="str">
-        <x:v>cadillac-lyriq-abs-releases-brake-pressure-reduced-braking-low-speeds</x:v>
+        <x:v>cadillac-lyriq-12v-battery-drain-2023</x:v>
       </x:c>
       <x:c r="C198" s="9" t="str">
         <x:v>2023-2024 | Cadillac | Lyriq</x:v>
       </x:c>
       <x:c r="D198" s="9" t="str">
-        <x:v>False ABS Activation Can Reduce Braking Below 25 mph (Recall 24V589)</x:v>
+        <x:v>Dead 12V Battery from Gateway or BECM Software Conditions</x:v>
       </x:c>
       <x:c r="E198" s="9" t="str">
-        <x:v>Check the VIN and open-field-action status. Cadillac updates the Electronic Brake Control Module software over the air or at an authorized dealer under recall 24V589 / GM N242453471 at no charge. Do not assume a rear-wheel-drive Lyriq is included.</x:v>
+        <x:v>Have an EV-qualified Cadillac technician reproduce the draw and scan every module. For the 2023 gateway condition, cycle the specified fuse and verify or update the gateway software. Apply PIP6021 only when all listed DTCs are present; otherwise continue normal service-information diagnosis. Accept applicable future OTA updates. Do not disconnect the 12V or high-voltage system from this card.</x:v>
       </x:c>
       <x:c r="F198" s="9" t="str">
-        <x:v>Check the VIN and open-field-action status. Cadillac updates the Electronic Brake Control Module software over the air or at an authorized dealer under recall 24V589 / GM N242453471 at no charge. Do not assume a rear-wheel-drive Lyriq is included.</x:v>
+        <x:v>Have an EV-qualified Cadillac technician reproduce the draw and scan every module. For the 2023 gateway condition, cycle the specified fuse and verify or update the gateway software. Apply PIP6021 only when all listed DTCs are present; otherwise continue normal service-information diagnosis. Accept applicable future OTA updates. Do not disconnect the 12V or high-voltage system from this card.</x:v>
       </x:c>
       <x:c r="G198" s="9" t="str">
-        <x:v>RECALL ROUTES ONLY</x:v>
+        <x:v>HIGH-VOLTAGE / EV-QUALIFIED SERVICE</x:v>
       </x:c>
       <x:c r="H198" s="9" t="str">
         <x:v>Cadillac certified-service locator</x:v>
@@ -7509,106 +7493,106 @@
         <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
       </x:c>
       <x:c r="J198" s="9" t="str">
-        <x:v>2023-2024 Cadillac Lyriq VIN/campaign completion and free remedy</x:v>
+        <x:v>2023-2024 Cadillac Lyriq EV-qualified diagnosis</x:v>
       </x:c>
       <x:c r="K198" s="9" t="str">
-        <x:v>authorized recall service</x:v>
+        <x:v>authorized EV service</x:v>
       </x:c>
       <x:c r="L198" s="9" t="str"/>
       <x:c r="M198" s="9" t="str">
+        <x:v>High-voltage diagnosis and remedy require qualified procedures and vehicle-specific data.</x:v>
+      </x:c>
+      <x:c r="N198" s="41" t="str">
+        <x:v>No consumer HV part, battery or generic scanner link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="409.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A199" s="40" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B199" s="9" t="str">
+        <x:v>cadillac-lyriq-abs-releases-brake-pressure-reduced-braking-low-speeds</x:v>
+      </x:c>
+      <x:c r="C199" s="9" t="str">
+        <x:v>2023-2024 | Cadillac | Lyriq</x:v>
+      </x:c>
+      <x:c r="D199" s="9" t="str">
+        <x:v>False ABS Activation Can Reduce Braking Below 25 mph (Recall 24V589)</x:v>
+      </x:c>
+      <x:c r="E199" s="9" t="str">
+        <x:v>Check the VIN and open-field-action status. Cadillac updates the Electronic Brake Control Module software over the air or at an authorized dealer under recall 24V589 / GM N242453471 at no charge. Do not assume a rear-wheel-drive Lyriq is included.</x:v>
+      </x:c>
+      <x:c r="F199" s="9" t="str">
+        <x:v>Check the VIN and open-field-action status. Cadillac updates the Electronic Brake Control Module software over the air or at an authorized dealer under recall 24V589 / GM N242453471 at no charge. Do not assume a rear-wheel-drive Lyriq is included.</x:v>
+      </x:c>
+      <x:c r="G199" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H199" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I199" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J199" s="9" t="str">
+        <x:v>2023-2024 Cadillac Lyriq VIN/campaign completion and free remedy</x:v>
+      </x:c>
+      <x:c r="K199" s="9" t="str">
+        <x:v>authorized recall service</x:v>
+      </x:c>
+      <x:c r="L199" s="9" t="str"/>
+      <x:c r="M199" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N198" s="41" t="str">
+      <x:c r="N199" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A199" s="40" t="str"/>
-      <x:c r="B199" s="9" t="str"/>
-      <x:c r="C199" s="9" t="str"/>
-      <x:c r="D199" s="9" t="str"/>
-      <x:c r="E199" s="9" t="str"/>
-      <x:c r="F199" s="9" t="str"/>
-      <x:c r="G199" s="9" t="str"/>
-      <x:c r="H199" s="9" t="str">
+    <x:row r="200" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A200" s="40" t="str"/>
+      <x:c r="B200" s="9" t="str"/>
+      <x:c r="C200" s="9" t="str"/>
+      <x:c r="D200" s="9" t="str"/>
+      <x:c r="E200" s="9" t="str"/>
+      <x:c r="F200" s="9" t="str"/>
+      <x:c r="G200" s="9" t="str"/>
+      <x:c r="H200" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I199" s="9" t="str">
+      <x:c r="I200" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J199" s="9" t="str">
+      <x:c r="J200" s="9" t="str">
         <x:v>2023-2024 Cadillac Lyriq VIN history</x:v>
       </x:c>
-      <x:c r="K199" s="9" t="str">
+      <x:c r="K200" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L199" s="9" t="str"/>
-      <x:c r="M199" s="9" t="str"/>
-      <x:c r="N199" s="41" t="str"/>
-    </x:row>
-    <x:row r="200" ht="396" hidden="0" customHeight="1">
-      <x:c r="A200" s="40" t="n">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B200" s="9" t="str">
-        <x:v>cadillac-lyriq-charge-port-2023</x:v>
-      </x:c>
-      <x:c r="C200" s="9" t="str">
-        <x:v>2023-2025 | Cadillac | Lyriq</x:v>
-      </x:c>
-      <x:c r="D200" s="9" t="str">
-        <x:v>Charge Port Door May Not Auto-Close After Unplugging</x:v>
-      </x:c>
-      <x:c r="E200" s="9" t="str">
-        <x:v>No repair is required for this exact condition. Close the door with its button, or it will close automatically when the vehicle is shifted out of Park. If the door will not respond to either action or charging itself fails, have Cadillac diagnose that separate symptom.</x:v>
-      </x:c>
-      <x:c r="F200" s="9" t="str">
-        <x:v>No repair is required for this exact condition. Close the door with its button, or it will close automatically when the vehicle is shifted out of Park. If the door will not respond to either action or charging itself fails, have Cadillac diagnose that separate symptom.</x:v>
-      </x:c>
-      <x:c r="G200" s="9" t="str">
-        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
-      </x:c>
-      <x:c r="H200" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I200" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J200" s="9" t="str">
-        <x:v>2023-2025 Cadillac Lyriq instruction-specific diagnosis</x:v>
-      </x:c>
-      <x:c r="K200" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
       <x:c r="L200" s="9" t="str"/>
-      <x:c r="M200" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
-      </x:c>
-      <x:c r="N200" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
+      <x:c r="M200" s="9" t="str"/>
+      <x:c r="N200" s="41" t="str"/>
     </x:row>
     <x:row r="201" ht="396" hidden="0" customHeight="1">
       <x:c r="A201" s="40" t="n">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B201" s="9" t="str">
-        <x:v>cadillac-lyriq-front-stabilizer-bar-bracket-bolts-loosen-separate</x:v>
+        <x:v>cadillac-lyriq-charge-port-2023</x:v>
       </x:c>
       <x:c r="C201" s="9" t="str">
         <x:v>2023-2025 | Cadillac | Lyriq</x:v>
       </x:c>
       <x:c r="D201" s="9" t="str">
-        <x:v>Loose Stabilizer Bracket Bolts Can Damage EV Cables (Recall 25V232)</x:v>
+        <x:v>Charge Port Door May Not Auto-Close After Unplugging</x:v>
       </x:c>
       <x:c r="E201" s="9" t="str">
-        <x:v>Check the VIN for recall 25V232 / GM N252494190. An authorized Cadillac EV dealer inspects and, as necessary, properly fastens the affected bracket bolts at no charge. A clunk or rattle may precede separation; do not work near high-voltage cables from this card.</x:v>
+        <x:v>No repair is required for this exact condition. Close the door with its button, or it will close automatically when the vehicle is shifted out of Park. If the door will not respond to either action or charging itself fails, have Cadillac diagnose that separate symptom.</x:v>
       </x:c>
       <x:c r="F201" s="9" t="str">
-        <x:v>Check the VIN for recall 25V232 / GM N252494190. An authorized Cadillac EV dealer inspects and, as necessary, properly fastens the affected bracket bolts at no charge. A clunk or rattle may precede separation; do not work near high-voltage cables from this card.</x:v>
+        <x:v>No repair is required for this exact condition. Close the door with its button, or it will close automatically when the vehicle is shifted out of Park. If the door will not respond to either action or charging itself fails, have Cadillac diagnose that separate symptom.</x:v>
       </x:c>
       <x:c r="G201" s="9" t="str">
-        <x:v>RECALL ROUTES ONLY</x:v>
+        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
       <x:c r="H201" s="9" t="str">
         <x:v>Cadillac certified-service locator</x:v>
@@ -7617,277 +7601,277 @@
         <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
       </x:c>
       <x:c r="J201" s="9" t="str">
-        <x:v>2023-2025 Cadillac Lyriq VIN/campaign completion and free remedy</x:v>
+        <x:v>2023-2025 Cadillac Lyriq instruction-specific diagnosis</x:v>
       </x:c>
       <x:c r="K201" s="9" t="str">
-        <x:v>authorized recall service</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L201" s="9" t="str"/>
       <x:c r="M201" s="9" t="str">
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+      </x:c>
+      <x:c r="N201" s="41" t="str">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="396" hidden="0" customHeight="1">
+      <x:c r="A202" s="40" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B202" s="9" t="str">
+        <x:v>cadillac-lyriq-front-stabilizer-bar-bracket-bolts-loosen-separate</x:v>
+      </x:c>
+      <x:c r="C202" s="9" t="str">
+        <x:v>2023-2025 | Cadillac | Lyriq</x:v>
+      </x:c>
+      <x:c r="D202" s="9" t="str">
+        <x:v>Loose Stabilizer Bracket Bolts Can Damage EV Cables (Recall 25V232)</x:v>
+      </x:c>
+      <x:c r="E202" s="9" t="str">
+        <x:v>Check the VIN for recall 25V232 / GM N252494190. An authorized Cadillac EV dealer inspects and, as necessary, properly fastens the affected bracket bolts at no charge. A clunk or rattle may precede separation; do not work near high-voltage cables from this card.</x:v>
+      </x:c>
+      <x:c r="F202" s="9" t="str">
+        <x:v>Check the VIN for recall 25V232 / GM N252494190. An authorized Cadillac EV dealer inspects and, as necessary, properly fastens the affected bracket bolts at no charge. A clunk or rattle may precede separation; do not work near high-voltage cables from this card.</x:v>
+      </x:c>
+      <x:c r="G202" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H202" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I202" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J202" s="9" t="str">
+        <x:v>2023-2025 Cadillac Lyriq VIN/campaign completion and free remedy</x:v>
+      </x:c>
+      <x:c r="K202" s="9" t="str">
+        <x:v>authorized recall service</x:v>
+      </x:c>
+      <x:c r="L202" s="9" t="str"/>
+      <x:c r="M202" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N201" s="41" t="str">
+      <x:c r="N202" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A202" s="40" t="str"/>
-      <x:c r="B202" s="9" t="str"/>
-      <x:c r="C202" s="9" t="str"/>
-      <x:c r="D202" s="9" t="str"/>
-      <x:c r="E202" s="9" t="str"/>
-      <x:c r="F202" s="9" t="str"/>
-      <x:c r="G202" s="9" t="str"/>
-      <x:c r="H202" s="9" t="str">
+    <x:row r="203" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A203" s="40" t="str"/>
+      <x:c r="B203" s="9" t="str"/>
+      <x:c r="C203" s="9" t="str"/>
+      <x:c r="D203" s="9" t="str"/>
+      <x:c r="E203" s="9" t="str"/>
+      <x:c r="F203" s="9" t="str"/>
+      <x:c r="G203" s="9" t="str"/>
+      <x:c r="H203" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I202" s="9" t="str">
+      <x:c r="I203" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J202" s="9" t="str">
+      <x:c r="J203" s="9" t="str">
         <x:v>2023-2025 Cadillac Lyriq VIN history</x:v>
       </x:c>
-      <x:c r="K202" s="9" t="str">
+      <x:c r="K203" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L202" s="9" t="str"/>
-      <x:c r="M202" s="9" t="str"/>
-      <x:c r="N202" s="41" t="str"/>
-    </x:row>
-    <x:row r="203" ht="620.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A203" s="40" t="n">
+      <x:c r="L203" s="9" t="str"/>
+      <x:c r="M203" s="9" t="str"/>
+      <x:c r="N203" s="41" t="str"/>
+    </x:row>
+    <x:row r="204" ht="620.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A204" s="40" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B203" s="9" t="str">
+      <x:c r="B204" s="9" t="str">
         <x:v>cadillac-lyriq-heat-pump-climate-system-failure-no-heat-extreme-cold</x:v>
       </x:c>
-      <x:c r="C203" s="9" t="str">
+      <x:c r="C204" s="9" t="str">
         <x:v>2024-2025 | Cadillac | Lyriq</x:v>
       </x:c>
-      <x:c r="D203" s="9" t="str">
+      <x:c r="D204" s="9" t="str">
         <x:v>Heat Pump / Climate System Failure and No Heat in Extreme Cold</x:v>
       </x:c>
-      <x:c r="E203" s="9" t="str">
+      <x:c r="E204" s="9" t="str">
         <x:v>For the coolant sensor harness defect (GM service update N232414770, about 557 affected 2024 RWD units), dealers perform a harness clip adjustment/replacement. Communication-fault and fast-charge sensor-conflict issues are addressed via control-module software updates. Have the dealer diagnose the specific fault and apply the latest HVAC/thermal-management software.</x:v>
       </x:c>
-      <x:c r="F203" s="9" t="str">
+      <x:c r="F204" s="9" t="str">
         <x:v>For the coolant sensor harness defect (GM service update N232414770, about 557 affected 2024 RWD units), dealers perform a harness clip adjustment/replacement. Communication-fault and fast-charge sensor-conflict issues are addressed via control-module software updates. Have the dealer diagnose the specific fault and apply the latest HVAC/thermal-management software.</x:v>
       </x:c>
-      <x:c r="G203" s="9" t="str">
+      <x:c r="G204" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H203" s="9" t="str">
+      <x:c r="H204" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Heat Pump / Climate System Failure and No Heat in Extreme Cold</x:v>
       </x:c>
-      <x:c r="I203" s="9" t="str">
+      <x:c r="I204" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J203" s="9" t="str">
+      <x:c r="J204" s="9" t="str">
         <x:v>2024-2025 Cadillac Lyriq; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K203" s="9" t="str">
+      <x:c r="K204" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L203" s="9" t="str"/>
-      <x:c r="M203" s="9" t="str">
+      <x:c r="L204" s="9" t="str"/>
+      <x:c r="M204" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N203" s="41" t="str">
+      <x:c r="N204" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A204" s="40" t="str"/>
-      <x:c r="B204" s="9" t="str"/>
-      <x:c r="C204" s="9" t="str"/>
-      <x:c r="D204" s="9" t="str"/>
-      <x:c r="E204" s="9" t="str"/>
-      <x:c r="F204" s="9" t="str"/>
-      <x:c r="G204" s="9" t="str"/>
-      <x:c r="H204" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I204" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J204" s="9" t="str">
+    <x:row r="205" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A205" s="40" t="str"/>
+      <x:c r="B205" s="9" t="str"/>
+      <x:c r="C205" s="9" t="str"/>
+      <x:c r="D205" s="9" t="str"/>
+      <x:c r="E205" s="9" t="str"/>
+      <x:c r="F205" s="9" t="str"/>
+      <x:c r="G205" s="9" t="str"/>
+      <x:c r="H205" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I205" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J205" s="9" t="str">
         <x:v>2024-2025 Cadillac Lyriq diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K204" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L204" s="9" t="str"/>
-      <x:c r="M204" s="9" t="str"/>
-      <x:c r="N204" s="41" t="str"/>
-    </x:row>
-    <x:row r="205" ht="607.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A205" s="40" t="n">
+      <x:c r="K205" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L205" s="9" t="str"/>
+      <x:c r="M205" s="9" t="str"/>
+      <x:c r="N205" s="41" t="str"/>
+    </x:row>
+    <x:row r="206" ht="607.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A206" s="40" t="n">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B205" s="9" t="str">
+      <x:c r="B206" s="9" t="str">
         <x:v>cadillac-lyriq-inconsistent-dc-fast-charging-speed-mid-session-power-dips</x:v>
       </x:c>
-      <x:c r="C205" s="9" t="str">
+      <x:c r="C206" s="9" t="str">
         <x:v>2023-2025 | Cadillac | Lyriq</x:v>
       </x:c>
-      <x:c r="D205" s="9" t="str">
+      <x:c r="D206" s="9" t="str">
         <x:v>Inconsistent DC Fast-Charging Speed With Mid-Session Power Dips</x:v>
       </x:c>
-      <x:c r="E205" s="9" t="str">
+      <x:c r="E206" s="9" t="str">
         <x:v>Precondition the battery before a DC fast-charge stop to reach and hold higher rates. Much of the behavior is inherent to the Lyriq's charge curve, but keep the vehicle software current (GM has tuned thermal/charging logic via OTA updates), choose an uncongested high-power charger, and report persistently abnormal low rates to a dealer to rule out a thermal-management fault.</x:v>
       </x:c>
-      <x:c r="F205" s="9" t="str">
+      <x:c r="F206" s="9" t="str">
         <x:v>Precondition the battery before a DC fast-charge stop to reach and hold higher rates. Much of the behavior is inherent to the Lyriq's charge curve, but keep the vehicle software current (GM has tuned thermal/charging logic via OTA updates), choose an uncongested high-power charger, and report persistently abnormal low rates to a dealer to rule out a thermal-management fault.</x:v>
       </x:c>
-      <x:c r="G205" s="9" t="str">
+      <x:c r="G206" s="9" t="str">
         <x:v>SOFTWARE / OPERATING-CONDITION SERVICE — PRODUCT HOLD</x:v>
       </x:c>
-      <x:c r="H205" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I205" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J205" s="9" t="str">
+      <x:c r="H206" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I206" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J206" s="9" t="str">
         <x:v>2023-2025 Cadillac Lyriq software, operating-condition and hardware diagnosis</x:v>
       </x:c>
-      <x:c r="K205" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L205" s="9" t="str"/>
-      <x:c r="M205" s="9" t="str">
-        <x:v>The source calls for updates, condition checks or diagnosis and does not establish a replaceable retail component.</x:v>
-      </x:c>
-      <x:c r="N205" s="41" t="str">
-        <x:v>No sensor, camera, display, battery or module link unless separate diagnosis proves hardware failure.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" ht="277.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A206" s="40" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="B206" s="9" t="str">
-        <x:v>cadillac-lyriq-instrument-cluster-display-goes-blank-while-driving</x:v>
-      </x:c>
-      <x:c r="C206" s="9" t="str">
-        <x:v>2023-2024 | Cadillac | Lyriq</x:v>
-      </x:c>
-      <x:c r="D206" s="9" t="str">
-        <x:v>Driver Display Can Go Blank While Driving (Recall 25V356)</x:v>
-      </x:c>
-      <x:c r="E206" s="9" t="str">
-        <x:v>Check the VIN and recall-completion status. Cadillac updates the video display control module over the air or at a dealer under recall 25V356 / GM N252500680 at no charge.</x:v>
-      </x:c>
-      <x:c r="F206" s="9" t="str">
-        <x:v>Check the VIN and recall-completion status. Cadillac updates the video display control module over the air or at a dealer under recall 25V356 / GM N252500680 at no charge.</x:v>
-      </x:c>
-      <x:c r="G206" s="9" t="str">
-        <x:v>RECALL ROUTES ONLY</x:v>
-      </x:c>
-      <x:c r="H206" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I206" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J206" s="9" t="str">
-        <x:v>2023-2024 Cadillac Lyriq VIN/campaign completion and free remedy</x:v>
-      </x:c>
       <x:c r="K206" s="9" t="str">
-        <x:v>authorized recall service</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L206" s="9" t="str"/>
       <x:c r="M206" s="9" t="str">
+        <x:v>The source calls for updates, condition checks or diagnosis and does not establish a replaceable retail component.</x:v>
+      </x:c>
+      <x:c r="N206" s="41" t="str">
+        <x:v>No sensor, camera, display, battery or module link unless separate diagnosis proves hardware failure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="277.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A207" s="40" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B207" s="9" t="str">
+        <x:v>cadillac-lyriq-instrument-cluster-display-goes-blank-while-driving</x:v>
+      </x:c>
+      <x:c r="C207" s="9" t="str">
+        <x:v>2023-2024 | Cadillac | Lyriq</x:v>
+      </x:c>
+      <x:c r="D207" s="9" t="str">
+        <x:v>Driver Display Can Go Blank While Driving (Recall 25V356)</x:v>
+      </x:c>
+      <x:c r="E207" s="9" t="str">
+        <x:v>Check the VIN and recall-completion status. Cadillac updates the video display control module over the air or at a dealer under recall 25V356 / GM N252500680 at no charge.</x:v>
+      </x:c>
+      <x:c r="F207" s="9" t="str">
+        <x:v>Check the VIN and recall-completion status. Cadillac updates the video display control module over the air or at a dealer under recall 25V356 / GM N252500680 at no charge.</x:v>
+      </x:c>
+      <x:c r="G207" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H207" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I207" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J207" s="9" t="str">
+        <x:v>2023-2024 Cadillac Lyriq VIN/campaign completion and free remedy</x:v>
+      </x:c>
+      <x:c r="K207" s="9" t="str">
+        <x:v>authorized recall service</x:v>
+      </x:c>
+      <x:c r="L207" s="9" t="str"/>
+      <x:c r="M207" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N206" s="41" t="str">
+      <x:c r="N207" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A207" s="40" t="str"/>
-      <x:c r="B207" s="9" t="str"/>
-      <x:c r="C207" s="9" t="str"/>
-      <x:c r="D207" s="9" t="str"/>
-      <x:c r="E207" s="9" t="str"/>
-      <x:c r="F207" s="9" t="str"/>
-      <x:c r="G207" s="9" t="str"/>
-      <x:c r="H207" s="9" t="str">
+    <x:row r="208" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A208" s="40" t="str"/>
+      <x:c r="B208" s="9" t="str"/>
+      <x:c r="C208" s="9" t="str"/>
+      <x:c r="D208" s="9" t="str"/>
+      <x:c r="E208" s="9" t="str"/>
+      <x:c r="F208" s="9" t="str"/>
+      <x:c r="G208" s="9" t="str"/>
+      <x:c r="H208" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I207" s="9" t="str">
+      <x:c r="I208" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J207" s="9" t="str">
+      <x:c r="J208" s="9" t="str">
         <x:v>2023-2024 Cadillac Lyriq VIN history</x:v>
       </x:c>
-      <x:c r="K207" s="9" t="str">
+      <x:c r="K208" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L207" s="9" t="str"/>
-      <x:c r="M207" s="9" t="str"/>
-      <x:c r="N207" s="41" t="str"/>
-    </x:row>
-    <x:row r="208" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A208" s="40" t="n">
+      <x:c r="L208" s="9" t="str"/>
+      <x:c r="M208" s="9" t="str"/>
+      <x:c r="N208" s="41" t="str"/>
+    </x:row>
+    <x:row r="209" ht="448.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A209" s="40" t="n">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B208" s="9" t="str">
+      <x:c r="B209" s="9" t="str">
         <x:v>cadillac-lyriq-range-estimation-2023</x:v>
-      </x:c>
-      <x:c r="C208" s="9" t="str">
-        <x:v>2023-2025 | Cadillac | Lyriq</x:v>
-      </x:c>
-      <x:c r="D208" s="9" t="str">
-        <x:v>Inaccurate Range Estimation in Cold Weather</x:v>
-      </x:c>
-      <x:c r="E208" s="9" t="str">
-        <x:v>GM has released OTA updates improving cold-weather range estimation accuracy. Pre-condition the battery while plugged in before departing in cold weather. Plan routes with 30% additional buffer in winter. Use the heated seats and steering wheel instead of cabin heat to maximize range.</x:v>
-      </x:c>
-      <x:c r="F208" s="9" t="str">
-        <x:v>GM has released OTA updates improving cold-weather range estimation accuracy. Pre-condition the battery while plugged in before departing in cold weather. Plan routes with 30% additional buffer in winter. Use the heated seats and steering wheel instead of cabin heat to maximize range.</x:v>
-      </x:c>
-      <x:c r="G208" s="9" t="str">
-        <x:v>SOFTWARE / OPERATING-CONDITION SERVICE — PRODUCT HOLD</x:v>
-      </x:c>
-      <x:c r="H208" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I208" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J208" s="9" t="str">
-        <x:v>2023-2025 Cadillac Lyriq software, operating-condition and hardware diagnosis</x:v>
-      </x:c>
-      <x:c r="K208" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L208" s="9" t="str"/>
-      <x:c r="M208" s="9" t="str">
-        <x:v>The source calls for updates, condition checks or diagnosis and does not establish a replaceable retail component.</x:v>
-      </x:c>
-      <x:c r="N208" s="41" t="str">
-        <x:v>No sensor, camera, display, battery or module link unless separate diagnosis proves hardware failure.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A209" s="40" t="n">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="B209" s="9" t="str">
-        <x:v>cadillac-lyriq-rear-camera-glitch-2023</x:v>
       </x:c>
       <x:c r="C209" s="9" t="str">
         <x:v>2023-2025 | Cadillac | Lyriq</x:v>
       </x:c>
       <x:c r="D209" s="9" t="str">
-        <x:v>Rear Camera and Surround Vision System Intermittent Failure</x:v>
+        <x:v>Inaccurate Range Estimation in Cold Weather</x:v>
       </x:c>
       <x:c r="E209" s="9" t="str">
-        <x:v>Apply the latest OTA software updates. If the issue persists, the dealer can reflash the camera control module. Check for moisture in the rear camera housing — condensation can affect image quality. A hard reset of the vehicle (park, lock, wait 5 minutes) usually restores camera function temporarily.</x:v>
+        <x:v>GM has released OTA updates improving cold-weather range estimation accuracy. Pre-condition the battery while plugged in before departing in cold weather. Plan routes with 30% additional buffer in winter. Use the heated seats and steering wheel instead of cabin heat to maximize range.</x:v>
       </x:c>
       <x:c r="F209" s="9" t="str">
-        <x:v>Apply the latest OTA software updates. If the issue persists, the dealer can reflash the camera control module. Check for moisture in the rear camera housing — condensation can affect image quality. A hard reset of the vehicle (park, lock, wait 5 minutes) usually restores camera function temporarily.</x:v>
+        <x:v>GM has released OTA updates improving cold-weather range estimation accuracy. Pre-condition the battery while plugged in before departing in cold weather. Plan routes with 30% additional buffer in winter. Use the heated seats and steering wheel instead of cabin heat to maximize range.</x:v>
       </x:c>
       <x:c r="G209" s="9" t="str">
         <x:v>SOFTWARE / OPERATING-CONDITION SERVICE — PRODUCT HOLD</x:v>
@@ -7912,27 +7896,27 @@
         <x:v>No sensor, camera, display, battery or module link unless separate diagnosis proves hardware failure.</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" ht="369.6000061035156" hidden="0" customHeight="1">
+    <x:row r="210" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A210" s="40" t="n">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B210" s="9" t="str">
-        <x:v>cadillac-lyriq-rear-seat-belt-anchor-bracket-improperly-welded</x:v>
+        <x:v>cadillac-lyriq-rear-camera-glitch-2023</x:v>
       </x:c>
       <x:c r="C210" s="9" t="str">
-        <x:v>2023-2024 | Cadillac | Lyriq</x:v>
+        <x:v>2023-2025 | Cadillac | Lyriq</x:v>
       </x:c>
       <x:c r="D210" s="9" t="str">
-        <x:v>Rear Seat-Belt Anchor Bracket May Be Improperly Welded (Recall 23V785)</x:v>
+        <x:v>Rear Camera and Surround Vision System Intermittent Failure</x:v>
       </x:c>
       <x:c r="E210" s="9" t="str">
-        <x:v>Check the VIN for recall 23V785 / GM N232425220. Until an involved vehicle is repaired, do not use the left-rear or center-rear seating positions. An authorized Cadillac EV dealer replaces the rear seat cushion frame at no charge.</x:v>
+        <x:v>Apply the latest OTA software updates. If the issue persists, the dealer can reflash the camera control module. Check for moisture in the rear camera housing — condensation can affect image quality. A hard reset of the vehicle (park, lock, wait 5 minutes) usually restores camera function temporarily.</x:v>
       </x:c>
       <x:c r="F210" s="9" t="str">
-        <x:v>Check the VIN for recall 23V785 / GM N232425220. Until an involved vehicle is repaired, do not use the left-rear or center-rear seating positions. An authorized Cadillac EV dealer replaces the rear seat cushion frame at no charge.</x:v>
+        <x:v>Apply the latest OTA software updates. If the issue persists, the dealer can reflash the camera control module. Check for moisture in the rear camera housing — condensation can affect image quality. A hard reset of the vehicle (park, lock, wait 5 minutes) usually restores camera function temporarily.</x:v>
       </x:c>
       <x:c r="G210" s="9" t="str">
-        <x:v>RECALL ROUTES ONLY</x:v>
+        <x:v>SOFTWARE / OPERATING-CONDITION SERVICE — PRODUCT HOLD</x:v>
       </x:c>
       <x:c r="H210" s="9" t="str">
         <x:v>Cadillac certified-service locator</x:v>
@@ -7941,103 +7925,103 @@
         <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
       </x:c>
       <x:c r="J210" s="9" t="str">
-        <x:v>2023-2024 Cadillac Lyriq VIN/campaign completion and free remedy</x:v>
+        <x:v>2023-2025 Cadillac Lyriq software, operating-condition and hardware diagnosis</x:v>
       </x:c>
       <x:c r="K210" s="9" t="str">
-        <x:v>authorized recall service</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L210" s="9" t="str"/>
       <x:c r="M210" s="9" t="str">
+        <x:v>The source calls for updates, condition checks or diagnosis and does not establish a replaceable retail component.</x:v>
+      </x:c>
+      <x:c r="N210" s="41" t="str">
+        <x:v>No sensor, camera, display, battery or module link unless separate diagnosis proves hardware failure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="369.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A211" s="40" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B211" s="9" t="str">
+        <x:v>cadillac-lyriq-rear-seat-belt-anchor-bracket-improperly-welded</x:v>
+      </x:c>
+      <x:c r="C211" s="9" t="str">
+        <x:v>2023-2024 | Cadillac | Lyriq</x:v>
+      </x:c>
+      <x:c r="D211" s="9" t="str">
+        <x:v>Rear Seat-Belt Anchor Bracket May Be Improperly Welded (Recall 23V785)</x:v>
+      </x:c>
+      <x:c r="E211" s="9" t="str">
+        <x:v>Check the VIN for recall 23V785 / GM N232425220. Until an involved vehicle is repaired, do not use the left-rear or center-rear seating positions. An authorized Cadillac EV dealer replaces the rear seat cushion frame at no charge.</x:v>
+      </x:c>
+      <x:c r="F211" s="9" t="str">
+        <x:v>Check the VIN for recall 23V785 / GM N232425220. Until an involved vehicle is repaired, do not use the left-rear or center-rear seating positions. An authorized Cadillac EV dealer replaces the rear seat cushion frame at no charge.</x:v>
+      </x:c>
+      <x:c r="G211" s="9" t="str">
+        <x:v>RECALL ROUTES ONLY</x:v>
+      </x:c>
+      <x:c r="H211" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I211" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J211" s="9" t="str">
+        <x:v>2023-2024 Cadillac Lyriq VIN/campaign completion and free remedy</x:v>
+      </x:c>
+      <x:c r="K211" s="9" t="str">
+        <x:v>authorized recall service</x:v>
+      </x:c>
+      <x:c r="L211" s="9" t="str"/>
+      <x:c r="M211" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N210" s="41" t="str">
+      <x:c r="N211" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="211" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A211" s="40" t="str"/>
-      <x:c r="B211" s="9" t="str"/>
-      <x:c r="C211" s="9" t="str"/>
-      <x:c r="D211" s="9" t="str"/>
-      <x:c r="E211" s="9" t="str"/>
-      <x:c r="F211" s="9" t="str"/>
-      <x:c r="G211" s="9" t="str"/>
-      <x:c r="H211" s="9" t="str">
+    <x:row r="212" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A212" s="40" t="str"/>
+      <x:c r="B212" s="9" t="str"/>
+      <x:c r="C212" s="9" t="str"/>
+      <x:c r="D212" s="9" t="str"/>
+      <x:c r="E212" s="9" t="str"/>
+      <x:c r="F212" s="9" t="str"/>
+      <x:c r="G212" s="9" t="str"/>
+      <x:c r="H212" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I211" s="9" t="str">
+      <x:c r="I212" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J211" s="9" t="str">
+      <x:c r="J212" s="9" t="str">
         <x:v>2023-2024 Cadillac Lyriq VIN history</x:v>
       </x:c>
-      <x:c r="K211" s="9" t="str">
+      <x:c r="K212" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L211" s="9" t="str"/>
-      <x:c r="M211" s="9" t="str"/>
-      <x:c r="N211" s="41" t="str"/>
-    </x:row>
-    <x:row r="212" ht="831.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A212" s="40" t="n">
+      <x:c r="L212" s="9" t="str"/>
+      <x:c r="M212" s="9" t="str"/>
+      <x:c r="N212" s="41" t="str"/>
+    </x:row>
+    <x:row r="213" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A213" s="40" t="n">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B212" s="9" t="str">
+      <x:c r="B213" s="9" t="str">
         <x:v>cadillac-northstar-oil-consumption-1994</x:v>
       </x:c>
-      <x:c r="C212" s="9" t="str">
+      <x:c r="C213" s="9" t="str">
         <x:v>1994-2005 | Cadillac | DeVille | 4.6L Northstar V8</x:v>
       </x:c>
-      <x:c r="D212" s="9" t="str">
+      <x:c r="D213" s="9" t="str">
         <x:v>High Oil Use Needs a Measured Consumption Test Before Repair (01-06-01-011O)</x:v>
       </x:c>
-      <x:c r="E212" s="9" t="str">
+      <x:c r="E213" s="9" t="str">
         <x:v>Measure oil use under consistent conditions before authorizing engine work. Verify the oil level and specification, inspect the oil pan, covers, lines and fittings for external leaks, check the PCV system and document mileage and oil added. Do not begin the normal test before 4,000 miles unless use exceeds one quart per 1,000 miles. If the measured result exceeds the applicable GM guideline, continue with the model-specific Service Information diagnosis; do not order engine parts from this card.</x:v>
       </x:c>
-      <x:c r="F212" s="9" t="str">
+      <x:c r="F213" s="9" t="str">
         <x:v>Measure oil use under consistent conditions before authorizing engine work. Verify the oil level and specification, inspect the oil pan, covers, lines and fittings for external leaks, check the PCV system and document mileage and oil added. Do not begin the normal test before 4,000 miles unless use exceeds one quart per 1,000 miles. If the measured result exceeds the applicable GM guideline, continue with the model-specific Service Information diagnosis; do not order engine parts from this card.</x:v>
-      </x:c>
-      <x:c r="G212" s="9" t="str">
-        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
-      </x:c>
-      <x:c r="H212" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I212" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J212" s="9" t="str">
-        <x:v>1994-2005 Cadillac DeVille instruction-specific diagnosis</x:v>
-      </x:c>
-      <x:c r="K212" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L212" s="9" t="str"/>
-      <x:c r="M212" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
-      </x:c>
-      <x:c r="N212" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213" ht="792" hidden="0" customHeight="1">
-      <x:c r="A213" s="40" t="n">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B213" s="9" t="str">
-        <x:v>cadillac-seville-ecs-strut-1998</x:v>
-      </x:c>
-      <x:c r="C213" s="9" t="str">
-        <x:v>2002-2002 | Cadillac | Seville | 4.6L V8 (VIN 9)</x:v>
-      </x:c>
-      <x:c r="D213" s="9" t="str">
-        <x:v>CVRSS Damper-Actuator DTC Requires Diagnosis Before Strut Replacement</x:v>
-      </x:c>
-      <x:c r="E213" s="9" t="str">
-        <x:v>Confirm that the 2002 Seville is an STS equipped with CVRSS RPO F45. Have a qualified technician retrieve the suspension DTCs and run the ESC damper-actuator output test. For an intermittent C0577-type fault, the OEM procedure commands the affected solenoid while the suspected wiring and connector are moved to isolate the circuit or component. Confirm the failed circuit or damper before replacing a strut; do not order a strut, install a passive-conversion kit or defeat the warning from this card.</x:v>
-      </x:c>
-      <x:c r="F213" s="9" t="str">
-        <x:v>Confirm that the 2002 Seville is an STS equipped with CVRSS RPO F45. Have a qualified technician retrieve the suspension DTCs and run the ESC damper-actuator output test. For an intermittent C0577-type fault, the OEM procedure commands the affected solenoid while the suspected wiring and connector are moved to isolate the circuit or component. Confirm the failed circuit or damper before replacing a strut; do not order a strut, install a passive-conversion kit or defeat the warning from this card.</x:v>
       </x:c>
       <x:c r="G213" s="9" t="str">
         <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
@@ -8049,7 +8033,7 @@
         <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
       </x:c>
       <x:c r="J213" s="9" t="str">
-        <x:v>2002-2002 Cadillac Seville instruction-specific diagnosis</x:v>
+        <x:v>1994-2005 Cadillac DeVille instruction-specific diagnosis</x:v>
       </x:c>
       <x:c r="K213" s="9" t="str">
         <x:v>manufacturer-capable service</x:v>
@@ -8062,3053 +8046,3121 @@
         <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="214" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="214" ht="792" hidden="0" customHeight="1">
       <x:c r="A214" s="40" t="n">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B214" s="9" t="str">
-        <x:v>cadillac-seville-northstar-hg-1993</x:v>
+        <x:v>cadillac-seville-ecs-strut-1998</x:v>
       </x:c>
       <x:c r="C214" s="9" t="str">
-        <x:v>1993-2004 | Cadillac | Seville | Northstar 4.6L</x:v>
+        <x:v>2002-2002 | Cadillac | Seville | 4.6L V8 (VIN 9)</x:v>
       </x:c>
       <x:c r="D214" s="9" t="str">
-        <x:v>Northstar 4.6L Head Gasket Failure</x:v>
+        <x:v>CVRSS Damper-Actuator DTC Requires Diagnosis Before Strut Replacement</x:v>
       </x:c>
       <x:c r="E214" s="9" t="str">
-        <x:v>The industry-standard repair uses Time-Sert inserts to repair the head bolt threads in the aluminum block with stronger steel threads. This can be performed with the engine in the vehicle. Use updated MLS head gaskets and proper torque specifications. Budget $2,500-$4,000 for this repair at a shop experienced with Northstars.</x:v>
+        <x:v>Confirm that the 2002 Seville is an STS equipped with CVRSS RPO F45. Have a qualified technician retrieve the suspension DTCs and run the ESC damper-actuator output test. For an intermittent C0577-type fault, the OEM procedure commands the affected solenoid while the suspected wiring and connector are moved to isolate the circuit or component. Confirm the failed circuit or damper before replacing a strut; do not order a strut, install a passive-conversion kit or defeat the warning from this card.</x:v>
       </x:c>
       <x:c r="F214" s="9" t="str">
-        <x:v>The industry-standard repair uses Time-Sert inserts to repair the head bolt threads in the aluminum block with stronger steel threads. This can be performed with the engine in the vehicle. Use updated MLS head gaskets and proper torque specifications. Budget $2,500-$4,000 for this repair at a shop experienced with Northstars.</x:v>
+        <x:v>Confirm that the 2002 Seville is an STS equipped with CVRSS RPO F45. Have a qualified technician retrieve the suspension DTCs and run the ESC damper-actuator output test. For an intermittent C0577-type fault, the OEM procedure commands the affected solenoid while the suspected wiring and connector are moved to isolate the circuit or component. Confirm the failed circuit or damper before replacing a strut; do not order a strut, install a passive-conversion kit or defeat the warning from this card.</x:v>
       </x:c>
       <x:c r="G214" s="9" t="str">
-        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
       <x:c r="H214" s="9" t="str">
-        <x:v>GM Genuine Parts catalog — Northstar 4.6L Head Gasket Failure</x:v>
+        <x:v>Cadillac certified-service locator</x:v>
       </x:c>
       <x:c r="I214" s="9" t="str">
-        <x:v>https://parts.gmparts.com/</x:v>
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
       </x:c>
       <x:c r="J214" s="9" t="str">
-        <x:v>1993-2004 Cadillac Seville; select exact VIN, engine, trim, position and current supersession</x:v>
+        <x:v>2002-2002 Cadillac Seville instruction-specific diagnosis</x:v>
       </x:c>
       <x:c r="K214" s="9" t="str">
-        <x:v>manufacturer VIN-select parts catalog</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L214" s="9" t="str"/>
       <x:c r="M214" s="9" t="str">
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+      </x:c>
+      <x:c r="N214" s="41" t="str">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A215" s="40" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B215" s="9" t="str">
+        <x:v>cadillac-seville-northstar-hg-1993</x:v>
+      </x:c>
+      <x:c r="C215" s="9" t="str">
+        <x:v>1993-2004 | Cadillac | Seville | Northstar 4.6L</x:v>
+      </x:c>
+      <x:c r="D215" s="9" t="str">
+        <x:v>Northstar 4.6L Head Gasket Failure</x:v>
+      </x:c>
+      <x:c r="E215" s="9" t="str">
+        <x:v>The industry-standard repair uses Time-Sert inserts to repair the head bolt threads in the aluminum block with stronger steel threads. This can be performed with the engine in the vehicle. Use updated MLS head gaskets and proper torque specifications. Budget $2,500-$4,000 for this repair at a shop experienced with Northstars.</x:v>
+      </x:c>
+      <x:c r="F215" s="9" t="str">
+        <x:v>The industry-standard repair uses Time-Sert inserts to repair the head bolt threads in the aluminum block with stronger steel threads. This can be performed with the engine in the vehicle. Use updated MLS head gaskets and proper torque specifications. Budget $2,500-$4,000 for this repair at a shop experienced with Northstars.</x:v>
+      </x:c>
+      <x:c r="G215" s="9" t="str">
+        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H215" s="9" t="str">
+        <x:v>GM Genuine Parts catalog — Northstar 4.6L Head Gasket Failure</x:v>
+      </x:c>
+      <x:c r="I215" s="9" t="str">
+        <x:v>https://parts.gmparts.com/</x:v>
+      </x:c>
+      <x:c r="J215" s="9" t="str">
+        <x:v>1993-2004 Cadillac Seville; select exact VIN, engine, trim, position and current supersession</x:v>
+      </x:c>
+      <x:c r="K215" s="9" t="str">
+        <x:v>manufacturer VIN-select parts catalog</x:v>
+      </x:c>
+      <x:c r="L215" s="9" t="str"/>
+      <x:c r="M215" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N214" s="41" t="str">
+      <x:c r="N215" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="215" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A215" s="40" t="str"/>
-      <x:c r="B215" s="9" t="str"/>
-      <x:c r="C215" s="9" t="str"/>
-      <x:c r="D215" s="9" t="str"/>
-      <x:c r="E215" s="9" t="str"/>
-      <x:c r="F215" s="9" t="str"/>
-      <x:c r="G215" s="9" t="str"/>
-      <x:c r="H215" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I215" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J215" s="9" t="str">
+    <x:row r="216" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A216" s="40" t="str"/>
+      <x:c r="B216" s="9" t="str"/>
+      <x:c r="C216" s="9" t="str"/>
+      <x:c r="D216" s="9" t="str"/>
+      <x:c r="E216" s="9" t="str"/>
+      <x:c r="F216" s="9" t="str"/>
+      <x:c r="G216" s="9" t="str"/>
+      <x:c r="H216" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I216" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J216" s="9" t="str">
         <x:v>1993-2004 Cadillac Seville diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K215" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L215" s="9" t="str"/>
-      <x:c r="M215" s="9" t="str"/>
-      <x:c r="N215" s="41" t="str"/>
-    </x:row>
-    <x:row r="216" ht="369.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A216" s="40" t="n">
+      <x:c r="K216" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L216" s="9" t="str"/>
+      <x:c r="M216" s="9" t="str"/>
+      <x:c r="N216" s="41" t="str"/>
+    </x:row>
+    <x:row r="217" ht="369.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A217" s="40" t="n">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B216" s="9" t="str">
+      <x:c r="B217" s="9" t="str">
         <x:v>cadillac-seville-sts-suspension-2000</x:v>
       </x:c>
-      <x:c r="C216" s="9" t="str">
+      <x:c r="C217" s="9" t="str">
         <x:v>1998-2004 | Cadillac | Seville</x:v>
       </x:c>
-      <x:c r="D216" s="9" t="str">
+      <x:c r="D217" s="9" t="str">
         <x:v>Magnetic Ride Control Shock Absorber Failure</x:v>
       </x:c>
-      <x:c r="E216" s="9" t="str">
+      <x:c r="E217" s="9" t="str">
         <x:v>Replace the failed MRC shock absorber. OEM replacements are expensive; aftermarket passive shock conversions are available at lower cost but disable the adaptive ride feature. Replace in pairs (both fronts or both rears).</x:v>
       </x:c>
-      <x:c r="F216" s="9" t="str">
+      <x:c r="F217" s="9" t="str">
         <x:v>Replace the failed MRC shock absorber. OEM replacements are expensive; aftermarket passive shock conversions are available at lower cost but disable the adaptive ride feature. Replace in pairs (both fronts or both rears).</x:v>
       </x:c>
-      <x:c r="G216" s="9" t="str">
+      <x:c r="G217" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H216" s="9" t="str">
+      <x:c r="H217" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Magnetic Ride Control Shock Absorber Failure</x:v>
       </x:c>
-      <x:c r="I216" s="9" t="str">
+      <x:c r="I217" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J216" s="9" t="str">
+      <x:c r="J217" s="9" t="str">
         <x:v>1998-2004 Cadillac Seville; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K216" s="9" t="str">
+      <x:c r="K217" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L216" s="9" t="str"/>
-      <x:c r="M216" s="9" t="str">
+      <x:c r="L217" s="9" t="str"/>
+      <x:c r="M217" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N216" s="41" t="str">
+      <x:c r="N217" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="217" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A217" s="40" t="str"/>
-      <x:c r="B217" s="9" t="str"/>
-      <x:c r="C217" s="9" t="str"/>
-      <x:c r="D217" s="9" t="str"/>
-      <x:c r="E217" s="9" t="str"/>
-      <x:c r="F217" s="9" t="str"/>
-      <x:c r="G217" s="9" t="str"/>
-      <x:c r="H217" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I217" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J217" s="9" t="str">
+    <x:row r="218" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A218" s="40" t="str"/>
+      <x:c r="B218" s="9" t="str"/>
+      <x:c r="C218" s="9" t="str"/>
+      <x:c r="D218" s="9" t="str"/>
+      <x:c r="E218" s="9" t="str"/>
+      <x:c r="F218" s="9" t="str"/>
+      <x:c r="G218" s="9" t="str"/>
+      <x:c r="H218" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I218" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J218" s="9" t="str">
         <x:v>1998-2004 Cadillac Seville diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K217" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L217" s="9" t="str"/>
-      <x:c r="M217" s="9" t="str"/>
-      <x:c r="N217" s="41" t="str"/>
-    </x:row>
-    <x:row r="218" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A218" s="40" t="n">
+      <x:c r="K218" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L218" s="9" t="str"/>
+      <x:c r="M218" s="9" t="str"/>
+      <x:c r="N218" s="41" t="str"/>
+    </x:row>
+    <x:row r="219" ht="448.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A219" s="40" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B218" s="9" t="str">
+      <x:c r="B219" s="9" t="str">
         <x:v>cadillac-srx-awd-power-transfer-2010</x:v>
       </x:c>
-      <x:c r="C218" s="9" t="str">
+      <x:c r="C219" s="9" t="str">
         <x:v>2010-2016 | Cadillac | SRX</x:v>
       </x:c>
-      <x:c r="D218" s="9" t="str">
+      <x:c r="D219" s="9" t="str">
         <x:v>AWD Power Transfer Unit (PTU) Seal Leak and Bearing Noise</x:v>
       </x:c>
-      <x:c r="E218" s="9" t="str">
+      <x:c r="E219" s="9" t="str">
         <x:v>If caught early (seal leak only), replace the PTU seals and refill with the correct fluid. If bearing noise is present, the PTU must be replaced as it is not rebuildable. Check the PTU fluid at every oil change — many dealerships do not include this in their inspections. Use the GM-specified fluid only.</x:v>
       </x:c>
-      <x:c r="F218" s="9" t="str">
+      <x:c r="F219" s="9" t="str">
         <x:v>If caught early (seal leak only), replace the PTU seals and refill with the correct fluid. If bearing noise is present, the PTU must be replaced as it is not rebuildable. Check the PTU fluid at every oil change — many dealerships do not include this in their inspections. Use the GM-specified fluid only.</x:v>
       </x:c>
-      <x:c r="G218" s="9" t="str">
+      <x:c r="G219" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H218" s="9" t="str">
+      <x:c r="H219" s="9" t="str">
         <x:v>GM Genuine Parts catalog — AWD Power Transfer Unit  Seal Leak and Bearing Noise</x:v>
       </x:c>
-      <x:c r="I218" s="9" t="str">
+      <x:c r="I219" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J218" s="9" t="str">
+      <x:c r="J219" s="9" t="str">
         <x:v>2010-2016 Cadillac SRX; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K218" s="9" t="str">
+      <x:c r="K219" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L218" s="9" t="str"/>
-      <x:c r="M218" s="9" t="str">
+      <x:c r="L219" s="9" t="str"/>
+      <x:c r="M219" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N218" s="41" t="str">
+      <x:c r="N219" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="219" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A219" s="40" t="str"/>
-      <x:c r="B219" s="9" t="str"/>
-      <x:c r="C219" s="9" t="str"/>
-      <x:c r="D219" s="9" t="str"/>
-      <x:c r="E219" s="9" t="str"/>
-      <x:c r="F219" s="9" t="str"/>
-      <x:c r="G219" s="9" t="str"/>
-      <x:c r="H219" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I219" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J219" s="9" t="str">
+    <x:row r="220" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A220" s="40" t="str"/>
+      <x:c r="B220" s="9" t="str"/>
+      <x:c r="C220" s="9" t="str"/>
+      <x:c r="D220" s="9" t="str"/>
+      <x:c r="E220" s="9" t="str"/>
+      <x:c r="F220" s="9" t="str"/>
+      <x:c r="G220" s="9" t="str"/>
+      <x:c r="H220" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I220" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J220" s="9" t="str">
         <x:v>2010-2016 Cadillac SRX diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K219" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L219" s="9" t="str"/>
-      <x:c r="M219" s="9" t="str"/>
-      <x:c r="N219" s="41" t="str"/>
-    </x:row>
-    <x:row r="220" ht="290.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A220" s="40" t="n">
+      <x:c r="K220" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L220" s="9" t="str"/>
+      <x:c r="M220" s="9" t="str"/>
+      <x:c r="N220" s="41" t="str"/>
+    </x:row>
+    <x:row r="221" ht="290.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A221" s="40" t="n">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B220" s="9" t="str">
+      <x:c r="B221" s="9" t="str">
         <x:v>cadillac-srx-cue-screen-2013</x:v>
       </x:c>
-      <x:c r="C220" s="9" t="str">
+      <x:c r="C221" s="9" t="str">
         <x:v>2013-2016 | Cadillac | SRX</x:v>
       </x:c>
-      <x:c r="D220" s="9" t="str">
+      <x:c r="D221" s="9" t="str">
         <x:v>CUE Infotainment Touchscreen Delamination</x:v>
       </x:c>
-      <x:c r="E220" s="9" t="str">
+      <x:c r="E221" s="9" t="str">
         <x:v>Replace the CUE screen with OEM (GM 23106488) or aftermarket unit. Straightforward DIY replacement - screen snaps out with trim tools. Apply screen protector after installation.</x:v>
       </x:c>
-      <x:c r="F220" s="9" t="str">
+      <x:c r="F221" s="9" t="str">
         <x:v>Replace the CUE screen with OEM (GM 23106488) or aftermarket unit. Straightforward DIY replacement - screen snaps out with trim tools. Apply screen protector after installation.</x:v>
       </x:c>
-      <x:c r="G220" s="9" t="str">
+      <x:c r="G221" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H220" s="9" t="str">
+      <x:c r="H221" s="9" t="str">
         <x:v>GM Genuine Parts catalog — CUE Infotainment Touchscreen Delamination</x:v>
       </x:c>
-      <x:c r="I220" s="9" t="str">
+      <x:c r="I221" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J220" s="9" t="str">
+      <x:c r="J221" s="9" t="str">
         <x:v>2013-2016 Cadillac SRX; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K220" s="9" t="str">
+      <x:c r="K221" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L220" s="9" t="str"/>
-      <x:c r="M220" s="9" t="str">
+      <x:c r="L221" s="9" t="str"/>
+      <x:c r="M221" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N220" s="41" t="str">
+      <x:c r="N221" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="221" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A221" s="40" t="str"/>
-      <x:c r="B221" s="9" t="str"/>
-      <x:c r="C221" s="9" t="str"/>
-      <x:c r="D221" s="9" t="str"/>
-      <x:c r="E221" s="9" t="str"/>
-      <x:c r="F221" s="9" t="str"/>
-      <x:c r="G221" s="9" t="str"/>
-      <x:c r="H221" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I221" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J221" s="9" t="str">
+    <x:row r="222" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A222" s="40" t="str"/>
+      <x:c r="B222" s="9" t="str"/>
+      <x:c r="C222" s="9" t="str"/>
+      <x:c r="D222" s="9" t="str"/>
+      <x:c r="E222" s="9" t="str"/>
+      <x:c r="F222" s="9" t="str"/>
+      <x:c r="G222" s="9" t="str"/>
+      <x:c r="H222" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I222" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J222" s="9" t="str">
         <x:v>2013-2016 Cadillac SRX diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K221" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L221" s="9" t="str"/>
-      <x:c r="M221" s="9" t="str"/>
-      <x:c r="N221" s="41" t="str"/>
-    </x:row>
-    <x:row r="222" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A222" s="40" t="n">
+      <x:c r="K222" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L222" s="9" t="str"/>
+      <x:c r="M222" s="9" t="str"/>
+      <x:c r="N222" s="41" t="str"/>
+    </x:row>
+    <x:row r="223" ht="448.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A223" s="40" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="B222" s="9" t="str">
+      <x:c r="B223" s="9" t="str">
         <x:v>cadillac-srx-liftgate-2010</x:v>
       </x:c>
-      <x:c r="C222" s="9" t="str">
+      <x:c r="C223" s="9" t="str">
         <x:v>2010-2014 | Cadillac | SRX</x:v>
       </x:c>
-      <x:c r="D222" s="9" t="str">
+      <x:c r="D223" s="9" t="str">
         <x:v>Power Liftgate May Sag or Reverse When the Right Gas Strut Is Worn</x:v>
       </x:c>
-      <x:c r="E222" s="9" t="str">
+      <x:c r="E223" s="9" t="str">
         <x:v>Have the right gas strut inspected and replace it only if it fails the GM condition checks. Do not replace the actuator or pump without diagnosis. The ShowMeTheParts lookup returned no candidate, so this card does not link or prescribe a generic pair of struts or a liftgate motor.</x:v>
       </x:c>
-      <x:c r="F222" s="9" t="str">
+      <x:c r="F223" s="9" t="str">
         <x:v>Have the right gas strut inspected and replace it only if it fails the GM condition checks. Do not replace the actuator or pump without diagnosis. The ShowMeTheParts lookup returned no candidate, so this card does not link or prescribe a generic pair of struts or a liftgate motor.</x:v>
       </x:c>
-      <x:c r="G222" s="9" t="str">
+      <x:c r="G223" s="9" t="str">
         <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
-      <x:c r="H222" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I222" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J222" s="9" t="str">
+      <x:c r="H223" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I223" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J223" s="9" t="str">
         <x:v>2010-2014 Cadillac SRX instruction-specific diagnosis</x:v>
       </x:c>
-      <x:c r="K222" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L222" s="9" t="str"/>
-      <x:c r="M222" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
-      </x:c>
-      <x:c r="N222" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A223" s="40" t="n">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="B223" s="9" t="str">
-        <x:v>cadillac-srx-strut-mount-2010</x:v>
-      </x:c>
-      <x:c r="C223" s="9" t="str">
-        <x:v>2010-2016 | Cadillac | SRX</x:v>
-      </x:c>
-      <x:c r="D223" s="9" t="str">
-        <x:v>Front Strut Mount Bearing Failure and Clunking</x:v>
-      </x:c>
-      <x:c r="E223" s="9" t="str">
-        <x:v>Replace both front strut mounts and bearings. This is typically done during strut replacement. Use OEM-quality mounts with metal bearing races rather than all-rubber designs. A wheel alignment is required after strut mount replacement. Replace struts at the same time if they have over 60,000 miles.</x:v>
-      </x:c>
-      <x:c r="F223" s="9" t="str">
-        <x:v>Replace both front strut mounts and bearings. This is typically done during strut replacement. Use OEM-quality mounts with metal bearing races rather than all-rubber designs. A wheel alignment is required after strut mount replacement. Replace struts at the same time if they have over 60,000 miles.</x:v>
-      </x:c>
-      <x:c r="G223" s="9" t="str">
-        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
-      </x:c>
-      <x:c r="H223" s="9" t="str">
-        <x:v>GM Genuine Parts catalog — Front Strut Mount Bearing Failure and Clunking</x:v>
-      </x:c>
-      <x:c r="I223" s="9" t="str">
-        <x:v>https://parts.gmparts.com/</x:v>
-      </x:c>
-      <x:c r="J223" s="9" t="str">
-        <x:v>2010-2016 Cadillac SRX; select exact VIN, engine, trim, position and current supersession</x:v>
-      </x:c>
       <x:c r="K223" s="9" t="str">
-        <x:v>manufacturer VIN-select parts catalog</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L223" s="9" t="str"/>
       <x:c r="M223" s="9" t="str">
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+      </x:c>
+      <x:c r="N223" s="41" t="str">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="501.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A224" s="40" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B224" s="9" t="str">
+        <x:v>cadillac-srx-strut-mount-2010</x:v>
+      </x:c>
+      <x:c r="C224" s="9" t="str">
+        <x:v>2010-2016 | Cadillac | SRX</x:v>
+      </x:c>
+      <x:c r="D224" s="9" t="str">
+        <x:v>Front Strut Mount Bearing Failure and Clunking</x:v>
+      </x:c>
+      <x:c r="E224" s="9" t="str">
+        <x:v>Replace both front strut mounts and bearings. This is typically done during strut replacement. Use OEM-quality mounts with metal bearing races rather than all-rubber designs. A wheel alignment is required after strut mount replacement. Replace struts at the same time if they have over 60,000 miles.</x:v>
+      </x:c>
+      <x:c r="F224" s="9" t="str">
+        <x:v>Replace both front strut mounts and bearings. This is typically done during strut replacement. Use OEM-quality mounts with metal bearing races rather than all-rubber designs. A wheel alignment is required after strut mount replacement. Replace struts at the same time if they have over 60,000 miles.</x:v>
+      </x:c>
+      <x:c r="G224" s="9" t="str">
+        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H224" s="9" t="str">
+        <x:v>GM Genuine Parts catalog — Front Strut Mount Bearing Failure and Clunking</x:v>
+      </x:c>
+      <x:c r="I224" s="9" t="str">
+        <x:v>https://parts.gmparts.com/</x:v>
+      </x:c>
+      <x:c r="J224" s="9" t="str">
+        <x:v>2010-2016 Cadillac SRX; select exact VIN, engine, trim, position and current supersession</x:v>
+      </x:c>
+      <x:c r="K224" s="9" t="str">
+        <x:v>manufacturer VIN-select parts catalog</x:v>
+      </x:c>
+      <x:c r="L224" s="9" t="str"/>
+      <x:c r="M224" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N223" s="41" t="str">
+      <x:c r="N224" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="224" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A224" s="40" t="str"/>
-      <x:c r="B224" s="9" t="str"/>
-      <x:c r="C224" s="9" t="str"/>
-      <x:c r="D224" s="9" t="str"/>
-      <x:c r="E224" s="9" t="str"/>
-      <x:c r="F224" s="9" t="str"/>
-      <x:c r="G224" s="9" t="str"/>
-      <x:c r="H224" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I224" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J224" s="9" t="str">
+    <x:row r="225" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A225" s="40" t="str"/>
+      <x:c r="B225" s="9" t="str"/>
+      <x:c r="C225" s="9" t="str"/>
+      <x:c r="D225" s="9" t="str"/>
+      <x:c r="E225" s="9" t="str"/>
+      <x:c r="F225" s="9" t="str"/>
+      <x:c r="G225" s="9" t="str"/>
+      <x:c r="H225" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I225" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J225" s="9" t="str">
         <x:v>2010-2016 Cadillac SRX diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K224" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L224" s="9" t="str"/>
-      <x:c r="M224" s="9" t="str"/>
-      <x:c r="N224" s="41" t="str"/>
-    </x:row>
-    <x:row r="225" ht="699.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A225" s="40" t="n">
+      <x:c r="K225" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L225" s="9" t="str"/>
+      <x:c r="M225" s="9" t="str"/>
+      <x:c r="N225" s="41" t="str"/>
+    </x:row>
+    <x:row r="226" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A226" s="40" t="n">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B225" s="9" t="str">
+      <x:c r="B226" s="9" t="str">
         <x:v>cadillac-srx-timing-chain-2010</x:v>
       </x:c>
-      <x:c r="C225" s="9" t="str">
+      <x:c r="C226" s="9" t="str">
         <x:v>2010-2012 | Cadillac | SRX | 2.8L Turbo V6 (RPO LAU), 3.0L V6 (RPO LF1), 3.6L V6 (RPO LFX), 3.0L V6 (RPO LFW)</x:v>
       </x:c>
-      <x:c r="D225" s="9" t="str">
+      <x:c r="D226" s="9" t="str">
         <x:v>High-Feature V6 Timing-Chain DTCs Require Exact Kit Identification</x:v>
       </x:c>
-      <x:c r="E225" s="9" t="str">
+      <x:c r="E226" s="9" t="str">
         <x:v>Have a qualified technician confirm the DTCs, engine RPO, build information and chain wear through current service information. If the bulletin applies, use the GM kit mapped to the exact application, inspect guides using the bulletin criterion and inspect pre-June 5, 2009 cylinder-head hardware when applicable. Do not order the frozen aftermarket kit or water pump from this card; the ShowMeTheParts lookup returned no candidate.</x:v>
       </x:c>
-      <x:c r="F225" s="9" t="str">
+      <x:c r="F226" s="9" t="str">
         <x:v>Have a qualified technician confirm the DTCs, engine RPO, build information and chain wear through current service information. If the bulletin applies, use the GM kit mapped to the exact application, inspect guides using the bulletin criterion and inspect pre-June 5, 2009 cylinder-head hardware when applicable. Do not order the frozen aftermarket kit or water pump from this card; the ShowMeTheParts lookup returned no candidate.</x:v>
       </x:c>
-      <x:c r="G225" s="9" t="str">
+      <x:c r="G226" s="9" t="str">
         <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
-      <x:c r="H225" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I225" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J225" s="9" t="str">
+      <x:c r="H226" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I226" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J226" s="9" t="str">
         <x:v>2010-2012 Cadillac SRX instruction-specific diagnosis</x:v>
       </x:c>
-      <x:c r="K225" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L225" s="9" t="str"/>
-      <x:c r="M225" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
-      </x:c>
-      <x:c r="N225" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A226" s="40" t="n">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B226" s="9" t="str">
-        <x:v>cadillac-sts-cue-screen-2008</x:v>
-      </x:c>
-      <x:c r="C226" s="9" t="str">
-        <x:v>2008-2011 | Cadillac | STS</x:v>
-      </x:c>
-      <x:c r="D226" s="9" t="str">
-        <x:v>Navigation and Climate Control Screen Delamination</x:v>
-      </x:c>
-      <x:c r="E226" s="9" t="str">
-        <x:v>Replace the touchscreen display unit. Aftermarket refurbished screens are available at lower cost than dealer parts. Some specialty shops can repair the delamination issue. A sunshade on the windshield when parked helps prevent heat damage to the replacement screen.</x:v>
-      </x:c>
-      <x:c r="F226" s="9" t="str">
-        <x:v>Replace the touchscreen display unit. Aftermarket refurbished screens are available at lower cost than dealer parts. Some specialty shops can repair the delamination issue. A sunshade on the windshield when parked helps prevent heat damage to the replacement screen.</x:v>
-      </x:c>
-      <x:c r="G226" s="9" t="str">
-        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
-      </x:c>
-      <x:c r="H226" s="9" t="str">
-        <x:v>GM Genuine Parts catalog — Navigation and Climate Control Screen Delamination</x:v>
-      </x:c>
-      <x:c r="I226" s="9" t="str">
-        <x:v>https://parts.gmparts.com/</x:v>
-      </x:c>
-      <x:c r="J226" s="9" t="str">
-        <x:v>2008-2011 Cadillac STS; select exact VIN, engine, trim, position and current supersession</x:v>
-      </x:c>
       <x:c r="K226" s="9" t="str">
-        <x:v>manufacturer VIN-select parts catalog</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L226" s="9" t="str"/>
       <x:c r="M226" s="9" t="str">
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+      </x:c>
+      <x:c r="N226" s="41" t="str">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="448.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A227" s="40" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B227" s="9" t="str">
+        <x:v>cadillac-sts-cue-screen-2008</x:v>
+      </x:c>
+      <x:c r="C227" s="9" t="str">
+        <x:v>2008-2011 | Cadillac | STS</x:v>
+      </x:c>
+      <x:c r="D227" s="9" t="str">
+        <x:v>Navigation and Climate Control Screen Delamination</x:v>
+      </x:c>
+      <x:c r="E227" s="9" t="str">
+        <x:v>Replace the touchscreen display unit. Aftermarket refurbished screens are available at lower cost than dealer parts. Some specialty shops can repair the delamination issue. A sunshade on the windshield when parked helps prevent heat damage to the replacement screen.</x:v>
+      </x:c>
+      <x:c r="F227" s="9" t="str">
+        <x:v>Replace the touchscreen display unit. Aftermarket refurbished screens are available at lower cost than dealer parts. Some specialty shops can repair the delamination issue. A sunshade on the windshield when parked helps prevent heat damage to the replacement screen.</x:v>
+      </x:c>
+      <x:c r="G227" s="9" t="str">
+        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H227" s="9" t="str">
+        <x:v>GM Genuine Parts catalog — Navigation and Climate Control Screen Delamination</x:v>
+      </x:c>
+      <x:c r="I227" s="9" t="str">
+        <x:v>https://parts.gmparts.com/</x:v>
+      </x:c>
+      <x:c r="J227" s="9" t="str">
+        <x:v>2008-2011 Cadillac STS; select exact VIN, engine, trim, position and current supersession</x:v>
+      </x:c>
+      <x:c r="K227" s="9" t="str">
+        <x:v>manufacturer VIN-select parts catalog</x:v>
+      </x:c>
+      <x:c r="L227" s="9" t="str"/>
+      <x:c r="M227" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N226" s="41" t="str">
+      <x:c r="N227" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="227" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A227" s="40" t="str"/>
-      <x:c r="B227" s="9" t="str"/>
-      <x:c r="C227" s="9" t="str"/>
-      <x:c r="D227" s="9" t="str"/>
-      <x:c r="E227" s="9" t="str"/>
-      <x:c r="F227" s="9" t="str"/>
-      <x:c r="G227" s="9" t="str"/>
-      <x:c r="H227" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I227" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J227" s="9" t="str">
+    <x:row r="228" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A228" s="40" t="str"/>
+      <x:c r="B228" s="9" t="str"/>
+      <x:c r="C228" s="9" t="str"/>
+      <x:c r="D228" s="9" t="str"/>
+      <x:c r="E228" s="9" t="str"/>
+      <x:c r="F228" s="9" t="str"/>
+      <x:c r="G228" s="9" t="str"/>
+      <x:c r="H228" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I228" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J228" s="9" t="str">
         <x:v>2008-2011 Cadillac STS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K227" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L227" s="9" t="str"/>
-      <x:c r="M227" s="9" t="str"/>
-      <x:c r="N227" s="41" t="str"/>
-    </x:row>
-    <x:row r="228" ht="607.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A228" s="40" t="n">
+      <x:c r="K228" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L228" s="9" t="str"/>
+      <x:c r="M228" s="9" t="str"/>
+      <x:c r="N228" s="41" t="str"/>
+    </x:row>
+    <x:row r="229" ht="607.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A229" s="40" t="n">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B228" s="9" t="str">
+      <x:c r="B229" s="9" t="str">
         <x:v>cadillac-sts-northstar-headgasket-1998</x:v>
       </x:c>
-      <x:c r="C228" s="9" t="str">
+      <x:c r="C229" s="9" t="str">
         <x:v>1998-2011 | Cadillac | STS | 4.6L Northstar V8</x:v>
       </x:c>
-      <x:c r="D228" s="9" t="str">
+      <x:c r="D229" s="9" t="str">
         <x:v>4.6L Northstar V8 Head Gasket Failure and Bolt Pull-Out</x:v>
       </x:c>
-      <x:c r="E228" s="9" t="str">
+      <x:c r="E229" s="9" t="str">
         <x:v>The permanent fix is the Northstar Performance "Norm's Inserts" or Time-Sert procedure — the engine is removed, heads pulled, and steel thread inserts are installed in all head bolt locations in the aluminum block. This is a 30+ hour job. Alternatively, a used/reman engine with inserts already installed can be swapped in. Bar's Leaks Head Gasket Fix (1111) is a temporary measure that can buy time.</x:v>
       </x:c>
-      <x:c r="F228" s="9" t="str">
+      <x:c r="F229" s="9" t="str">
         <x:v>The permanent fix is the Northstar Performance "Norm's Inserts" or Time-Sert procedure — the engine is removed, heads pulled, and steel thread inserts are installed in all head bolt locations in the aluminum block. This is a 30+ hour job. Alternatively, a used/reman engine with inserts already installed can be swapped in. Bar's Leaks Head Gasket Fix (1111) is a temporary measure that can buy time.</x:v>
       </x:c>
-      <x:c r="G228" s="9" t="str">
+      <x:c r="G229" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H228" s="9" t="str">
+      <x:c r="H229" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 4.6L Northstar V8 Head Gasket Failure and Bolt Pull-Out</x:v>
       </x:c>
-      <x:c r="I228" s="9" t="str">
+      <x:c r="I229" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J228" s="9" t="str">
+      <x:c r="J229" s="9" t="str">
         <x:v>1998-2011 Cadillac STS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K228" s="9" t="str">
+      <x:c r="K229" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L228" s="9" t="str"/>
-      <x:c r="M228" s="9" t="str">
+      <x:c r="L229" s="9" t="str"/>
+      <x:c r="M229" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N228" s="41" t="str">
+      <x:c r="N229" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="229" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A229" s="40" t="str"/>
-      <x:c r="B229" s="9" t="str"/>
-      <x:c r="C229" s="9" t="str"/>
-      <x:c r="D229" s="9" t="str"/>
-      <x:c r="E229" s="9" t="str"/>
-      <x:c r="F229" s="9" t="str"/>
-      <x:c r="G229" s="9" t="str"/>
-      <x:c r="H229" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I229" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J229" s="9" t="str">
+    <x:row r="230" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A230" s="40" t="str"/>
+      <x:c r="B230" s="9" t="str"/>
+      <x:c r="C230" s="9" t="str"/>
+      <x:c r="D230" s="9" t="str"/>
+      <x:c r="E230" s="9" t="str"/>
+      <x:c r="F230" s="9" t="str"/>
+      <x:c r="G230" s="9" t="str"/>
+      <x:c r="H230" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I230" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J230" s="9" t="str">
         <x:v>1998-2011 Cadillac STS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K229" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L229" s="9" t="str"/>
-      <x:c r="M229" s="9" t="str"/>
-      <x:c r="N229" s="41" t="str"/>
-    </x:row>
-    <x:row r="230" ht="514.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A230" s="40" t="n">
+      <x:c r="K230" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L230" s="9" t="str"/>
+      <x:c r="M230" s="9" t="str"/>
+      <x:c r="N230" s="41" t="str"/>
+    </x:row>
+    <x:row r="231" ht="514.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A231" s="40" t="n">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="B230" s="9" t="str">
+      <x:c r="B231" s="9" t="str">
         <x:v>cadillac-sts-rear-subframe-2005</x:v>
       </x:c>
-      <x:c r="C230" s="9" t="str">
+      <x:c r="C231" s="9" t="str">
         <x:v>2005-2011 | Cadillac | STS</x:v>
       </x:c>
-      <x:c r="D230" s="9" t="str">
+      <x:c r="D231" s="9" t="str">
         <x:v>Rear Subframe Cradle Mount Cracking and Separation</x:v>
       </x:c>
-      <x:c r="E230" s="9" t="str">
+      <x:c r="E231" s="9" t="str">
         <x:v>Inspect rear subframe mounting points for cracking — look from underneath for rust-through at the four rear cradle mounts. If caught early, a body shop can weld reinforcement plates. If advanced, the mounts may need to be cut out and new mounting plates welded in. This is a structural repair that must be done properly for safety.</x:v>
       </x:c>
-      <x:c r="F230" s="9" t="str">
+      <x:c r="F231" s="9" t="str">
         <x:v>Inspect rear subframe mounting points for cracking — look from underneath for rust-through at the four rear cradle mounts. If caught early, a body shop can weld reinforcement plates. If advanced, the mounts may need to be cut out and new mounting plates welded in. This is a structural repair that must be done properly for safety.</x:v>
       </x:c>
-      <x:c r="G230" s="9" t="str">
+      <x:c r="G231" s="9" t="str">
         <x:v>SPECIALIST / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H230" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I230" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J230" s="9" t="str">
+      <x:c r="H231" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I231" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J231" s="9" t="str">
         <x:v>2005-2011 Cadillac STS diagnosis, VIN/RPO confirmation and repair</x:v>
-      </x:c>
-      <x:c r="K230" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L230" s="9" t="str"/>
-      <x:c r="M230" s="9" t="str">
-        <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
-      </x:c>
-      <x:c r="N230" s="41" t="str">
-        <x:v>Use a qualified specialist or manufacturer service route; no generic kit or one-size-fits-all part.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="231" ht="897.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A231" s="40" t="n">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="B231" s="9" t="str">
-        <x:v>cadillac-sts-timing-chain-2005</x:v>
-      </x:c>
-      <x:c r="C231" s="9" t="str">
-        <x:v>2007-2011 | Cadillac | STS | 3.6L V6 (RPO LY7), 3.6L V6 (RPO LLT)</x:v>
-      </x:c>
-      <x:c r="D231" s="9" t="str">
-        <x:v>3.6L V6 Timing-Chain DTCs Require Exact Kit and Guide Inspection</x:v>
-      </x:c>
-      <x:c r="E231" s="9" t="str">
-        <x:v>Have a qualified technician confirm the 3.6L engine RPO, DTCs, build information and chain wear through current service information. For a 2007 vehicle, use the current 07-06-01-013 early-build identification instructions where directed. If 12-06-01-009E applies, use the GM kit mapped to the exact application, inspect guides using the bulletin criterion and inspect pre-June 5, 2009 cylinder-head hardware when applicable. Do not order a generic timing kit or oil from this card; the ShowMeTheParts lookup returned no candidate.</x:v>
-      </x:c>
-      <x:c r="F231" s="9" t="str">
-        <x:v>Have a qualified technician confirm the 3.6L engine RPO, DTCs, build information and chain wear through current service information. For a 2007 vehicle, use the current 07-06-01-013 early-build identification instructions where directed. If 12-06-01-009E applies, use the GM kit mapped to the exact application, inspect guides using the bulletin criterion and inspect pre-June 5, 2009 cylinder-head hardware when applicable. Do not order a generic timing kit or oil from this card; the ShowMeTheParts lookup returned no candidate.</x:v>
-      </x:c>
-      <x:c r="G231" s="9" t="str">
-        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
-      </x:c>
-      <x:c r="H231" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I231" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J231" s="9" t="str">
-        <x:v>2007-2011 Cadillac STS instruction-specific diagnosis</x:v>
       </x:c>
       <x:c r="K231" s="9" t="str">
         <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L231" s="9" t="str"/>
       <x:c r="M231" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+        <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
       <x:c r="N231" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="232" ht="567.5999755859375" hidden="0" customHeight="1">
+        <x:v>Use a qualified specialist or manufacturer service route; no generic kit or one-size-fits-all part.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A232" s="40" t="n">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B232" s="9" t="str">
-        <x:v>cadillac-sts-transmission-overheating-2005</x:v>
+        <x:v>cadillac-sts-timing-chain-2005</x:v>
       </x:c>
       <x:c r="C232" s="9" t="str">
-        <x:v>2005-2011 | Cadillac | STS | 3.6L V6</x:v>
+        <x:v>2007-2011 | Cadillac | STS | 3.6L V6 (RPO LY7), 3.6L V6 (RPO LLT)</x:v>
       </x:c>
       <x:c r="D232" s="9" t="str">
-        <x:v>6L50 6-Speed Automatic Transmission Overheating and Harsh Shifts</x:v>
+        <x:v>3.6L V6 Timing-Chain DTCs Require Exact Kit and Guide Inspection</x:v>
       </x:c>
       <x:c r="E232" s="9" t="str">
-        <x:v>Perform a complete transmission fluid and filter change (not a flush) every 30,000 miles using Dexron VI. Install an auxiliary transmission cooler for vehicles used in hot climates or towing. If shifts are already harsh, a valve body rebuild or replacement with updated solenoids may be required. Torque converter replacement is needed if shudder is present.</x:v>
+        <x:v>Have a qualified technician confirm the 3.6L engine RPO, DTCs, build information and chain wear through current service information. For a 2007 vehicle, use the current 07-06-01-013 early-build identification instructions where directed. If 12-06-01-009E applies, use the GM kit mapped to the exact application, inspect guides using the bulletin criterion and inspect pre-June 5, 2009 cylinder-head hardware when applicable. Do not order a generic timing kit or oil from this card; the ShowMeTheParts lookup returned no candidate.</x:v>
       </x:c>
       <x:c r="F232" s="9" t="str">
-        <x:v>Perform a complete transmission fluid and filter change (not a flush) every 30,000 miles using Dexron VI. Install an auxiliary transmission cooler for vehicles used in hot climates or towing. If shifts are already harsh, a valve body rebuild or replacement with updated solenoids may be required. Torque converter replacement is needed if shudder is present.</x:v>
+        <x:v>Have a qualified technician confirm the 3.6L engine RPO, DTCs, build information and chain wear through current service information. For a 2007 vehicle, use the current 07-06-01-013 early-build identification instructions where directed. If 12-06-01-009E applies, use the GM kit mapped to the exact application, inspect guides using the bulletin criterion and inspect pre-June 5, 2009 cylinder-head hardware when applicable. Do not order a generic timing kit or oil from this card; the ShowMeTheParts lookup returned no candidate.</x:v>
       </x:c>
       <x:c r="G232" s="9" t="str">
-        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+        <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
       <x:c r="H232" s="9" t="str">
-        <x:v>GM Genuine Parts catalog — 6L50 6-Speed Automatic Transmission Overheating and Harsh Shifts</x:v>
+        <x:v>Cadillac certified-service locator</x:v>
       </x:c>
       <x:c r="I232" s="9" t="str">
-        <x:v>https://parts.gmparts.com/</x:v>
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
       </x:c>
       <x:c r="J232" s="9" t="str">
-        <x:v>2005-2011 Cadillac STS; select exact VIN, engine, trim, position and current supersession</x:v>
+        <x:v>2007-2011 Cadillac STS instruction-specific diagnosis</x:v>
       </x:c>
       <x:c r="K232" s="9" t="str">
-        <x:v>manufacturer VIN-select parts catalog</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L232" s="9" t="str"/>
       <x:c r="M232" s="9" t="str">
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+      </x:c>
+      <x:c r="N232" s="41" t="str">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A233" s="40" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B233" s="9" t="str">
+        <x:v>cadillac-sts-transmission-overheating-2005</x:v>
+      </x:c>
+      <x:c r="C233" s="9" t="str">
+        <x:v>2005-2011 | Cadillac | STS | 3.6L V6</x:v>
+      </x:c>
+      <x:c r="D233" s="9" t="str">
+        <x:v>6L50 6-Speed Automatic Transmission Overheating and Harsh Shifts</x:v>
+      </x:c>
+      <x:c r="E233" s="9" t="str">
+        <x:v>Perform a complete transmission fluid and filter change (not a flush) every 30,000 miles using Dexron VI. Install an auxiliary transmission cooler for vehicles used in hot climates or towing. If shifts are already harsh, a valve body rebuild or replacement with updated solenoids may be required. Torque converter replacement is needed if shudder is present.</x:v>
+      </x:c>
+      <x:c r="F233" s="9" t="str">
+        <x:v>Perform a complete transmission fluid and filter change (not a flush) every 30,000 miles using Dexron VI. Install an auxiliary transmission cooler for vehicles used in hot climates or towing. If shifts are already harsh, a valve body rebuild or replacement with updated solenoids may be required. Torque converter replacement is needed if shudder is present.</x:v>
+      </x:c>
+      <x:c r="G233" s="9" t="str">
+        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H233" s="9" t="str">
+        <x:v>GM Genuine Parts catalog — 6L50 6-Speed Automatic Transmission Overheating and Harsh Shifts</x:v>
+      </x:c>
+      <x:c r="I233" s="9" t="str">
+        <x:v>https://parts.gmparts.com/</x:v>
+      </x:c>
+      <x:c r="J233" s="9" t="str">
+        <x:v>2005-2011 Cadillac STS; select exact VIN, engine, trim, position and current supersession</x:v>
+      </x:c>
+      <x:c r="K233" s="9" t="str">
+        <x:v>manufacturer VIN-select parts catalog</x:v>
+      </x:c>
+      <x:c r="L233" s="9" t="str"/>
+      <x:c r="M233" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N232" s="41" t="str">
+      <x:c r="N233" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="233" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A233" s="40" t="str"/>
-      <x:c r="B233" s="9" t="str"/>
-      <x:c r="C233" s="9" t="str"/>
-      <x:c r="D233" s="9" t="str"/>
-      <x:c r="E233" s="9" t="str"/>
-      <x:c r="F233" s="9" t="str"/>
-      <x:c r="G233" s="9" t="str"/>
-      <x:c r="H233" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I233" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J233" s="9" t="str">
+    <x:row r="234" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A234" s="40" t="str"/>
+      <x:c r="B234" s="9" t="str"/>
+      <x:c r="C234" s="9" t="str"/>
+      <x:c r="D234" s="9" t="str"/>
+      <x:c r="E234" s="9" t="str"/>
+      <x:c r="F234" s="9" t="str"/>
+      <x:c r="G234" s="9" t="str"/>
+      <x:c r="H234" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I234" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J234" s="9" t="str">
         <x:v>2005-2011 Cadillac STS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K233" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L233" s="9" t="str"/>
-      <x:c r="M233" s="9" t="str"/>
-      <x:c r="N233" s="41" t="str"/>
-    </x:row>
-    <x:row r="234" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A234" s="40" t="n">
+      <x:c r="K234" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L234" s="9" t="str"/>
+      <x:c r="M234" s="9" t="str"/>
+      <x:c r="N234" s="41" t="str"/>
+    </x:row>
+    <x:row r="235" ht="686.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A235" s="40" t="n">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B234" s="9" t="str">
+      <x:c r="B235" s="9" t="str">
         <x:v>cadillac-xt4-20t-timing-chain-2019</x:v>
       </x:c>
-      <x:c r="C234" s="9" t="str">
+      <x:c r="C235" s="9" t="str">
         <x:v>2019-2019 | Cadillac | XT4 | 2.0L Turbo I4 (RPO LSY)</x:v>
       </x:c>
-      <x:c r="D234" s="9" t="str">
+      <x:c r="D235" s="9" t="str">
         <x:v>Front-Engine Rattle May Require Timing-Chain Tensioner Inspection</x:v>
       </x:c>
-      <x:c r="E234" s="9" t="str">
+      <x:c r="E235" s="9" t="str">
         <x:v>Have a qualified technician verify the engine RPO and DTCs, inspect both camshaft actuator valve snap rings, then inspect the timing-chain tensioner and guides using current Cadillac service information. Replace only the failed or damaged components identified by that inspection. The exact ShowMeTheParts lookup returned no timing-chain candidate, so the former aftermarket kit and water-pump links were removed.</x:v>
       </x:c>
-      <x:c r="F234" s="9" t="str">
+      <x:c r="F235" s="9" t="str">
         <x:v>Have a qualified technician verify the engine RPO and DTCs, inspect both camshaft actuator valve snap rings, then inspect the timing-chain tensioner and guides using current Cadillac service information. Replace only the failed or damaged components identified by that inspection. The exact ShowMeTheParts lookup returned no timing-chain candidate, so the former aftermarket kit and water-pump links were removed.</x:v>
       </x:c>
-      <x:c r="G234" s="9" t="str">
+      <x:c r="G235" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H234" s="9" t="str">
+      <x:c r="H235" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Front-Engine Rattle May Require Timing-Chain Tensioner Inspection</x:v>
       </x:c>
-      <x:c r="I234" s="9" t="str">
+      <x:c r="I235" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J234" s="9" t="str">
+      <x:c r="J235" s="9" t="str">
         <x:v>2019-2019 Cadillac XT4; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K234" s="9" t="str">
+      <x:c r="K235" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L234" s="9" t="str"/>
-      <x:c r="M234" s="9" t="str">
+      <x:c r="L235" s="9" t="str"/>
+      <x:c r="M235" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N234" s="41" t="str">
+      <x:c r="N235" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="235" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A235" s="40" t="str"/>
-      <x:c r="B235" s="9" t="str"/>
-      <x:c r="C235" s="9" t="str"/>
-      <x:c r="D235" s="9" t="str"/>
-      <x:c r="E235" s="9" t="str"/>
-      <x:c r="F235" s="9" t="str"/>
-      <x:c r="G235" s="9" t="str"/>
-      <x:c r="H235" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I235" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J235" s="9" t="str">
+    <x:row r="236" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A236" s="40" t="str"/>
+      <x:c r="B236" s="9" t="str"/>
+      <x:c r="C236" s="9" t="str"/>
+      <x:c r="D236" s="9" t="str"/>
+      <x:c r="E236" s="9" t="str"/>
+      <x:c r="F236" s="9" t="str"/>
+      <x:c r="G236" s="9" t="str"/>
+      <x:c r="H236" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I236" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J236" s="9" t="str">
         <x:v>2019-2019 Cadillac XT4 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K235" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L235" s="9" t="str"/>
-      <x:c r="M235" s="9" t="str"/>
-      <x:c r="N235" s="41" t="str"/>
-    </x:row>
-    <x:row r="236" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A236" s="40" t="n">
+      <x:c r="K236" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L236" s="9" t="str"/>
+      <x:c r="M236" s="9" t="str"/>
+      <x:c r="N236" s="41" t="str"/>
+    </x:row>
+    <x:row r="237" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A237" s="40" t="n">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B236" s="9" t="str">
+      <x:c r="B237" s="9" t="str">
         <x:v>cadillac-xt4-infotainment-issues-2019</x:v>
       </x:c>
-      <x:c r="C236" s="9" t="str">
+      <x:c r="C237" s="9" t="str">
         <x:v>2020-2020 | Cadillac | XT4</x:v>
       </x:c>
-      <x:c r="D236" s="9" t="str">
+      <x:c r="D237" s="9" t="str">
         <x:v>Blank Radio Display or No Audio Is Limited to Early Radio Software</x:v>
       </x:c>
-      <x:c r="E236" s="9" t="str">
+      <x:c r="E237" s="9" t="str">
         <x:v>Check the equipment RPOs and radio build number before applying this bulletin. If the version is U145/V145 or earlier, a qualified technician should reprogram the A11 radio by USB under current GM procedures. If it is U146/V146 or later, stop and diagnose through current service information. The former generic replacement-screen link was removed.</x:v>
       </x:c>
-      <x:c r="F236" s="9" t="str">
+      <x:c r="F237" s="9" t="str">
         <x:v>Check the equipment RPOs and radio build number before applying this bulletin. If the version is U145/V145 or earlier, a qualified technician should reprogram the A11 radio by USB under current GM procedures. If it is U146/V146 or later, stop and diagnose through current service information. The former generic replacement-screen link was removed.</x:v>
       </x:c>
-      <x:c r="G236" s="9" t="str">
+      <x:c r="G237" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H236" s="9" t="str">
+      <x:c r="H237" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Blank Radio Display or No Audio Is Limited to Early Radio Software</x:v>
       </x:c>
-      <x:c r="I236" s="9" t="str">
+      <x:c r="I237" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J236" s="9" t="str">
+      <x:c r="J237" s="9" t="str">
         <x:v>2020-2020 Cadillac XT4; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K236" s="9" t="str">
+      <x:c r="K237" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L236" s="9" t="str"/>
-      <x:c r="M236" s="9" t="str">
+      <x:c r="L237" s="9" t="str"/>
+      <x:c r="M237" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N236" s="41" t="str">
+      <x:c r="N237" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="237" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A237" s="40" t="str"/>
-      <x:c r="B237" s="9" t="str"/>
-      <x:c r="C237" s="9" t="str"/>
-      <x:c r="D237" s="9" t="str"/>
-      <x:c r="E237" s="9" t="str"/>
-      <x:c r="F237" s="9" t="str"/>
-      <x:c r="G237" s="9" t="str"/>
-      <x:c r="H237" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I237" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J237" s="9" t="str">
+    <x:row r="238" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A238" s="40" t="str"/>
+      <x:c r="B238" s="9" t="str"/>
+      <x:c r="C238" s="9" t="str"/>
+      <x:c r="D238" s="9" t="str"/>
+      <x:c r="E238" s="9" t="str"/>
+      <x:c r="F238" s="9" t="str"/>
+      <x:c r="G238" s="9" t="str"/>
+      <x:c r="H238" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I238" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J238" s="9" t="str">
         <x:v>2020-2020 Cadillac XT4 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K237" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L237" s="9" t="str"/>
-      <x:c r="M237" s="9" t="str"/>
-      <x:c r="N237" s="41" t="str"/>
-    </x:row>
-    <x:row r="238" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A238" s="40" t="n">
+      <x:c r="K238" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L238" s="9" t="str"/>
+      <x:c r="M238" s="9" t="str"/>
+      <x:c r="N238" s="41" t="str"/>
+    </x:row>
+    <x:row r="239" ht="686.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A239" s="40" t="n">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="B238" s="9" t="str">
+      <x:c r="B239" s="9" t="str">
         <x:v>cadillac-xt4-transmission-hesitation-2019</x:v>
       </x:c>
-      <x:c r="C238" s="9" t="str">
+      <x:c r="C239" s="9" t="str">
         <x:v>2019-2019 | Cadillac | XT4 | 2.0L Turbo I4 (RPO LSY)</x:v>
       </x:c>
-      <x:c r="D238" s="9" t="str">
+      <x:c r="D239" s="9" t="str">
         <x:v>9T50 Surge or Shudder Requires a Transmission Glycol Test</x:v>
       </x:c>
-      <x:c r="E238" s="9" t="str">
+      <x:c r="E239" s="9" t="str">
         <x:v>Have a qualified transmission technician verify RPO M3H, check fluid level and condition and perform the GM glycol test. With no detected glycol, follow the bulletin drain-and-fill procedure using the specified DEXRON VI fluid; at 50 ppm or more, follow the transmission and cooler replacement path. Do not substitute a universal additive or flush kit. The exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
       </x:c>
-      <x:c r="F238" s="9" t="str">
+      <x:c r="F239" s="9" t="str">
         <x:v>Have a qualified transmission technician verify RPO M3H, check fluid level and condition and perform the GM glycol test. With no detected glycol, follow the bulletin drain-and-fill procedure using the specified DEXRON VI fluid; at 50 ppm or more, follow the transmission and cooler replacement path. Do not substitute a universal additive or flush kit. The exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
       </x:c>
-      <x:c r="G238" s="9" t="str">
+      <x:c r="G239" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H238" s="9" t="str">
+      <x:c r="H239" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 9T50 Surge or Shudder Requires a Transmission Glycol Test</x:v>
       </x:c>
-      <x:c r="I238" s="9" t="str">
+      <x:c r="I239" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J238" s="9" t="str">
+      <x:c r="J239" s="9" t="str">
         <x:v>2019-2019 Cadillac XT4; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K238" s="9" t="str">
+      <x:c r="K239" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L238" s="9" t="str"/>
-      <x:c r="M238" s="9" t="str">
+      <x:c r="L239" s="9" t="str"/>
+      <x:c r="M239" s="9" t="str">
         <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
       </x:c>
-      <x:c r="N238" s="41" t="str">
+      <x:c r="N239" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="239" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A239" s="40" t="str"/>
-      <x:c r="B239" s="9" t="str"/>
-      <x:c r="C239" s="9" t="str"/>
-      <x:c r="D239" s="9" t="str"/>
-      <x:c r="E239" s="9" t="str"/>
-      <x:c r="F239" s="9" t="str"/>
-      <x:c r="G239" s="9" t="str"/>
-      <x:c r="H239" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I239" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J239" s="9" t="str">
+    <x:row r="240" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A240" s="40" t="str"/>
+      <x:c r="B240" s="9" t="str"/>
+      <x:c r="C240" s="9" t="str"/>
+      <x:c r="D240" s="9" t="str"/>
+      <x:c r="E240" s="9" t="str"/>
+      <x:c r="F240" s="9" t="str"/>
+      <x:c r="G240" s="9" t="str"/>
+      <x:c r="H240" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I240" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J240" s="9" t="str">
         <x:v>2019-2019 Cadillac XT4 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K239" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L239" s="9" t="str"/>
-      <x:c r="M239" s="9" t="str"/>
-      <x:c r="N239" s="41" t="str"/>
-    </x:row>
-    <x:row r="240" ht="554.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A240" s="40" t="n">
+      <x:c r="K240" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L240" s="9" t="str"/>
+      <x:c r="M240" s="9" t="str"/>
+      <x:c r="N240" s="41" t="str"/>
+    </x:row>
+    <x:row r="241" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A241" s="40" t="n">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="B240" s="9" t="str">
+      <x:c r="B241" s="9" t="str">
         <x:v>cadillac-xt4-turbo-issues-2019</x:v>
       </x:c>
-      <x:c r="C240" s="9" t="str">
+      <x:c r="C241" s="9" t="str">
         <x:v>2019-2025 | Cadillac | XT4 | 2.0T LSY</x:v>
       </x:c>
-      <x:c r="D240" s="9" t="str">
+      <x:c r="D241" s="9" t="str">
         <x:v>2.0T LSY Engine - PCV and Turbo Coolant Line Issues</x:v>
       </x:c>
-      <x:c r="E240" s="9" t="str">
+      <x:c r="E241" s="9" t="str">
         <x:v>Inspect turbo coolant lines and connections for leaks - replace lines if seeping. PCV system is integrated into valve cover - replace valve cover assembly if PCV fails. GM has released updated coolant line designs for some affected vehicles. Regular maintenance with full synthetic oil at 5,000-mile intervals is important for turbo health.</x:v>
       </x:c>
-      <x:c r="F240" s="9" t="str">
+      <x:c r="F241" s="9" t="str">
         <x:v>Inspect turbo coolant lines and connections for leaks - replace lines if seeping. PCV system is integrated into valve cover - replace valve cover assembly if PCV fails. GM has released updated coolant line designs for some affected vehicles. Regular maintenance with full synthetic oil at 5,000-mile intervals is important for turbo health.</x:v>
       </x:c>
-      <x:c r="G240" s="9" t="str">
+      <x:c r="G241" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H240" s="9" t="str">
+      <x:c r="H241" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 2.0T LSY Engine - PCV and Turbo Coolant Line Issues</x:v>
       </x:c>
-      <x:c r="I240" s="9" t="str">
+      <x:c r="I241" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J240" s="9" t="str">
+      <x:c r="J241" s="9" t="str">
         <x:v>2019-2025 Cadillac XT4; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K240" s="9" t="str">
+      <x:c r="K241" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L240" s="9" t="str"/>
-      <x:c r="M240" s="9" t="str">
+      <x:c r="L241" s="9" t="str"/>
+      <x:c r="M241" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N240" s="41" t="str">
+      <x:c r="N241" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="241" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A241" s="40" t="str"/>
-      <x:c r="B241" s="9" t="str"/>
-      <x:c r="C241" s="9" t="str"/>
-      <x:c r="D241" s="9" t="str"/>
-      <x:c r="E241" s="9" t="str"/>
-      <x:c r="F241" s="9" t="str"/>
-      <x:c r="G241" s="9" t="str"/>
-      <x:c r="H241" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I241" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J241" s="9" t="str">
+    <x:row r="242" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A242" s="40" t="str"/>
+      <x:c r="B242" s="9" t="str"/>
+      <x:c r="C242" s="9" t="str"/>
+      <x:c r="D242" s="9" t="str"/>
+      <x:c r="E242" s="9" t="str"/>
+      <x:c r="F242" s="9" t="str"/>
+      <x:c r="G242" s="9" t="str"/>
+      <x:c r="H242" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I242" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J242" s="9" t="str">
         <x:v>2019-2025 Cadillac XT4 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K241" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L241" s="9" t="str"/>
-      <x:c r="M241" s="9" t="str"/>
-      <x:c r="N241" s="41" t="str"/>
-    </x:row>
-    <x:row r="242" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A242" s="40" t="n">
+      <x:c r="K242" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L242" s="9" t="str"/>
+      <x:c r="M242" s="9" t="str"/>
+      <x:c r="N242" s="41" t="str"/>
+    </x:row>
+    <x:row r="243" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A243" s="40" t="n">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="B242" s="9" t="str">
+      <x:c r="B243" s="9" t="str">
         <x:v>cadillac-xt4-turbo-oil-consumption-2019</x:v>
       </x:c>
-      <x:c r="C242" s="9" t="str">
+      <x:c r="C243" s="9" t="str">
         <x:v>2019-2025 | Cadillac | XT4 | 2.0L Turbo</x:v>
       </x:c>
-      <x:c r="D242" s="9" t="str">
+      <x:c r="D243" s="9" t="str">
         <x:v>2.0L Turbo Excessive Oil Consumption</x:v>
       </x:c>
-      <x:c r="E242" s="9" t="str">
+      <x:c r="E243" s="9" t="str">
         <x:v>Monitor oil level between changes and top off as needed. Use only Dexos1 Gen3 certified 0W-20 synthetic oil. Have the PCV system inspected for proper function. If consumption exceeds 1 quart per 2,000 miles, request a GM oil consumption test from the dealer. Document consumption for warranty purposes.</x:v>
       </x:c>
-      <x:c r="F242" s="9" t="str">
+      <x:c r="F243" s="9" t="str">
         <x:v>Monitor oil level between changes and top off as needed. Use only Dexos1 Gen3 certified 0W-20 synthetic oil. Have the PCV system inspected for proper function. If consumption exceeds 1 quart per 2,000 miles, request a GM oil consumption test from the dealer. Document consumption for warranty purposes.</x:v>
       </x:c>
-      <x:c r="G242" s="9" t="str">
+      <x:c r="G243" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H242" s="9" t="str">
+      <x:c r="H243" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 2.0L Turbo Excessive Oil Consumption</x:v>
       </x:c>
-      <x:c r="I242" s="9" t="str">
+      <x:c r="I243" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J242" s="9" t="str">
+      <x:c r="J243" s="9" t="str">
         <x:v>2019-2025 Cadillac XT4; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K242" s="9" t="str">
+      <x:c r="K243" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L242" s="9" t="str"/>
-      <x:c r="M242" s="9" t="str">
+      <x:c r="L243" s="9" t="str"/>
+      <x:c r="M243" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N242" s="41" t="str">
+      <x:c r="N243" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="243" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A243" s="40" t="str"/>
-      <x:c r="B243" s="9" t="str"/>
-      <x:c r="C243" s="9" t="str"/>
-      <x:c r="D243" s="9" t="str"/>
-      <x:c r="E243" s="9" t="str"/>
-      <x:c r="F243" s="9" t="str"/>
-      <x:c r="G243" s="9" t="str"/>
-      <x:c r="H243" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I243" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J243" s="9" t="str">
+    <x:row r="244" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A244" s="40" t="str"/>
+      <x:c r="B244" s="9" t="str"/>
+      <x:c r="C244" s="9" t="str"/>
+      <x:c r="D244" s="9" t="str"/>
+      <x:c r="E244" s="9" t="str"/>
+      <x:c r="F244" s="9" t="str"/>
+      <x:c r="G244" s="9" t="str"/>
+      <x:c r="H244" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I244" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J244" s="9" t="str">
         <x:v>2019-2025 Cadillac XT4 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K243" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L243" s="9" t="str"/>
-      <x:c r="M243" s="9" t="str"/>
-      <x:c r="N243" s="41" t="str"/>
-    </x:row>
-    <x:row r="244" ht="660" hidden="0" customHeight="1">
-      <x:c r="A244" s="40" t="n">
+      <x:c r="K244" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L244" s="9" t="str"/>
+      <x:c r="M244" s="9" t="str"/>
+      <x:c r="N244" s="41" t="str"/>
+    </x:row>
+    <x:row r="245" ht="660" hidden="0" customHeight="1">
+      <x:c r="A245" s="40" t="n">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="B244" s="9" t="str">
+      <x:c r="B245" s="9" t="str">
         <x:v>cadillac-xt5-9speed-shudder-2017</x:v>
       </x:c>
-      <x:c r="C244" s="9" t="str">
+      <x:c r="C245" s="9" t="str">
         <x:v>2020-2021 | Cadillac | XT5</x:v>
       </x:c>
-      <x:c r="D244" s="9" t="str">
+      <x:c r="D245" s="9" t="str">
         <x:v>Low-Speed TCC Shudder Must Be Confirmed Before a Fluid Drain and Fill</x:v>
       </x:c>
-      <x:c r="E244" s="9" t="str">
+      <x:c r="E245" s="9" t="str">
         <x:v>Have a qualified transmission technician verify RPO M3G or M3W and confirm the event is TCC shudder using slip-speed data or the commanded-on test. If the bulletin criteria are met, follow the GM DEXRON VI drain-and-fill procedure and drive at least 200 miles before judging the repair. Do not use a universal additive or flush kit. The exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
       </x:c>
-      <x:c r="F244" s="9" t="str">
+      <x:c r="F245" s="9" t="str">
         <x:v>Have a qualified transmission technician verify RPO M3G or M3W and confirm the event is TCC shudder using slip-speed data or the commanded-on test. If the bulletin criteria are met, follow the GM DEXRON VI drain-and-fill procedure and drive at least 200 miles before judging the repair. Do not use a universal additive or flush kit. The exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
       </x:c>
-      <x:c r="G244" s="9" t="str">
+      <x:c r="G245" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H244" s="9" t="str">
+      <x:c r="H245" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Low-Speed TCC Shudder Must Be Confirmed Before a Fluid Drain and Fill</x:v>
       </x:c>
-      <x:c r="I244" s="9" t="str">
+      <x:c r="I245" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J244" s="9" t="str">
+      <x:c r="J245" s="9" t="str">
         <x:v>2020-2021 Cadillac XT5; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K244" s="9" t="str">
+      <x:c r="K245" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L244" s="9" t="str"/>
-      <x:c r="M244" s="9" t="str">
+      <x:c r="L245" s="9" t="str"/>
+      <x:c r="M245" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N244" s="41" t="str">
+      <x:c r="N245" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="245" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A245" s="40" t="str"/>
-      <x:c r="B245" s="9" t="str"/>
-      <x:c r="C245" s="9" t="str"/>
-      <x:c r="D245" s="9" t="str"/>
-      <x:c r="E245" s="9" t="str"/>
-      <x:c r="F245" s="9" t="str"/>
-      <x:c r="G245" s="9" t="str"/>
-      <x:c r="H245" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I245" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J245" s="9" t="str">
+    <x:row r="246" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A246" s="40" t="str"/>
+      <x:c r="B246" s="9" t="str"/>
+      <x:c r="C246" s="9" t="str"/>
+      <x:c r="D246" s="9" t="str"/>
+      <x:c r="E246" s="9" t="str"/>
+      <x:c r="F246" s="9" t="str"/>
+      <x:c r="G246" s="9" t="str"/>
+      <x:c r="H246" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I246" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J246" s="9" t="str">
         <x:v>2020-2021 Cadillac XT5 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K245" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L245" s="9" t="str"/>
-      <x:c r="M245" s="9" t="str"/>
-      <x:c r="N245" s="41" t="str"/>
-    </x:row>
-    <x:row r="246" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A246" s="40" t="n">
+      <x:c r="K246" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L246" s="9" t="str"/>
+      <x:c r="M246" s="9" t="str"/>
+      <x:c r="N246" s="41" t="str"/>
+    </x:row>
+    <x:row r="247" ht="501.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A247" s="40" t="n">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="B246" s="9" t="str">
+      <x:c r="B247" s="9" t="str">
         <x:v>cadillac-xt5-brake-vibration-2017</x:v>
       </x:c>
-      <x:c r="C246" s="9" t="str">
+      <x:c r="C247" s="9" t="str">
         <x:v>2017-2025 | Cadillac | XT5</x:v>
       </x:c>
-      <x:c r="D246" s="9" t="str">
+      <x:c r="D247" s="9" t="str">
         <x:v>Front Brake Rotor Warping and Pedal Pulsation</x:v>
       </x:c>
-      <x:c r="E246" s="9" t="str">
+      <x:c r="E247" s="9" t="str">
         <x:v>Replace the front brake rotors with quality aftermarket rotors that meet or exceed OEM thickness. Bed in the new rotors and pads properly with a series of moderate stops. Avoid hard braking followed by holding the brake (which creates hot spots). Upgrading to slotted rotors can help manage heat better.</x:v>
       </x:c>
-      <x:c r="F246" s="9" t="str">
+      <x:c r="F247" s="9" t="str">
         <x:v>Replace the front brake rotors with quality aftermarket rotors that meet or exceed OEM thickness. Bed in the new rotors and pads properly with a series of moderate stops. Avoid hard braking followed by holding the brake (which creates hot spots). Upgrading to slotted rotors can help manage heat better.</x:v>
       </x:c>
-      <x:c r="G246" s="9" t="str">
+      <x:c r="G247" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H246" s="9" t="str">
+      <x:c r="H247" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Front Brake Rotor Warping and Pedal Pulsation</x:v>
       </x:c>
-      <x:c r="I246" s="9" t="str">
+      <x:c r="I247" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J246" s="9" t="str">
+      <x:c r="J247" s="9" t="str">
         <x:v>2017-2025 Cadillac XT5; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K246" s="9" t="str">
+      <x:c r="K247" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L246" s="9" t="str"/>
-      <x:c r="M246" s="9" t="str">
+      <x:c r="L247" s="9" t="str"/>
+      <x:c r="M247" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N246" s="41" t="str">
+      <x:c r="N247" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="247" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A247" s="40" t="str"/>
-      <x:c r="B247" s="9" t="str"/>
-      <x:c r="C247" s="9" t="str"/>
-      <x:c r="D247" s="9" t="str"/>
-      <x:c r="E247" s="9" t="str"/>
-      <x:c r="F247" s="9" t="str"/>
-      <x:c r="G247" s="9" t="str"/>
-      <x:c r="H247" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I247" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J247" s="9" t="str">
+    <x:row r="248" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A248" s="40" t="str"/>
+      <x:c r="B248" s="9" t="str"/>
+      <x:c r="C248" s="9" t="str"/>
+      <x:c r="D248" s="9" t="str"/>
+      <x:c r="E248" s="9" t="str"/>
+      <x:c r="F248" s="9" t="str"/>
+      <x:c r="G248" s="9" t="str"/>
+      <x:c r="H248" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I248" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J248" s="9" t="str">
         <x:v>2017-2025 Cadillac XT5 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K247" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L247" s="9" t="str"/>
-      <x:c r="M247" s="9" t="str"/>
-      <x:c r="N247" s="41" t="str"/>
-    </x:row>
-    <x:row r="248" ht="620.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A248" s="40" t="n">
+      <x:c r="K248" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L248" s="9" t="str"/>
+      <x:c r="M248" s="9" t="str"/>
+      <x:c r="N248" s="41" t="str"/>
+    </x:row>
+    <x:row r="249" ht="620.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A249" s="40" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="B248" s="9" t="str">
+      <x:c r="B249" s="9" t="str">
         <x:v>cadillac-xt5-electronic-gear-selector-park-switch-fault-persistent-shift</x:v>
       </x:c>
-      <x:c r="C248" s="9" t="str">
+      <x:c r="C249" s="9" t="str">
         <x:v>2017-2019 | Cadillac | XT5 | Luxury, Premium Luxury, Platinum | 3.6L V6 (LGX)</x:v>
       </x:c>
-      <x:c r="D248" s="9" t="str">
+      <x:c r="D249" s="9" t="str">
         <x:v>Electronic Gear Selector Park-Switch Fault - Persistent 'Shift to Park' Message / Won't Power Down (TSB 19-NA-206)</x:v>
       </x:c>
-      <x:c r="E248" s="9" t="str">
+      <x:c r="E249" s="9" t="str">
         <x:v>Per GM TSB 19-NA-206 the repair is often installing an in-line jumper harness (P/N 84733196) at the shifter connector; where that does not resolve it, the shifter assembly is replaced. Replacement requires removing the center console trim and generally needs no special programming. Pressing the Park button squarely in the center can be a temporary workaround for the dual-sensor design.</x:v>
       </x:c>
-      <x:c r="F248" s="9" t="str">
+      <x:c r="F249" s="9" t="str">
         <x:v>Per GM TSB 19-NA-206 the repair is often installing an in-line jumper harness (P/N 84733196) at the shifter connector; where that does not resolve it, the shifter assembly is replaced. Replacement requires removing the center console trim and generally needs no special programming. Pressing the Park button squarely in the center can be a temporary workaround for the dual-sensor design.</x:v>
       </x:c>
-      <x:c r="G248" s="9" t="str">
+      <x:c r="G249" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H248" s="9" t="str">
+      <x:c r="H249" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Electronic Gear Selector Park-Switch Fault - Persistent 'Shift to Park' Message / Won't Power Down</x:v>
       </x:c>
-      <x:c r="I248" s="9" t="str">
+      <x:c r="I249" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J248" s="9" t="str">
+      <x:c r="J249" s="9" t="str">
         <x:v>2017-2019 Cadillac XT5; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K248" s="9" t="str">
+      <x:c r="K249" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L248" s="9" t="str"/>
-      <x:c r="M248" s="9" t="str">
+      <x:c r="L249" s="9" t="str"/>
+      <x:c r="M249" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N248" s="41" t="str">
+      <x:c r="N249" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="249" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A249" s="40" t="str"/>
-      <x:c r="B249" s="9" t="str"/>
-      <x:c r="C249" s="9" t="str"/>
-      <x:c r="D249" s="9" t="str"/>
-      <x:c r="E249" s="9" t="str"/>
-      <x:c r="F249" s="9" t="str"/>
-      <x:c r="G249" s="9" t="str"/>
-      <x:c r="H249" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I249" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J249" s="9" t="str">
+    <x:row r="250" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A250" s="40" t="str"/>
+      <x:c r="B250" s="9" t="str"/>
+      <x:c r="C250" s="9" t="str"/>
+      <x:c r="D250" s="9" t="str"/>
+      <x:c r="E250" s="9" t="str"/>
+      <x:c r="F250" s="9" t="str"/>
+      <x:c r="G250" s="9" t="str"/>
+      <x:c r="H250" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I250" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J250" s="9" t="str">
         <x:v>2017-2019 Cadillac XT5 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K249" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L249" s="9" t="str"/>
-      <x:c r="M249" s="9" t="str"/>
-      <x:c r="N249" s="41" t="str"/>
-    </x:row>
-    <x:row r="250" ht="422.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A250" s="40" t="n">
+      <x:c r="K250" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L250" s="9" t="str"/>
+      <x:c r="M250" s="9" t="str"/>
+      <x:c r="N250" s="41" t="str"/>
+    </x:row>
+    <x:row r="251" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A251" s="40" t="n">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B250" s="9" t="str">
+      <x:c r="B251" s="9" t="str">
         <x:v>cadillac-xt5-fuel-pump-jet-nozzle-manufacturing-defect-causing-sudden-eng</x:v>
       </x:c>
-      <x:c r="C250" s="9" t="str">
+      <x:c r="C251" s="9" t="str">
         <x:v>2020-2020 | Cadillac | XT5</x:v>
       </x:c>
-      <x:c r="D250" s="9" t="str">
+      <x:c r="D251" s="9" t="str">
         <x:v>Recall 20V639: AWD Fuel-Pump Mixing-Tube Burr May Cause a Stall</x:v>
       </x:c>
-      <x:c r="E250" s="9" t="str">
+      <x:c r="E251" s="9" t="str">
         <x:v>Check the VIN for an open NHTSA 20V639 / GM N202314760 campaign. If open, arrange the dealer fuel-pump module replacement at no charge. Do not buy the recall pump from a commerce link; GM directs use of the VIN and electronic parts catalog for the exact module.</x:v>
       </x:c>
-      <x:c r="F250" s="9" t="str">
+      <x:c r="F251" s="9" t="str">
         <x:v>Check the VIN for an open NHTSA 20V639 / GM N202314760 campaign. If open, arrange the dealer fuel-pump module replacement at no charge. Do not buy the recall pump from a commerce link; GM directs use of the VIN and electronic parts catalog for the exact module.</x:v>
       </x:c>
-      <x:c r="G250" s="9" t="str">
+      <x:c r="G251" s="9" t="str">
         <x:v>RECALL ROUTES ONLY</x:v>
       </x:c>
-      <x:c r="H250" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I250" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J250" s="9" t="str">
+      <x:c r="H251" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I251" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J251" s="9" t="str">
         <x:v>2020-2020 Cadillac XT5 VIN/campaign completion and free remedy</x:v>
       </x:c>
-      <x:c r="K250" s="9" t="str">
+      <x:c r="K251" s="9" t="str">
         <x:v>authorized recall service</x:v>
       </x:c>
-      <x:c r="L250" s="9" t="str"/>
-      <x:c r="M250" s="9" t="str">
+      <x:c r="L251" s="9" t="str"/>
+      <x:c r="M251" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N250" s="41" t="str">
+      <x:c r="N251" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="251" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A251" s="40" t="str"/>
-      <x:c r="B251" s="9" t="str"/>
-      <x:c r="C251" s="9" t="str"/>
-      <x:c r="D251" s="9" t="str"/>
-      <x:c r="E251" s="9" t="str"/>
-      <x:c r="F251" s="9" t="str"/>
-      <x:c r="G251" s="9" t="str"/>
-      <x:c r="H251" s="9" t="str">
+    <x:row r="252" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A252" s="40" t="str"/>
+      <x:c r="B252" s="9" t="str"/>
+      <x:c r="C252" s="9" t="str"/>
+      <x:c r="D252" s="9" t="str"/>
+      <x:c r="E252" s="9" t="str"/>
+      <x:c r="F252" s="9" t="str"/>
+      <x:c r="G252" s="9" t="str"/>
+      <x:c r="H252" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I251" s="9" t="str">
+      <x:c r="I252" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J251" s="9" t="str">
+      <x:c r="J252" s="9" t="str">
         <x:v>2020-2020 Cadillac XT5 VIN history</x:v>
       </x:c>
-      <x:c r="K251" s="9" t="str">
+      <x:c r="K252" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L251" s="9" t="str"/>
-      <x:c r="M251" s="9" t="str"/>
-      <x:c r="N251" s="41" t="str"/>
-    </x:row>
-    <x:row r="252" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A252" s="40" t="n">
+      <x:c r="L252" s="9" t="str"/>
+      <x:c r="M252" s="9" t="str"/>
+      <x:c r="N252" s="41" t="str"/>
+    </x:row>
+    <x:row r="253" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A253" s="40" t="n">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B252" s="9" t="str">
+      <x:c r="B253" s="9" t="str">
         <x:v>cadillac-xt5-liftgate-strut-2017</x:v>
       </x:c>
-      <x:c r="C252" s="9" t="str">
+      <x:c r="C253" s="9" t="str">
         <x:v>2017-2025 | Cadillac | XT5</x:v>
       </x:c>
-      <x:c r="D252" s="9" t="str">
+      <x:c r="D253" s="9" t="str">
         <x:v>Power Liftgate Strut Failure and Erratic Operation</x:v>
       </x:c>
-      <x:c r="E252" s="9" t="str">
+      <x:c r="E253" s="9" t="str">
         <x:v>Replace both power liftgate struts as a pair. Use OEM struts for proper fit with the power liftgate system. After replacement, the liftgate height setting may need to be reprogrammed. If the liftgate motor is also weak, it should be replaced at the same time. Lubricating the hinge points helps reduce strain on the struts.</x:v>
       </x:c>
-      <x:c r="F252" s="9" t="str">
+      <x:c r="F253" s="9" t="str">
         <x:v>Replace both power liftgate struts as a pair. Use OEM struts for proper fit with the power liftgate system. After replacement, the liftgate height setting may need to be reprogrammed. If the liftgate motor is also weak, it should be replaced at the same time. Lubricating the hinge points helps reduce strain on the struts.</x:v>
       </x:c>
-      <x:c r="G252" s="9" t="str">
+      <x:c r="G253" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H252" s="9" t="str">
+      <x:c r="H253" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Power Liftgate Strut Failure and Erratic Operation</x:v>
       </x:c>
-      <x:c r="I252" s="9" t="str">
+      <x:c r="I253" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J252" s="9" t="str">
+      <x:c r="J253" s="9" t="str">
         <x:v>2017-2025 Cadillac XT5; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K252" s="9" t="str">
+      <x:c r="K253" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L252" s="9" t="str"/>
-      <x:c r="M252" s="9" t="str">
+      <x:c r="L253" s="9" t="str"/>
+      <x:c r="M253" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N252" s="41" t="str">
+      <x:c r="N253" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="253" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A253" s="40" t="str"/>
-      <x:c r="B253" s="9" t="str"/>
-      <x:c r="C253" s="9" t="str"/>
-      <x:c r="D253" s="9" t="str"/>
-      <x:c r="E253" s="9" t="str"/>
-      <x:c r="F253" s="9" t="str"/>
-      <x:c r="G253" s="9" t="str"/>
-      <x:c r="H253" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I253" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J253" s="9" t="str">
+    <x:row r="254" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A254" s="40" t="str"/>
+      <x:c r="B254" s="9" t="str"/>
+      <x:c r="C254" s="9" t="str"/>
+      <x:c r="D254" s="9" t="str"/>
+      <x:c r="E254" s="9" t="str"/>
+      <x:c r="F254" s="9" t="str"/>
+      <x:c r="G254" s="9" t="str"/>
+      <x:c r="H254" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I254" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J254" s="9" t="str">
         <x:v>2017-2025 Cadillac XT5 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K253" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L253" s="9" t="str"/>
-      <x:c r="M253" s="9" t="str"/>
-      <x:c r="N253" s="41" t="str"/>
-    </x:row>
-    <x:row r="254" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A254" s="40" t="n">
+      <x:c r="K254" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L254" s="9" t="str"/>
+      <x:c r="M254" s="9" t="str"/>
+      <x:c r="N254" s="41" t="str"/>
+    </x:row>
+    <x:row r="255" ht="475.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A255" s="40" t="n">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="B254" s="9" t="str">
+      <x:c r="B255" s="9" t="str">
         <x:v>cadillac-xt5-timing-chain-2017</x:v>
       </x:c>
-      <x:c r="C254" s="9" t="str">
+      <x:c r="C255" s="9" t="str">
         <x:v>2017-2025 | Cadillac | XT5 | 3.6L V6 LGX, 3.6L V6 LFX, 2.0T LSY</x:v>
       </x:c>
-      <x:c r="D254" s="9" t="str">
+      <x:c r="D255" s="9" t="str">
         <x:v>3.6L V6 Timing Chain Issues (XT5 V6 models)</x:v>
       </x:c>
-      <x:c r="E254" s="9" t="str">
+      <x:c r="E255" s="9" t="str">
         <x:v>Same timing chain replacement as SRX/CTS 3.6L. Cloyes 9-0753S kit, replace water pump simultaneously. The LGX timing chain typically lasts longer than the LFX, so preventive replacement at 100,000+ miles is recommended rather than the 80,000-mile interval for earlier engines.</x:v>
       </x:c>
-      <x:c r="F254" s="9" t="str">
+      <x:c r="F255" s="9" t="str">
         <x:v>Same timing chain replacement as SRX/CTS 3.6L. Cloyes 9-0753S kit, replace water pump simultaneously. The LGX timing chain typically lasts longer than the LFX, so preventive replacement at 100,000+ miles is recommended rather than the 80,000-mile interval for earlier engines.</x:v>
       </x:c>
-      <x:c r="G254" s="9" t="str">
+      <x:c r="G255" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H254" s="9" t="str">
+      <x:c r="H255" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 3.6L V6 Timing Chain Issues</x:v>
       </x:c>
-      <x:c r="I254" s="9" t="str">
+      <x:c r="I255" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J254" s="9" t="str">
+      <x:c r="J255" s="9" t="str">
         <x:v>2017-2025 Cadillac XT5; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K254" s="9" t="str">
+      <x:c r="K255" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L254" s="9" t="str"/>
-      <x:c r="M254" s="9" t="str">
+      <x:c r="L255" s="9" t="str"/>
+      <x:c r="M255" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N254" s="41" t="str">
+      <x:c r="N255" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="255" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A255" s="40" t="str"/>
-      <x:c r="B255" s="9" t="str"/>
-      <x:c r="C255" s="9" t="str"/>
-      <x:c r="D255" s="9" t="str"/>
-      <x:c r="E255" s="9" t="str"/>
-      <x:c r="F255" s="9" t="str"/>
-      <x:c r="G255" s="9" t="str"/>
-      <x:c r="H255" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I255" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J255" s="9" t="str">
+    <x:row r="256" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A256" s="40" t="str"/>
+      <x:c r="B256" s="9" t="str"/>
+      <x:c r="C256" s="9" t="str"/>
+      <x:c r="D256" s="9" t="str"/>
+      <x:c r="E256" s="9" t="str"/>
+      <x:c r="F256" s="9" t="str"/>
+      <x:c r="G256" s="9" t="str"/>
+      <x:c r="H256" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I256" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J256" s="9" t="str">
         <x:v>2017-2025 Cadillac XT5 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K255" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L255" s="9" t="str"/>
-      <x:c r="M255" s="9" t="str"/>
-      <x:c r="N255" s="41" t="str"/>
-    </x:row>
-    <x:row r="256" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A256" s="40" t="n">
+      <x:c r="K256" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L256" s="9" t="str"/>
+      <x:c r="M256" s="9" t="str"/>
+      <x:c r="N256" s="41" t="str"/>
+    </x:row>
+    <x:row r="257" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A257" s="40" t="n">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="B256" s="9" t="str">
+      <x:c r="B257" s="9" t="str">
         <x:v>cadillac-xt5-transmission-shudder-2017</x:v>
       </x:c>
-      <x:c r="C256" s="9" t="str">
+      <x:c r="C257" s="9" t="str">
         <x:v>2017-2025 | Cadillac | XT5</x:v>
       </x:c>
-      <x:c r="D256" s="9" t="str">
+      <x:c r="D257" s="9" t="str">
         <x:v>8-Speed / 9-Speed Transmission Shudder and Harsh Shifting</x:v>
       </x:c>
-      <x:c r="E256" s="9" t="str">
+      <x:c r="E257" s="9" t="str">
         <x:v>First step is a TCM software update at the dealer - multiple calibrations have been released. For 8-speed shudder, a fluid exchange with Mobil 1 LV ATF HP may resolve it. The 9-speed typically responds well to software updates. Persistent issues may require torque converter replacement (8-speed) or valve body replacement (9-speed).</x:v>
       </x:c>
-      <x:c r="F256" s="9" t="str">
+      <x:c r="F257" s="9" t="str">
         <x:v>First step is a TCM software update at the dealer - multiple calibrations have been released. For 8-speed shudder, a fluid exchange with Mobil 1 LV ATF HP may resolve it. The 9-speed typically responds well to software updates. Persistent issues may require torque converter replacement (8-speed) or valve body replacement (9-speed).</x:v>
       </x:c>
-      <x:c r="G256" s="9" t="str">
+      <x:c r="G257" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H256" s="9" t="str">
+      <x:c r="H257" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 8-Speed / 9-Speed Transmission Shudder and Harsh Shifting</x:v>
       </x:c>
-      <x:c r="I256" s="9" t="str">
+      <x:c r="I257" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J256" s="9" t="str">
+      <x:c r="J257" s="9" t="str">
         <x:v>2017-2025 Cadillac XT5; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K256" s="9" t="str">
+      <x:c r="K257" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L256" s="9" t="str"/>
-      <x:c r="M256" s="9" t="str">
+      <x:c r="L257" s="9" t="str"/>
+      <x:c r="M257" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N256" s="41" t="str">
+      <x:c r="N257" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="257" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A257" s="40" t="str"/>
-      <x:c r="B257" s="9" t="str"/>
-      <x:c r="C257" s="9" t="str"/>
-      <x:c r="D257" s="9" t="str"/>
-      <x:c r="E257" s="9" t="str"/>
-      <x:c r="F257" s="9" t="str"/>
-      <x:c r="G257" s="9" t="str"/>
-      <x:c r="H257" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I257" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J257" s="9" t="str">
+    <x:row r="258" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A258" s="40" t="str"/>
+      <x:c r="B258" s="9" t="str"/>
+      <x:c r="C258" s="9" t="str"/>
+      <x:c r="D258" s="9" t="str"/>
+      <x:c r="E258" s="9" t="str"/>
+      <x:c r="F258" s="9" t="str"/>
+      <x:c r="G258" s="9" t="str"/>
+      <x:c r="H258" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I258" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J258" s="9" t="str">
         <x:v>2017-2025 Cadillac XT5 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K257" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L257" s="9" t="str"/>
-      <x:c r="M257" s="9" t="str"/>
-      <x:c r="N257" s="41" t="str"/>
-    </x:row>
-    <x:row r="258" ht="660" hidden="0" customHeight="1">
-      <x:c r="A258" s="40" t="n">
+      <x:c r="K258" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L258" s="9" t="str"/>
+      <x:c r="M258" s="9" t="str"/>
+      <x:c r="N258" s="41" t="str"/>
+    </x:row>
+    <x:row r="259" ht="660" hidden="0" customHeight="1">
+      <x:c r="A259" s="40" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B258" s="9" t="str">
+      <x:c r="B259" s="9" t="str">
         <x:v>cadillac-xt6-9speed-transmission-2020</x:v>
       </x:c>
-      <x:c r="C258" s="9" t="str">
+      <x:c r="C259" s="9" t="str">
         <x:v>2020-2021 | Cadillac | XT6</x:v>
       </x:c>
-      <x:c r="D258" s="9" t="str">
+      <x:c r="D259" s="9" t="str">
         <x:v>Low-Speed TCC Shudder Must Be Confirmed Before a Fluid Drain and Fill</x:v>
       </x:c>
-      <x:c r="E258" s="9" t="str">
+      <x:c r="E259" s="9" t="str">
         <x:v>Have a qualified transmission technician verify RPO M3G or M3W and confirm the event is TCC shudder using slip-speed data or the commanded-on test. If the bulletin criteria are met, follow the GM DEXRON VI drain-and-fill procedure and drive at least 200 miles before judging the repair. Do not use a universal additive or flush kit. The exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
       </x:c>
-      <x:c r="F258" s="9" t="str">
+      <x:c r="F259" s="9" t="str">
         <x:v>Have a qualified transmission technician verify RPO M3G or M3W and confirm the event is TCC shudder using slip-speed data or the commanded-on test. If the bulletin criteria are met, follow the GM DEXRON VI drain-and-fill procedure and drive at least 200 miles before judging the repair. Do not use a universal additive or flush kit. The exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
       </x:c>
-      <x:c r="G258" s="9" t="str">
+      <x:c r="G259" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H258" s="9" t="str">
+      <x:c r="H259" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Low-Speed TCC Shudder Must Be Confirmed Before a Fluid Drain and Fill</x:v>
       </x:c>
-      <x:c r="I258" s="9" t="str">
+      <x:c r="I259" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J258" s="9" t="str">
+      <x:c r="J259" s="9" t="str">
         <x:v>2020-2021 Cadillac XT6; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K258" s="9" t="str">
+      <x:c r="K259" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L258" s="9" t="str"/>
-      <x:c r="M258" s="9" t="str">
+      <x:c r="L259" s="9" t="str"/>
+      <x:c r="M259" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N258" s="41" t="str">
+      <x:c r="N259" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="259" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A259" s="40" t="str"/>
-      <x:c r="B259" s="9" t="str"/>
-      <x:c r="C259" s="9" t="str"/>
-      <x:c r="D259" s="9" t="str"/>
-      <x:c r="E259" s="9" t="str"/>
-      <x:c r="F259" s="9" t="str"/>
-      <x:c r="G259" s="9" t="str"/>
-      <x:c r="H259" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I259" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J259" s="9" t="str">
+    <x:row r="260" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A260" s="40" t="str"/>
+      <x:c r="B260" s="9" t="str"/>
+      <x:c r="C260" s="9" t="str"/>
+      <x:c r="D260" s="9" t="str"/>
+      <x:c r="E260" s="9" t="str"/>
+      <x:c r="F260" s="9" t="str"/>
+      <x:c r="G260" s="9" t="str"/>
+      <x:c r="H260" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I260" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J260" s="9" t="str">
         <x:v>2020-2021 Cadillac XT6 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K259" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L259" s="9" t="str"/>
-      <x:c r="M259" s="9" t="str"/>
-      <x:c r="N259" s="41" t="str"/>
-    </x:row>
-    <x:row r="260" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A260" s="40" t="n">
+      <x:c r="K260" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L260" s="9" t="str"/>
+      <x:c r="M260" s="9" t="str"/>
+      <x:c r="N260" s="41" t="str"/>
+    </x:row>
+    <x:row r="261" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A261" s="40" t="n">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B260" s="9" t="str">
+      <x:c r="B261" s="9" t="str">
         <x:v>cadillac-xt6-auto-stop-2020</x:v>
       </x:c>
-      <x:c r="C260" s="9" t="str">
+      <x:c r="C261" s="9" t="str">
         <x:v>2020-2025 | Cadillac | XT6</x:v>
       </x:c>
-      <x:c r="D260" s="9" t="str">
+      <x:c r="D261" s="9" t="str">
         <x:v>Auto Start-Stop Harshness and Battery Issues</x:v>
       </x:c>
-      <x:c r="E260" s="9" t="str">
+      <x:c r="E261" s="9" t="str">
         <x:v>Replace the AGM battery with a fresh ACDelco unit if the system is not functioning properly. Have the battery monitor sensor reset after replacement. GM has released recalibrations to improve start-stop smoothness. Aftermarket start-stop eliminator modules are available for owners who want to permanently disable the feature.</x:v>
       </x:c>
-      <x:c r="F260" s="9" t="str">
+      <x:c r="F261" s="9" t="str">
         <x:v>Replace the AGM battery with a fresh ACDelco unit if the system is not functioning properly. Have the battery monitor sensor reset after replacement. GM has released recalibrations to improve start-stop smoothness. Aftermarket start-stop eliminator modules are available for owners who want to permanently disable the feature.</x:v>
       </x:c>
-      <x:c r="G260" s="9" t="str">
+      <x:c r="G261" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H260" s="9" t="str">
+      <x:c r="H261" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Auto Start-Stop Harshness and Battery Issues</x:v>
       </x:c>
-      <x:c r="I260" s="9" t="str">
+      <x:c r="I261" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J260" s="9" t="str">
+      <x:c r="J261" s="9" t="str">
         <x:v>2020-2025 Cadillac XT6; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K260" s="9" t="str">
+      <x:c r="K261" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L260" s="9" t="str"/>
-      <x:c r="M260" s="9" t="str">
+      <x:c r="L261" s="9" t="str"/>
+      <x:c r="M261" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N260" s="41" t="str">
+      <x:c r="N261" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="261" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A261" s="40" t="str"/>
-      <x:c r="B261" s="9" t="str"/>
-      <x:c r="C261" s="9" t="str"/>
-      <x:c r="D261" s="9" t="str"/>
-      <x:c r="E261" s="9" t="str"/>
-      <x:c r="F261" s="9" t="str"/>
-      <x:c r="G261" s="9" t="str"/>
-      <x:c r="H261" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I261" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J261" s="9" t="str">
+    <x:row r="262" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A262" s="40" t="str"/>
+      <x:c r="B262" s="9" t="str"/>
+      <x:c r="C262" s="9" t="str"/>
+      <x:c r="D262" s="9" t="str"/>
+      <x:c r="E262" s="9" t="str"/>
+      <x:c r="F262" s="9" t="str"/>
+      <x:c r="G262" s="9" t="str"/>
+      <x:c r="H262" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I262" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J262" s="9" t="str">
         <x:v>2020-2025 Cadillac XT6 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K261" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L261" s="9" t="str"/>
-      <x:c r="M261" s="9" t="str"/>
-      <x:c r="N261" s="41" t="str"/>
-    </x:row>
-    <x:row r="262" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A262" s="40" t="n">
+      <x:c r="K262" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L262" s="9" t="str"/>
+      <x:c r="M262" s="9" t="str"/>
+      <x:c r="N262" s="41" t="str"/>
+    </x:row>
+    <x:row r="263" ht="448.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A263" s="40" t="n">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B262" s="9" t="str">
+      <x:c r="B263" s="9" t="str">
         <x:v>cadillac-xt6-ptu-leak-2020</x:v>
       </x:c>
-      <x:c r="C262" s="9" t="str">
+      <x:c r="C263" s="9" t="str">
         <x:v>2020-2025 | Cadillac | XT6</x:v>
       </x:c>
-      <x:c r="D262" s="9" t="str">
+      <x:c r="D263" s="9" t="str">
         <x:v>AWD Power Transfer Unit Fluid Leak</x:v>
       </x:c>
-      <x:c r="E262" s="9" t="str">
+      <x:c r="E263" s="9" t="str">
         <x:v>Inspect the PTU seals and replace if leaking. Top off with the GM-specified PTU fluid. If the PTU is already noisy from running low on fluid, replacement is required as the unit is not rebuildable. Add PTU fluid level check to your routine maintenance schedule every 15,000 miles.</x:v>
       </x:c>
-      <x:c r="F262" s="9" t="str">
+      <x:c r="F263" s="9" t="str">
         <x:v>Inspect the PTU seals and replace if leaking. Top off with the GM-specified PTU fluid. If the PTU is already noisy from running low on fluid, replacement is required as the unit is not rebuildable. Add PTU fluid level check to your routine maintenance schedule every 15,000 miles.</x:v>
       </x:c>
-      <x:c r="G262" s="9" t="str">
+      <x:c r="G263" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H262" s="9" t="str">
+      <x:c r="H263" s="9" t="str">
         <x:v>GM Genuine Parts catalog — AWD Power Transfer Unit Fluid Leak</x:v>
       </x:c>
-      <x:c r="I262" s="9" t="str">
+      <x:c r="I263" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J262" s="9" t="str">
+      <x:c r="J263" s="9" t="str">
         <x:v>2020-2025 Cadillac XT6; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K262" s="9" t="str">
+      <x:c r="K263" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L262" s="9" t="str"/>
-      <x:c r="M262" s="9" t="str">
+      <x:c r="L263" s="9" t="str"/>
+      <x:c r="M263" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N262" s="41" t="str">
+      <x:c r="N263" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="263" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A263" s="40" t="str"/>
-      <x:c r="B263" s="9" t="str"/>
-      <x:c r="C263" s="9" t="str"/>
-      <x:c r="D263" s="9" t="str"/>
-      <x:c r="E263" s="9" t="str"/>
-      <x:c r="F263" s="9" t="str"/>
-      <x:c r="G263" s="9" t="str"/>
-      <x:c r="H263" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I263" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J263" s="9" t="str">
+    <x:row r="264" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A264" s="40" t="str"/>
+      <x:c r="B264" s="9" t="str"/>
+      <x:c r="C264" s="9" t="str"/>
+      <x:c r="D264" s="9" t="str"/>
+      <x:c r="E264" s="9" t="str"/>
+      <x:c r="F264" s="9" t="str"/>
+      <x:c r="G264" s="9" t="str"/>
+      <x:c r="H264" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I264" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J264" s="9" t="str">
         <x:v>2020-2025 Cadillac XT6 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K263" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L263" s="9" t="str"/>
-      <x:c r="M263" s="9" t="str"/>
-      <x:c r="N263" s="41" t="str"/>
-    </x:row>
-    <x:row r="264" ht="435.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A264" s="40" t="n">
+      <x:c r="K264" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L264" s="9" t="str"/>
+      <x:c r="M264" s="9" t="str"/>
+      <x:c r="N264" s="41" t="str"/>
+    </x:row>
+    <x:row r="265" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A265" s="40" t="n">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="B264" s="9" t="str">
+      <x:c r="B265" s="9" t="str">
         <x:v>cadillac-xt6-timing-chain-2020</x:v>
       </x:c>
-      <x:c r="C264" s="9" t="str">
+      <x:c r="C265" s="9" t="str">
         <x:v>2020-2025 | Cadillac | XT6</x:v>
       </x:c>
-      <x:c r="D264" s="9" t="str">
+      <x:c r="D265" s="9" t="str">
         <x:v>3.6L V6 Timing Chain Concern (XT6)</x:v>
       </x:c>
-      <x:c r="E264" s="9" t="str">
+      <x:c r="E265" s="9" t="str">
         <x:v>Monitor for timing chain rattle on cold starts. If codes or rattle develop, complete timing chain replacement is needed. Preventive replacement at 100,000-120,000 miles is wise based on the 3.6L's track record. Same Cloyes 9-0753S kit as other 3.6L applications.</x:v>
       </x:c>
-      <x:c r="F264" s="9" t="str">
+      <x:c r="F265" s="9" t="str">
         <x:v>Monitor for timing chain rattle on cold starts. If codes or rattle develop, complete timing chain replacement is needed. Preventive replacement at 100,000-120,000 miles is wise based on the 3.6L's track record. Same Cloyes 9-0753S kit as other 3.6L applications.</x:v>
       </x:c>
-      <x:c r="G264" s="9" t="str">
+      <x:c r="G265" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H264" s="9" t="str">
+      <x:c r="H265" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 3.6L V6 Timing Chain Concern</x:v>
       </x:c>
-      <x:c r="I264" s="9" t="str">
+      <x:c r="I265" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J264" s="9" t="str">
+      <x:c r="J265" s="9" t="str">
         <x:v>2020-2025 Cadillac XT6; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K264" s="9" t="str">
+      <x:c r="K265" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L264" s="9" t="str"/>
-      <x:c r="M264" s="9" t="str">
+      <x:c r="L265" s="9" t="str"/>
+      <x:c r="M265" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N264" s="41" t="str">
+      <x:c r="N265" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="265" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A265" s="40" t="str"/>
-      <x:c r="B265" s="9" t="str"/>
-      <x:c r="C265" s="9" t="str"/>
-      <x:c r="D265" s="9" t="str"/>
-      <x:c r="E265" s="9" t="str"/>
-      <x:c r="F265" s="9" t="str"/>
-      <x:c r="G265" s="9" t="str"/>
-      <x:c r="H265" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I265" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J265" s="9" t="str">
+    <x:row r="266" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A266" s="40" t="str"/>
+      <x:c r="B266" s="9" t="str"/>
+      <x:c r="C266" s="9" t="str"/>
+      <x:c r="D266" s="9" t="str"/>
+      <x:c r="E266" s="9" t="str"/>
+      <x:c r="F266" s="9" t="str"/>
+      <x:c r="G266" s="9" t="str"/>
+      <x:c r="H266" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I266" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J266" s="9" t="str">
         <x:v>2020-2025 Cadillac XT6 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K265" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L265" s="9" t="str"/>
-      <x:c r="M265" s="9" t="str"/>
-      <x:c r="N265" s="41" t="str"/>
-    </x:row>
-    <x:row r="266" ht="330" hidden="0" customHeight="1">
-      <x:c r="A266" s="40" t="n">
+      <x:c r="K266" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L266" s="9" t="str"/>
+      <x:c r="M266" s="9" t="str"/>
+      <x:c r="N266" s="41" t="str"/>
+    </x:row>
+    <x:row r="267" ht="330" hidden="0" customHeight="1">
+      <x:c r="A267" s="40" t="n">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B266" s="9" t="str">
+      <x:c r="B267" s="9" t="str">
         <x:v>cadillac-xt6-transmission-shudder-2020</x:v>
       </x:c>
-      <x:c r="C266" s="9" t="str">
+      <x:c r="C267" s="9" t="str">
         <x:v>2020-2023 | Cadillac | XT6</x:v>
       </x:c>
-      <x:c r="D266" s="9" t="str">
+      <x:c r="D267" s="9" t="str">
         <x:v>9-Speed Automatic Transmission Shudder and Harsh Shifts</x:v>
       </x:c>
-      <x:c r="E266" s="9" t="str">
+      <x:c r="E267" s="9" t="str">
         <x:v>A transmission fluid flush with the updated Mobil 1 Blue Label fluid resolves mild cases. Severe cases require torque converter replacement. A GM TSB authorizes fluid flush as the first repair attempt.</x:v>
       </x:c>
-      <x:c r="F266" s="9" t="str">
+      <x:c r="F267" s="9" t="str">
         <x:v>A transmission fluid flush with the updated Mobil 1 Blue Label fluid resolves mild cases. Severe cases require torque converter replacement. A GM TSB authorizes fluid flush as the first repair attempt.</x:v>
       </x:c>
-      <x:c r="G266" s="9" t="str">
+      <x:c r="G267" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H266" s="9" t="str">
+      <x:c r="H267" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 9-Speed Automatic Transmission Shudder and Harsh Shifts</x:v>
       </x:c>
-      <x:c r="I266" s="9" t="str">
+      <x:c r="I267" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J266" s="9" t="str">
+      <x:c r="J267" s="9" t="str">
         <x:v>2020-2023 Cadillac XT6; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K266" s="9" t="str">
+      <x:c r="K267" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L266" s="9" t="str"/>
-      <x:c r="M266" s="9" t="str">
+      <x:c r="L267" s="9" t="str"/>
+      <x:c r="M267" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N266" s="41" t="str">
+      <x:c r="N267" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="267" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A267" s="40" t="str"/>
-      <x:c r="B267" s="9" t="str"/>
-      <x:c r="C267" s="9" t="str"/>
-      <x:c r="D267" s="9" t="str"/>
-      <x:c r="E267" s="9" t="str"/>
-      <x:c r="F267" s="9" t="str"/>
-      <x:c r="G267" s="9" t="str"/>
-      <x:c r="H267" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I267" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J267" s="9" t="str">
+    <x:row r="268" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A268" s="40" t="str"/>
+      <x:c r="B268" s="9" t="str"/>
+      <x:c r="C268" s="9" t="str"/>
+      <x:c r="D268" s="9" t="str"/>
+      <x:c r="E268" s="9" t="str"/>
+      <x:c r="F268" s="9" t="str"/>
+      <x:c r="G268" s="9" t="str"/>
+      <x:c r="H268" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I268" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J268" s="9" t="str">
         <x:v>2020-2023 Cadillac XT6 diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K267" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L267" s="9" t="str"/>
-      <x:c r="M267" s="9" t="str"/>
-      <x:c r="N267" s="41" t="str"/>
-    </x:row>
-    <x:row r="268" ht="541.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A268" s="40" t="n">
+      <x:c r="K268" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L268" s="9" t="str"/>
+      <x:c r="M268" s="9" t="str"/>
+      <x:c r="N268" s="41" t="str"/>
+    </x:row>
+    <x:row r="269" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A269" s="40" t="n">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B268" s="9" t="str">
+      <x:c r="B269" s="9" t="str">
         <x:v>cadillac-xts-3-6l-direct-injection-intake-valve-carbon-buildup</x:v>
       </x:c>
-      <x:c r="C268" s="9" t="str">
+      <x:c r="C269" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | Luxury, Premium, Platinum, V-Sport, Vsport | 3.6L V6 (LFX), 3.6L Twin-Turbo V6 (LF3)</x:v>
       </x:c>
-      <x:c r="D268" s="9" t="str">
+      <x:c r="D269" s="9" t="str">
         <x:v>3.6L Direct-Injection Intake Valve Carbon Buildup</x:v>
       </x:c>
-      <x:c r="E268" s="9" t="str">
+      <x:c r="E269" s="9" t="str">
         <x:v>Clean the intake valves by walnut-shell media blasting (the accepted fix for GDI coking); chemical intake cleaners help mildly but do not remove hardened deposits. To slow recurrence, install an oil catch can on the PCV line and/or a reduced-orifice PCV to keep oil vapor out of the intake. Periodic top-end cleaning is preventive maintenance on these DI engines.</x:v>
       </x:c>
-      <x:c r="F268" s="9" t="str">
+      <x:c r="F269" s="9" t="str">
         <x:v>Clean the intake valves by walnut-shell media blasting (the accepted fix for GDI coking); chemical intake cleaners help mildly but do not remove hardened deposits. To slow recurrence, install an oil catch can on the PCV line and/or a reduced-orifice PCV to keep oil vapor out of the intake. Periodic top-end cleaning is preventive maintenance on these DI engines.</x:v>
       </x:c>
-      <x:c r="G268" s="9" t="str">
+      <x:c r="G269" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H268" s="9" t="str">
+      <x:c r="H269" s="9" t="str">
         <x:v>GM Genuine Parts catalog — 3.6L Direct-Injection Intake Valve Carbon Buildup</x:v>
       </x:c>
-      <x:c r="I268" s="9" t="str">
+      <x:c r="I269" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J268" s="9" t="str">
+      <x:c r="J269" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K268" s="9" t="str">
+      <x:c r="K269" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L268" s="9" t="str"/>
-      <x:c r="M268" s="9" t="str">
+      <x:c r="L269" s="9" t="str"/>
+      <x:c r="M269" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N268" s="41" t="str">
+      <x:c r="N269" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="269" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A269" s="40" t="str"/>
-      <x:c r="B269" s="9" t="str"/>
-      <x:c r="C269" s="9" t="str"/>
-      <x:c r="D269" s="9" t="str"/>
-      <x:c r="E269" s="9" t="str"/>
-      <x:c r="F269" s="9" t="str"/>
-      <x:c r="G269" s="9" t="str"/>
-      <x:c r="H269" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I269" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J269" s="9" t="str">
+    <x:row r="270" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A270" s="40" t="str"/>
+      <x:c r="B270" s="9" t="str"/>
+      <x:c r="C270" s="9" t="str"/>
+      <x:c r="D270" s="9" t="str"/>
+      <x:c r="E270" s="9" t="str"/>
+      <x:c r="F270" s="9" t="str"/>
+      <x:c r="G270" s="9" t="str"/>
+      <x:c r="H270" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I270" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J270" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K269" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L269" s="9" t="str"/>
-      <x:c r="M269" s="9" t="str"/>
-      <x:c r="N269" s="41" t="str"/>
-    </x:row>
-    <x:row r="270" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A270" s="40" t="n">
+      <x:c r="K270" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L270" s="9" t="str"/>
+      <x:c r="M270" s="9" t="str"/>
+      <x:c r="N270" s="41" t="str"/>
+    </x:row>
+    <x:row r="271" ht="501.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A271" s="40" t="n">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="B270" s="9" t="str">
+      <x:c r="B271" s="9" t="str">
         <x:v>cadillac-xts-brake-booster-pump-connector-corrosion</x:v>
       </x:c>
-      <x:c r="C270" s="9" t="str">
+      <x:c r="C271" s="9" t="str">
         <x:v>2013-2014 | Cadillac | XTS</x:v>
       </x:c>
-      <x:c r="D270" s="9" t="str">
+      <x:c r="D271" s="9" t="str">
         <x:v>Recall 14V116: Brake-Booster Pump Connector Corrosion Can Create a Fire Risk</x:v>
       </x:c>
-      <x:c r="E270" s="9" t="str">
+      <x:c r="E271" s="9" t="str">
         <x:v>Check the VIN for an open NHTSA 14V116 / GM 14062 campaign. If open, arrange the dealer recall remedy, which includes sealing the cavity plugs, rerouting the vacuum-pump vent hose and replacing the affected front body harness when required. Do not purchase recall components from the former commerce links.</x:v>
       </x:c>
-      <x:c r="F270" s="9" t="str">
+      <x:c r="F271" s="9" t="str">
         <x:v>Check the VIN for an open NHTSA 14V116 / GM 14062 campaign. If open, arrange the dealer recall remedy, which includes sealing the cavity plugs, rerouting the vacuum-pump vent hose and replacing the affected front body harness when required. Do not purchase recall components from the former commerce links.</x:v>
       </x:c>
-      <x:c r="G270" s="9" t="str">
+      <x:c r="G271" s="9" t="str">
         <x:v>RECALL ROUTES ONLY</x:v>
       </x:c>
-      <x:c r="H270" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I270" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J270" s="9" t="str">
+      <x:c r="H271" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I271" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J271" s="9" t="str">
         <x:v>2013-2014 Cadillac XTS VIN/campaign completion and free remedy</x:v>
       </x:c>
-      <x:c r="K270" s="9" t="str">
+      <x:c r="K271" s="9" t="str">
         <x:v>authorized recall service</x:v>
       </x:c>
-      <x:c r="L270" s="9" t="str"/>
-      <x:c r="M270" s="9" t="str">
+      <x:c r="L271" s="9" t="str"/>
+      <x:c r="M271" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N270" s="41" t="str">
+      <x:c r="N271" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="271" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A271" s="40" t="str"/>
-      <x:c r="B271" s="9" t="str"/>
-      <x:c r="C271" s="9" t="str"/>
-      <x:c r="D271" s="9" t="str"/>
-      <x:c r="E271" s="9" t="str"/>
-      <x:c r="F271" s="9" t="str"/>
-      <x:c r="G271" s="9" t="str"/>
-      <x:c r="H271" s="9" t="str">
+    <x:row r="272" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A272" s="40" t="str"/>
+      <x:c r="B272" s="9" t="str"/>
+      <x:c r="C272" s="9" t="str"/>
+      <x:c r="D272" s="9" t="str"/>
+      <x:c r="E272" s="9" t="str"/>
+      <x:c r="F272" s="9" t="str"/>
+      <x:c r="G272" s="9" t="str"/>
+      <x:c r="H272" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I271" s="9" t="str">
+      <x:c r="I272" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J271" s="9" t="str">
+      <x:c r="J272" s="9" t="str">
         <x:v>2013-2014 Cadillac XTS VIN history</x:v>
       </x:c>
-      <x:c r="K271" s="9" t="str">
+      <x:c r="K272" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L271" s="9" t="str"/>
-      <x:c r="M271" s="9" t="str"/>
-      <x:c r="N271" s="41" t="str"/>
-    </x:row>
-    <x:row r="272" ht="369.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A272" s="40" t="n">
+      <x:c r="L272" s="9" t="str"/>
+      <x:c r="M272" s="9" t="str"/>
+      <x:c r="N272" s="41" t="str"/>
+    </x:row>
+    <x:row r="273" ht="369.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A273" s="40" t="n">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="B272" s="9" t="str">
+      <x:c r="B273" s="9" t="str">
         <x:v>cadillac-xts-brake-lamps-flash-intermittently-cruise-disengages</x:v>
       </x:c>
-      <x:c r="C272" s="9" t="str">
+      <x:c r="C273" s="9" t="str">
         <x:v>2013-2013 | Cadillac | XTS</x:v>
       </x:c>
-      <x:c r="D272" s="9" t="str">
+      <x:c r="D273" s="9" t="str">
         <x:v>Recall 13V220: Brake Lamps May Flash and Cruise Control May Disengage</x:v>
       </x:c>
-      <x:c r="E272" s="9" t="str">
+      <x:c r="E273" s="9" t="str">
         <x:v>Check the VIN for an open NHTSA 13V220 / GM 13158 campaign. If open, arrange dealer reprogramming of the body control module at no charge. No parts are required by the recall, so all former switch and module commerce links were removed.</x:v>
       </x:c>
-      <x:c r="F272" s="9" t="str">
+      <x:c r="F273" s="9" t="str">
         <x:v>Check the VIN for an open NHTSA 13V220 / GM 13158 campaign. If open, arrange dealer reprogramming of the body control module at no charge. No parts are required by the recall, so all former switch and module commerce links were removed.</x:v>
       </x:c>
-      <x:c r="G272" s="9" t="str">
+      <x:c r="G273" s="9" t="str">
         <x:v>RECALL ROUTES ONLY</x:v>
       </x:c>
-      <x:c r="H272" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I272" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J272" s="9" t="str">
+      <x:c r="H273" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I273" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J273" s="9" t="str">
         <x:v>2013-2013 Cadillac XTS VIN/campaign completion and free remedy</x:v>
       </x:c>
-      <x:c r="K272" s="9" t="str">
+      <x:c r="K273" s="9" t="str">
         <x:v>authorized recall service</x:v>
       </x:c>
-      <x:c r="L272" s="9" t="str"/>
-      <x:c r="M272" s="9" t="str">
+      <x:c r="L273" s="9" t="str"/>
+      <x:c r="M273" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N272" s="41" t="str">
+      <x:c r="N273" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="273" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A273" s="40" t="str"/>
-      <x:c r="B273" s="9" t="str"/>
-      <x:c r="C273" s="9" t="str"/>
-      <x:c r="D273" s="9" t="str"/>
-      <x:c r="E273" s="9" t="str"/>
-      <x:c r="F273" s="9" t="str"/>
-      <x:c r="G273" s="9" t="str"/>
-      <x:c r="H273" s="9" t="str">
+    <x:row r="274" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A274" s="40" t="str"/>
+      <x:c r="B274" s="9" t="str"/>
+      <x:c r="C274" s="9" t="str"/>
+      <x:c r="D274" s="9" t="str"/>
+      <x:c r="E274" s="9" t="str"/>
+      <x:c r="F274" s="9" t="str"/>
+      <x:c r="G274" s="9" t="str"/>
+      <x:c r="H274" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I273" s="9" t="str">
+      <x:c r="I274" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J273" s="9" t="str">
+      <x:c r="J274" s="9" t="str">
         <x:v>2013-2013 Cadillac XTS VIN history</x:v>
       </x:c>
-      <x:c r="K273" s="9" t="str">
+      <x:c r="K274" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L273" s="9" t="str"/>
-      <x:c r="M273" s="9" t="str"/>
-      <x:c r="N273" s="41" t="str"/>
-    </x:row>
-    <x:row r="274" ht="198" hidden="0" customHeight="1">
-      <x:c r="A274" s="40" t="n">
+      <x:c r="L274" s="9" t="str"/>
+      <x:c r="M274" s="9" t="str"/>
+      <x:c r="N274" s="41" t="str"/>
+    </x:row>
+    <x:row r="275" ht="198" hidden="0" customHeight="1">
+      <x:c r="A275" s="40" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B274" s="9" t="str">
+      <x:c r="B275" s="9" t="str">
         <x:v>cadillac-xts-cue-screen-2013</x:v>
       </x:c>
-      <x:c r="C274" s="9" t="str">
+      <x:c r="C275" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS</x:v>
       </x:c>
-      <x:c r="D274" s="9" t="str">
+      <x:c r="D275" s="9" t="str">
         <x:v>CUE Infotainment Touchscreen Delamination - XTS</x:v>
       </x:c>
-      <x:c r="E274" s="9" t="str">
+      <x:c r="E275" s="9" t="str">
         <x:v>Replace CUE screen with OEM (GM 23106488) or aftermarket unit. Straightforward DIY.</x:v>
       </x:c>
-      <x:c r="F274" s="9" t="str">
+      <x:c r="F275" s="9" t="str">
         <x:v>Replace CUE screen with OEM (GM 23106488) or aftermarket unit. Straightforward DIY.</x:v>
       </x:c>
-      <x:c r="G274" s="9" t="str">
+      <x:c r="G275" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H274" s="9" t="str">
+      <x:c r="H275" s="9" t="str">
         <x:v>GM Genuine Parts catalog — CUE Infotainment Touchscreen Delamination - XTS</x:v>
       </x:c>
-      <x:c r="I274" s="9" t="str">
+      <x:c r="I275" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J274" s="9" t="str">
+      <x:c r="J275" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K274" s="9" t="str">
+      <x:c r="K275" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L274" s="9" t="str"/>
-      <x:c r="M274" s="9" t="str">
+      <x:c r="L275" s="9" t="str"/>
+      <x:c r="M275" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N274" s="41" t="str">
+      <x:c r="N275" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="275" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A275" s="40" t="str"/>
-      <x:c r="B275" s="9" t="str"/>
-      <x:c r="C275" s="9" t="str"/>
-      <x:c r="D275" s="9" t="str"/>
-      <x:c r="E275" s="9" t="str"/>
-      <x:c r="F275" s="9" t="str"/>
-      <x:c r="G275" s="9" t="str"/>
-      <x:c r="H275" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I275" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J275" s="9" t="str">
+    <x:row r="276" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A276" s="40" t="str"/>
+      <x:c r="B276" s="9" t="str"/>
+      <x:c r="C276" s="9" t="str"/>
+      <x:c r="D276" s="9" t="str"/>
+      <x:c r="E276" s="9" t="str"/>
+      <x:c r="F276" s="9" t="str"/>
+      <x:c r="G276" s="9" t="str"/>
+      <x:c r="H276" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I276" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J276" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K275" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L275" s="9" t="str"/>
-      <x:c r="M275" s="9" t="str"/>
-      <x:c r="N275" s="41" t="str"/>
-    </x:row>
-    <x:row r="276" ht="435.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A276" s="40" t="n">
+      <x:c r="K276" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L276" s="9" t="str"/>
+      <x:c r="M276" s="9" t="str"/>
+      <x:c r="N276" s="41" t="str"/>
+    </x:row>
+    <x:row r="277" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A277" s="40" t="n">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="B276" s="9" t="str">
+      <x:c r="B277" s="9" t="str">
         <x:v>cadillac-xts-electric-parking-brake-2013</x:v>
       </x:c>
-      <x:c r="C276" s="9" t="str">
+      <x:c r="C277" s="9" t="str">
         <x:v>2013-2015 | Cadillac | XTS</x:v>
       </x:c>
-      <x:c r="D276" s="9" t="str">
+      <x:c r="D277" s="9" t="str">
         <x:v>Recall 14V541: Electronic Parking-Brake Software May Allow Brake Drag</x:v>
       </x:c>
-      <x:c r="E276" s="9" t="str">
+      <x:c r="E277" s="9" t="str">
         <x:v>Check the VIN for an open NHTSA 14V541 / GM 14471 campaign. If open, arrange dealer reprogramming of the electronic parking-brake control module at no charge. The recall remedy is software, not automatic actuator, switch or pad replacement, so the former parts links were removed.</x:v>
       </x:c>
-      <x:c r="F276" s="9" t="str">
+      <x:c r="F277" s="9" t="str">
         <x:v>Check the VIN for an open NHTSA 14V541 / GM 14471 campaign. If open, arrange dealer reprogramming of the electronic parking-brake control module at no charge. The recall remedy is software, not automatic actuator, switch or pad replacement, so the former parts links were removed.</x:v>
       </x:c>
-      <x:c r="G276" s="9" t="str">
+      <x:c r="G277" s="9" t="str">
         <x:v>RECALL ROUTES ONLY</x:v>
       </x:c>
-      <x:c r="H276" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I276" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J276" s="9" t="str">
+      <x:c r="H277" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I277" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J277" s="9" t="str">
         <x:v>2013-2015 Cadillac XTS VIN/campaign completion and free remedy</x:v>
       </x:c>
-      <x:c r="K276" s="9" t="str">
+      <x:c r="K277" s="9" t="str">
         <x:v>authorized recall service</x:v>
       </x:c>
-      <x:c r="L276" s="9" t="str"/>
-      <x:c r="M276" s="9" t="str">
+      <x:c r="L277" s="9" t="str"/>
+      <x:c r="M277" s="9" t="str">
         <x:v>The VIN-specific campaign controls inspection, parts and remedy eligibility.</x:v>
       </x:c>
-      <x:c r="N276" s="41" t="str">
+      <x:c r="N277" s="41" t="str">
         <x:v>No retail part or scanner link; verify campaign completion by VIN.</x:v>
       </x:c>
     </x:row>
-    <x:row r="277" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A277" s="40" t="str"/>
-      <x:c r="B277" s="9" t="str"/>
-      <x:c r="C277" s="9" t="str"/>
-      <x:c r="D277" s="9" t="str"/>
-      <x:c r="E277" s="9" t="str"/>
-      <x:c r="F277" s="9" t="str"/>
-      <x:c r="G277" s="9" t="str"/>
-      <x:c r="H277" s="9" t="str">
+    <x:row r="278" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A278" s="40" t="str"/>
+      <x:c r="B278" s="9" t="str"/>
+      <x:c r="C278" s="9" t="str"/>
+      <x:c r="D278" s="9" t="str"/>
+      <x:c r="E278" s="9" t="str"/>
+      <x:c r="F278" s="9" t="str"/>
+      <x:c r="G278" s="9" t="str"/>
+      <x:c r="H278" s="9" t="str">
         <x:v>NHTSA recall lookup</x:v>
       </x:c>
-      <x:c r="I277" s="9" t="str">
+      <x:c r="I278" s="9" t="str">
         <x:v>https://www.nhtsa.gov/recalls</x:v>
       </x:c>
-      <x:c r="J277" s="9" t="str">
+      <x:c r="J278" s="9" t="str">
         <x:v>2013-2015 Cadillac XTS VIN history</x:v>
       </x:c>
-      <x:c r="K277" s="9" t="str">
+      <x:c r="K278" s="9" t="str">
         <x:v>government recall lookup</x:v>
       </x:c>
-      <x:c r="L277" s="9" t="str"/>
-      <x:c r="M277" s="9" t="str"/>
-      <x:c r="N277" s="41" t="str"/>
-    </x:row>
-    <x:row r="278" ht="765.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A278" s="40" t="n">
+      <x:c r="L278" s="9" t="str"/>
+      <x:c r="M278" s="9" t="str"/>
+      <x:c r="N278" s="41" t="str"/>
+    </x:row>
+    <x:row r="279" ht="765.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A279" s="40" t="n">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B278" s="9" t="str">
+      <x:c r="B279" s="9" t="str">
         <x:v>cadillac-xts-hid-xenon-headlight-ballast-failure-housing-moisture</x:v>
       </x:c>
-      <x:c r="C278" s="9" t="str">
+      <x:c r="C279" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | 3.6L V6 LFX/LGX, 3.6L V6 Twin-Turbo LF3</x:v>
       </x:c>
-      <x:c r="D278" s="9" t="str">
+      <x:c r="D279" s="9" t="str">
         <x:v>HID Xenon Headlight Ballast Failure &amp; Housing Moisture</x:v>
       </x:c>
-      <x:c r="E278" s="9" t="str">
+      <x:c r="E279" s="9" t="str">
         <x:v>Diagnose by swapping the D3S bulb side-to-side; if the fault follows the position, the ballast/igniter is bad, not the bulb. Replace the failed HID ballast/control module and reseal the housing; dry out and re-gasket any housing showing condensation. Inspect the ballast connector and chassis ground for corrosion and repair before installing new parts, or the new ballast will fail again. Use OEM-grade D3S bulbs and a matching ballast to avoid color/flicker issues.</x:v>
       </x:c>
-      <x:c r="F278" s="9" t="str">
+      <x:c r="F279" s="9" t="str">
         <x:v>Diagnose by swapping the D3S bulb side-to-side; if the fault follows the position, the ballast/igniter is bad, not the bulb. Replace the failed HID ballast/control module and reseal the housing; dry out and re-gasket any housing showing condensation. Inspect the ballast connector and chassis ground for corrosion and repair before installing new parts, or the new ballast will fail again. Use OEM-grade D3S bulbs and a matching ballast to avoid color/flicker issues.</x:v>
       </x:c>
-      <x:c r="G278" s="9" t="str">
+      <x:c r="G279" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H278" s="9" t="str">
+      <x:c r="H279" s="9" t="str">
         <x:v>GM Genuine Parts catalog — HID Xenon Headlight Ballast Failure &amp; Housing Moisture</x:v>
       </x:c>
-      <x:c r="I278" s="9" t="str">
+      <x:c r="I279" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J278" s="9" t="str">
+      <x:c r="J279" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K278" s="9" t="str">
+      <x:c r="K279" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L278" s="9" t="str"/>
-      <x:c r="M278" s="9" t="str">
+      <x:c r="L279" s="9" t="str"/>
+      <x:c r="M279" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N278" s="41" t="str">
+      <x:c r="N279" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="279" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A279" s="40" t="str"/>
-      <x:c r="B279" s="9" t="str"/>
-      <x:c r="C279" s="9" t="str"/>
-      <x:c r="D279" s="9" t="str"/>
-      <x:c r="E279" s="9" t="str"/>
-      <x:c r="F279" s="9" t="str"/>
-      <x:c r="G279" s="9" t="str"/>
-      <x:c r="H279" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I279" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J279" s="9" t="str">
+    <x:row r="280" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A280" s="40" t="str"/>
+      <x:c r="B280" s="9" t="str"/>
+      <x:c r="C280" s="9" t="str"/>
+      <x:c r="D280" s="9" t="str"/>
+      <x:c r="E280" s="9" t="str"/>
+      <x:c r="F280" s="9" t="str"/>
+      <x:c r="G280" s="9" t="str"/>
+      <x:c r="H280" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I280" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J280" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K279" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L279" s="9" t="str"/>
-      <x:c r="M279" s="9" t="str"/>
-      <x:c r="N279" s="41" t="str"/>
-    </x:row>
-    <x:row r="280" ht="818.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A280" s="40" t="n">
+      <x:c r="K280" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L280" s="9" t="str"/>
+      <x:c r="M280" s="9" t="str"/>
+      <x:c r="N280" s="41" t="str"/>
+    </x:row>
+    <x:row r="281" ht="818.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A281" s="40" t="n">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B280" s="9" t="str">
+      <x:c r="B281" s="9" t="str">
         <x:v>cadillac-xts-high-pressure-direct-injection-fuel-pump-failure</x:v>
       </x:c>
-      <x:c r="C280" s="9" t="str">
+      <x:c r="C281" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | 3.6L V6 LFX/LGX, 3.6L V6 Twin-Turbo LF3</x:v>
       </x:c>
-      <x:c r="D280" s="9" t="str">
+      <x:c r="D281" s="9" t="str">
         <x:v>High-Pressure Direct-Injection Fuel Pump Failure</x:v>
       </x:c>
-      <x:c r="E280" s="9" t="str">
+      <x:c r="E281" s="9" t="str">
         <x:v>Perform a live high-side fuel-pressure test during acceleration and on a warm restart to confirm the HPFP versus injectors or the low-pressure (in-tank) pump. Replace the high-pressure fuel pump and its sealing/lifter components; many shops also replace the camshaft pump-drive lifter and inspect the lobe. Use fresh GM-spec fuel-system sealant and torque to spec to avoid leaks. OEM HPFP PN 12641740 (supersedes 12622475; aftermarket Delphi HM10007 / GDP106 cross-references). Reset fuel trims after the repair.</x:v>
       </x:c>
-      <x:c r="F280" s="9" t="str">
+      <x:c r="F281" s="9" t="str">
         <x:v>Perform a live high-side fuel-pressure test during acceleration and on a warm restart to confirm the HPFP versus injectors or the low-pressure (in-tank) pump. Replace the high-pressure fuel pump and its sealing/lifter components; many shops also replace the camshaft pump-drive lifter and inspect the lobe. Use fresh GM-spec fuel-system sealant and torque to spec to avoid leaks. OEM HPFP PN 12641740 (supersedes 12622475; aftermarket Delphi HM10007 / GDP106 cross-references). Reset fuel trims after the repair.</x:v>
       </x:c>
-      <x:c r="G280" s="9" t="str">
+      <x:c r="G281" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H280" s="9" t="str">
+      <x:c r="H281" s="9" t="str">
         <x:v>GM Genuine Parts catalog — High-Pressure Direct-Injection Fuel Pump Failure</x:v>
       </x:c>
-      <x:c r="I280" s="9" t="str">
+      <x:c r="I281" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J280" s="9" t="str">
+      <x:c r="J281" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K280" s="9" t="str">
+      <x:c r="K281" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L280" s="9" t="str"/>
-      <x:c r="M280" s="9" t="str">
+      <x:c r="L281" s="9" t="str"/>
+      <x:c r="M281" s="9" t="str">
         <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
       </x:c>
-      <x:c r="N280" s="41" t="str">
+      <x:c r="N281" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="281" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A281" s="40" t="str"/>
-      <x:c r="B281" s="9" t="str"/>
-      <x:c r="C281" s="9" t="str"/>
-      <x:c r="D281" s="9" t="str"/>
-      <x:c r="E281" s="9" t="str"/>
-      <x:c r="F281" s="9" t="str"/>
-      <x:c r="G281" s="9" t="str"/>
-      <x:c r="H281" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I281" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J281" s="9" t="str">
+    <x:row r="282" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A282" s="40" t="str"/>
+      <x:c r="B282" s="9" t="str"/>
+      <x:c r="C282" s="9" t="str"/>
+      <x:c r="D282" s="9" t="str"/>
+      <x:c r="E282" s="9" t="str"/>
+      <x:c r="F282" s="9" t="str"/>
+      <x:c r="G282" s="9" t="str"/>
+      <x:c r="H282" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I282" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J282" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K281" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L281" s="9" t="str"/>
-      <x:c r="M281" s="9" t="str"/>
-      <x:c r="N281" s="41" t="str"/>
-    </x:row>
-    <x:row r="282" ht="660" hidden="0" customHeight="1">
-      <x:c r="A282" s="40" t="n">
+      <x:c r="K282" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L282" s="9" t="str"/>
+      <x:c r="M282" s="9" t="str"/>
+      <x:c r="N282" s="41" t="str"/>
+    </x:row>
+    <x:row r="283" ht="660" hidden="0" customHeight="1">
+      <x:c r="A283" s="40" t="n">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B282" s="9" t="str">
+      <x:c r="B283" s="9" t="str">
         <x:v>cadillac-xts-hvac-blend-door-actuator-clicking-blower-resistor-no-heat</x:v>
       </x:c>
-      <x:c r="C282" s="9" t="str">
+      <x:c r="C283" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | 3.6L V6 LFX/LGX, 3.6L V6 Twin-Turbo LF3</x:v>
       </x:c>
-      <x:c r="D282" s="9" t="str">
+      <x:c r="D283" s="9" t="str">
         <x:v>HVAC Blend Door Actuator Clicking / Blower Resistor No Heat</x:v>
       </x:c>
-      <x:c r="E282" s="9" t="str">
+      <x:c r="E283" s="9" t="str">
         <x:v>For the clicking: identify the failing blend-door actuator (listen/feel behind the dash while cycling temperature), replace the actuator and re-run the HVAC calibration/relearn. For no/limited fan: test the blower motor resistor/control module and the blower motor itself; replace the failed resistor module (and motor if it's drawing high current). Clear any HVAC actuator codes after replacement.</x:v>
       </x:c>
-      <x:c r="F282" s="9" t="str">
+      <x:c r="F283" s="9" t="str">
         <x:v>For the clicking: identify the failing blend-door actuator (listen/feel behind the dash while cycling temperature), replace the actuator and re-run the HVAC calibration/relearn. For no/limited fan: test the blower motor resistor/control module and the blower motor itself; replace the failed resistor module (and motor if it's drawing high current). Clear any HVAC actuator codes after replacement.</x:v>
       </x:c>
-      <x:c r="G282" s="9" t="str">
+      <x:c r="G283" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H282" s="9" t="str">
+      <x:c r="H283" s="9" t="str">
         <x:v>GM Genuine Parts catalog — HVAC Blend Door Actuator Clicking / Blower Resistor No Heat</x:v>
       </x:c>
-      <x:c r="I282" s="9" t="str">
+      <x:c r="I283" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J282" s="9" t="str">
+      <x:c r="J283" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K282" s="9" t="str">
+      <x:c r="K283" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L282" s="9" t="str"/>
-      <x:c r="M282" s="9" t="str">
+      <x:c r="L283" s="9" t="str"/>
+      <x:c r="M283" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N282" s="41" t="str">
+      <x:c r="N283" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="283" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A283" s="40" t="str"/>
-      <x:c r="B283" s="9" t="str"/>
-      <x:c r="C283" s="9" t="str"/>
-      <x:c r="D283" s="9" t="str"/>
-      <x:c r="E283" s="9" t="str"/>
-      <x:c r="F283" s="9" t="str"/>
-      <x:c r="G283" s="9" t="str"/>
-      <x:c r="H283" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I283" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J283" s="9" t="str">
+    <x:row r="284" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A284" s="40" t="str"/>
+      <x:c r="B284" s="9" t="str"/>
+      <x:c r="C284" s="9" t="str"/>
+      <x:c r="D284" s="9" t="str"/>
+      <x:c r="E284" s="9" t="str"/>
+      <x:c r="F284" s="9" t="str"/>
+      <x:c r="G284" s="9" t="str"/>
+      <x:c r="H284" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I284" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J284" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K283" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L283" s="9" t="str"/>
-      <x:c r="M283" s="9" t="str"/>
-      <x:c r="N283" s="41" t="str"/>
-    </x:row>
-    <x:row r="284" ht="607.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A284" s="40" t="n">
+      <x:c r="K284" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L284" s="9" t="str"/>
+      <x:c r="M284" s="9" t="str"/>
+      <x:c r="N284" s="41" t="str"/>
+    </x:row>
+    <x:row r="285" ht="607.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A285" s="40" t="n">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B284" s="9" t="str">
+      <x:c r="B285" s="9" t="str">
         <x:v>cadillac-xts-illuminated-door-handle-led-failure</x:v>
       </x:c>
-      <x:c r="C284" s="9" t="str">
+      <x:c r="C285" s="9" t="str">
         <x:v>2013-2013 | Cadillac | XTS</x:v>
       </x:c>
-      <x:c r="D284" s="9" t="str">
+      <x:c r="D285" s="9" t="str">
         <x:v>Early-Build Illuminated Door Handles May Fail from Water Intrusion</x:v>
       </x:c>
-      <x:c r="E284" s="9" t="str">
+      <x:c r="E285" s="9" t="str">
         <x:v>Verify RPO HD7 and the build date before applying this bulletin. For an affected handle, follow current service information to replace the complete outside handle assembly and the cable for that door; GM specifically warns against replacing only the PCB insert. Use the electronic parts catalog for the exact painted handle rather than the former generic commerce links.</x:v>
       </x:c>
-      <x:c r="F284" s="9" t="str">
+      <x:c r="F285" s="9" t="str">
         <x:v>Verify RPO HD7 and the build date before applying this bulletin. For an affected handle, follow current service information to replace the complete outside handle assembly and the cable for that door; GM specifically warns against replacing only the PCB insert. Use the electronic parts catalog for the exact painted handle rather than the former generic commerce links.</x:v>
       </x:c>
-      <x:c r="G284" s="9" t="str">
+      <x:c r="G285" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H284" s="9" t="str">
+      <x:c r="H285" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Early-Build Illuminated Door Handles May Fail from Water Intrusion</x:v>
       </x:c>
-      <x:c r="I284" s="9" t="str">
+      <x:c r="I285" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J284" s="9" t="str">
+      <x:c r="J285" s="9" t="str">
         <x:v>2013-2013 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K284" s="9" t="str">
+      <x:c r="K285" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L284" s="9" t="str"/>
-      <x:c r="M284" s="9" t="str">
+      <x:c r="L285" s="9" t="str"/>
+      <x:c r="M285" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N284" s="41" t="str">
+      <x:c r="N285" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="285" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A285" s="40" t="str"/>
-      <x:c r="B285" s="9" t="str"/>
-      <x:c r="C285" s="9" t="str"/>
-      <x:c r="D285" s="9" t="str"/>
-      <x:c r="E285" s="9" t="str"/>
-      <x:c r="F285" s="9" t="str"/>
-      <x:c r="G285" s="9" t="str"/>
-      <x:c r="H285" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I285" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J285" s="9" t="str">
+    <x:row r="286" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A286" s="40" t="str"/>
+      <x:c r="B286" s="9" t="str"/>
+      <x:c r="C286" s="9" t="str"/>
+      <x:c r="D286" s="9" t="str"/>
+      <x:c r="E286" s="9" t="str"/>
+      <x:c r="F286" s="9" t="str"/>
+      <x:c r="G286" s="9" t="str"/>
+      <x:c r="H286" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I286" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J286" s="9" t="str">
         <x:v>2013-2013 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K285" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L285" s="9" t="str"/>
-      <x:c r="M285" s="9" t="str"/>
-      <x:c r="N285" s="41" t="str"/>
-    </x:row>
-    <x:row r="286" ht="514.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A286" s="40" t="n">
+      <x:c r="K286" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L286" s="9" t="str"/>
+      <x:c r="M286" s="9" t="str"/>
+      <x:c r="N286" s="41" t="str"/>
+    </x:row>
+    <x:row r="287" ht="514.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A287" s="40" t="n">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="B286" s="9" t="str">
+      <x:c r="B287" s="9" t="str">
         <x:v>cadillac-xts-magnetic-ride-control-strut-shock-failure</x:v>
       </x:c>
-      <x:c r="C286" s="9" t="str">
+      <x:c r="C287" s="9" t="str">
         <x:v>2013-2015 | Cadillac | XTS</x:v>
       </x:c>
-      <x:c r="D286" s="9" t="str">
+      <x:c r="D287" s="9" t="str">
         <x:v>Rear-Shock Seepage or Clunk Requires Inspection Before Replacement</x:v>
       </x:c>
-      <x:c r="E286" s="9" t="str">
+      <x:c r="E287" s="9" t="str">
         <x:v>Have the rear suspension inspected under current GM procedures. Do not replace a shock for light seepage alone. If the upper mount shifted, check and torque the mounting bolts to the bulletin specification and verify the Electronic Suspension Control Module calibration. Replace a shock only when diagnosis confirms an actual failure.</x:v>
       </x:c>
-      <x:c r="F286" s="9" t="str">
+      <x:c r="F287" s="9" t="str">
         <x:v>Have the rear suspension inspected under current GM procedures. Do not replace a shock for light seepage alone. If the upper mount shifted, check and torque the mounting bolts to the bulletin specification and verify the Electronic Suspension Control Module calibration. Replace a shock only when diagnosis confirms an actual failure.</x:v>
       </x:c>
-      <x:c r="G286" s="9" t="str">
+      <x:c r="G287" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H286" s="9" t="str">
+      <x:c r="H287" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Rear-Shock Seepage or Clunk Requires Inspection Before Replacement</x:v>
       </x:c>
-      <x:c r="I286" s="9" t="str">
+      <x:c r="I287" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J286" s="9" t="str">
+      <x:c r="J287" s="9" t="str">
         <x:v>2013-2015 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K286" s="9" t="str">
+      <x:c r="K287" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L286" s="9" t="str"/>
-      <x:c r="M286" s="9" t="str">
+      <x:c r="L287" s="9" t="str"/>
+      <x:c r="M287" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N286" s="41" t="str">
+      <x:c r="N287" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="287" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A287" s="40" t="str"/>
-      <x:c r="B287" s="9" t="str"/>
-      <x:c r="C287" s="9" t="str"/>
-      <x:c r="D287" s="9" t="str"/>
-      <x:c r="E287" s="9" t="str"/>
-      <x:c r="F287" s="9" t="str"/>
-      <x:c r="G287" s="9" t="str"/>
-      <x:c r="H287" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I287" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J287" s="9" t="str">
+    <x:row r="288" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A288" s="40" t="str"/>
+      <x:c r="B288" s="9" t="str"/>
+      <x:c r="C288" s="9" t="str"/>
+      <x:c r="D288" s="9" t="str"/>
+      <x:c r="E288" s="9" t="str"/>
+      <x:c r="F288" s="9" t="str"/>
+      <x:c r="G288" s="9" t="str"/>
+      <x:c r="H288" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I288" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J288" s="9" t="str">
         <x:v>2013-2015 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K287" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L287" s="9" t="str"/>
-      <x:c r="M287" s="9" t="str"/>
-      <x:c r="N287" s="41" t="str"/>
-    </x:row>
-    <x:row r="288" ht="752.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A288" s="40" t="n">
+      <x:c r="K288" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L288" s="9" t="str"/>
+      <x:c r="M288" s="9" t="str"/>
+      <x:c r="N288" s="41" t="str"/>
+    </x:row>
+    <x:row r="289" ht="752.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A289" s="40" t="n">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="B288" s="9" t="str">
+      <x:c r="B289" s="9" t="str">
         <x:v>cadillac-xts-parasitic-battery-drain-modules-not-entering-sleep-mode</x:v>
       </x:c>
-      <x:c r="C288" s="9" t="str">
+      <x:c r="C289" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | Luxury, Premium, Platinum, V-Sport, Vsport | 3.6L V6 (LFX), 3.6L Twin-Turbo V6 (LF3)</x:v>
       </x:c>
-      <x:c r="D288" s="9" t="str">
+      <x:c r="D289" s="9" t="str">
         <x:v>Parasitic Battery Drain / Modules Not Entering Sleep Mode</x:v>
       </x:c>
-      <x:c r="E288" s="9" t="str">
+      <x:c r="E289" s="9" t="str">
         <x:v>Perform a parasitic-draw test (normal is under ~50mA once modules sleep, roughly 30-40 seconds after lockup) and pull-fuse isolation to find the circuit that stays awake. Common fixes include replacing/reflashing a faulty CUE/radio module or BCM, repairing a chattering switch/connector that wakes the bus, and removing non-OEM accessories (aftermarket LEDs are a documented trigger). Replace the battery if it has been repeatedly deep-cycled.</x:v>
       </x:c>
-      <x:c r="F288" s="9" t="str">
+      <x:c r="F289" s="9" t="str">
         <x:v>Perform a parasitic-draw test (normal is under ~50mA once modules sleep, roughly 30-40 seconds after lockup) and pull-fuse isolation to find the circuit that stays awake. Common fixes include replacing/reflashing a faulty CUE/radio module or BCM, repairing a chattering switch/connector that wakes the bus, and removing non-OEM accessories (aftermarket LEDs are a documented trigger). Replace the battery if it has been repeatedly deep-cycled.</x:v>
       </x:c>
-      <x:c r="G288" s="9" t="str">
+      <x:c r="G289" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H288" s="9" t="str">
+      <x:c r="H289" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Parasitic Battery Drain / Modules Not Entering Sleep Mode</x:v>
       </x:c>
-      <x:c r="I288" s="9" t="str">
+      <x:c r="I289" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J288" s="9" t="str">
+      <x:c r="J289" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K288" s="9" t="str">
+      <x:c r="K289" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L288" s="9" t="str"/>
-      <x:c r="M288" s="9" t="str">
+      <x:c r="L289" s="9" t="str"/>
+      <x:c r="M289" s="9" t="str">
         <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
       </x:c>
-      <x:c r="N288" s="41" t="str">
+      <x:c r="N289" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="289" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A289" s="40" t="str"/>
-      <x:c r="B289" s="9" t="str"/>
-      <x:c r="C289" s="9" t="str"/>
-      <x:c r="D289" s="9" t="str"/>
-      <x:c r="E289" s="9" t="str"/>
-      <x:c r="F289" s="9" t="str"/>
-      <x:c r="G289" s="9" t="str"/>
-      <x:c r="H289" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I289" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J289" s="9" t="str">
+    <x:row r="290" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A290" s="40" t="str"/>
+      <x:c r="B290" s="9" t="str"/>
+      <x:c r="C290" s="9" t="str"/>
+      <x:c r="D290" s="9" t="str"/>
+      <x:c r="E290" s="9" t="str"/>
+      <x:c r="F290" s="9" t="str"/>
+      <x:c r="G290" s="9" t="str"/>
+      <x:c r="H290" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I290" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J290" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K289" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L289" s="9" t="str"/>
-      <x:c r="M289" s="9" t="str"/>
-      <x:c r="N289" s="41" t="str"/>
-    </x:row>
-    <x:row r="290" ht="673.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A290" s="40" t="n">
+      <x:c r="K290" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L290" s="9" t="str"/>
+      <x:c r="M290" s="9" t="str"/>
+      <x:c r="N290" s="41" t="str"/>
+    </x:row>
+    <x:row r="291" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A291" s="40" t="n">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="B290" s="9" t="str">
+      <x:c r="B291" s="9" t="str">
         <x:v>cadillac-xts-passenger-presence-system-fault-passenger-airbag-light</x:v>
       </x:c>
-      <x:c r="C290" s="9" t="str">
+      <x:c r="C291" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | Luxury, Premium, Platinum, V-Sport, Vsport | 3.6L V6 (LFX), 3.6L Twin-Turbo V6 (LF3)</x:v>
       </x:c>
-      <x:c r="D290" s="9" t="str">
+      <x:c r="D291" s="9" t="str">
         <x:v>Passenger Presence System Fault / Passenger Airbag Light On</x:v>
       </x:c>
-      <x:c r="E290" s="9" t="str">
+      <x:c r="E291" s="9" t="str">
         <x:v>Diagnose with a scan tool for airbag/occupant-classification codes. First inspect, reseat, and clean the under-seat connector and wiring harness (corroded/loose pins are the most common cause). If the sensor/pressure-mat or Passenger Presence Module itself has failed, replace it; in some cases the sensor is integrated into the seat cushion, raising cost. A post-repair occupant-classification recalibration may be required.</x:v>
       </x:c>
-      <x:c r="F290" s="9" t="str">
+      <x:c r="F291" s="9" t="str">
         <x:v>Diagnose with a scan tool for airbag/occupant-classification codes. First inspect, reseat, and clean the under-seat connector and wiring harness (corroded/loose pins are the most common cause). If the sensor/pressure-mat or Passenger Presence Module itself has failed, replace it; in some cases the sensor is integrated into the seat cushion, raising cost. A post-repair occupant-classification recalibration may be required.</x:v>
       </x:c>
-      <x:c r="G290" s="9" t="str">
+      <x:c r="G291" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H290" s="9" t="str">
+      <x:c r="H291" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Passenger Presence System Fault / Passenger Airbag Light On</x:v>
       </x:c>
-      <x:c r="I290" s="9" t="str">
+      <x:c r="I291" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J290" s="9" t="str">
+      <x:c r="J291" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K290" s="9" t="str">
+      <x:c r="K291" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L290" s="9" t="str"/>
-      <x:c r="M290" s="9" t="str">
+      <x:c r="L291" s="9" t="str"/>
+      <x:c r="M291" s="9" t="str">
         <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
       </x:c>
-      <x:c r="N290" s="41" t="str">
+      <x:c r="N291" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="291" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A291" s="40" t="str"/>
-      <x:c r="B291" s="9" t="str"/>
-      <x:c r="C291" s="9" t="str"/>
-      <x:c r="D291" s="9" t="str"/>
-      <x:c r="E291" s="9" t="str"/>
-      <x:c r="F291" s="9" t="str"/>
-      <x:c r="G291" s="9" t="str"/>
-      <x:c r="H291" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I291" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J291" s="9" t="str">
+    <x:row r="292" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A292" s="40" t="str"/>
+      <x:c r="B292" s="9" t="str"/>
+      <x:c r="C292" s="9" t="str"/>
+      <x:c r="D292" s="9" t="str"/>
+      <x:c r="E292" s="9" t="str"/>
+      <x:c r="F292" s="9" t="str"/>
+      <x:c r="G292" s="9" t="str"/>
+      <x:c r="H292" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I292" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J292" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K291" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L291" s="9" t="str"/>
-      <x:c r="M291" s="9" t="str"/>
-      <x:c r="N291" s="41" t="str"/>
-    </x:row>
-    <x:row r="292" ht="1003.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A292" s="40" t="n">
+      <x:c r="K292" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L292" s="9" t="str"/>
+      <x:c r="M292" s="9" t="str"/>
+      <x:c r="N292" s="41" t="str"/>
+    </x:row>
+    <x:row r="293" ht="1003.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A293" s="40" t="n">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B292" s="9" t="str">
+      <x:c r="B293" s="9" t="str">
         <x:v>cadillac-xts-rear-air-suspension-sudden-collapse</x:v>
       </x:c>
-      <x:c r="C292" s="9" t="str">
+      <x:c r="C293" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | 3.6L V6 LFX/LGX, 3.6L V6 Twin-Turbo LF3</x:v>
       </x:c>
-      <x:c r="D292" s="9" t="str">
+      <x:c r="D293" s="9" t="str">
         <x:v>Rear Air Suspension Sudden Collapse (F38 Air Ride)</x:v>
       </x:c>
-      <x:c r="E292" s="9" t="str">
+      <x:c r="E293" s="9" t="str">
         <x:v>Diagnose with a scan tool for leveling-system codes and a smoke/soap test of the air springs and lines. Replace failed rear air springs/struts and the air supply unit (compressor with integrated dryer). Many owners with repeat failures convert to a passive coil-spring/strut conversion kit (Strutmasters/Arnott) to permanently eliminate the air system. Always replace the air dryer/desiccant when servicing the compressor or moisture will quickly kill the new unit. OEM compressor assembly PN 84355910 (ACDelco 22956965); Arnott aftermarket compressor and spring kits are common cross-references.</x:v>
       </x:c>
-      <x:c r="F292" s="9" t="str">
+      <x:c r="F293" s="9" t="str">
         <x:v>Diagnose with a scan tool for leveling-system codes and a smoke/soap test of the air springs and lines. Replace failed rear air springs/struts and the air supply unit (compressor with integrated dryer). Many owners with repeat failures convert to a passive coil-spring/strut conversion kit (Strutmasters/Arnott) to permanently eliminate the air system. Always replace the air dryer/desiccant when servicing the compressor or moisture will quickly kill the new unit. OEM compressor assembly PN 84355910 (ACDelco 22956965); Arnott aftermarket compressor and spring kits are common cross-references.</x:v>
       </x:c>
-      <x:c r="G292" s="9" t="str">
+      <x:c r="G293" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H292" s="9" t="str">
+      <x:c r="H293" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Rear Air Suspension Sudden Collapse</x:v>
       </x:c>
-      <x:c r="I292" s="9" t="str">
+      <x:c r="I293" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J292" s="9" t="str">
+      <x:c r="J293" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K292" s="9" t="str">
+      <x:c r="K293" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L292" s="9" t="str"/>
-      <x:c r="M292" s="9" t="str">
+      <x:c r="L293" s="9" t="str"/>
+      <x:c r="M293" s="9" t="str">
         <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
       </x:c>
-      <x:c r="N292" s="41" t="str">
+      <x:c r="N293" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="293" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A293" s="40" t="str"/>
-      <x:c r="B293" s="9" t="str"/>
-      <x:c r="C293" s="9" t="str"/>
-      <x:c r="D293" s="9" t="str"/>
-      <x:c r="E293" s="9" t="str"/>
-      <x:c r="F293" s="9" t="str"/>
-      <x:c r="G293" s="9" t="str"/>
-      <x:c r="H293" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I293" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J293" s="9" t="str">
+    <x:row r="294" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A294" s="40" t="str"/>
+      <x:c r="B294" s="9" t="str"/>
+      <x:c r="C294" s="9" t="str"/>
+      <x:c r="D294" s="9" t="str"/>
+      <x:c r="E294" s="9" t="str"/>
+      <x:c r="F294" s="9" t="str"/>
+      <x:c r="G294" s="9" t="str"/>
+      <x:c r="H294" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I294" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J294" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K293" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L293" s="9" t="str"/>
-      <x:c r="M293" s="9" t="str"/>
-      <x:c r="N293" s="41" t="str"/>
-    </x:row>
-    <x:row r="294" ht="752.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A294" s="40" t="n">
+      <x:c r="K294" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L294" s="9" t="str"/>
+      <x:c r="M294" s="9" t="str"/>
+      <x:c r="N294" s="41" t="str"/>
+    </x:row>
+    <x:row r="295" ht="752.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A295" s="40" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="B294" s="9" t="str">
+      <x:c r="B295" s="9" t="str">
         <x:v>cadillac-xts-safety-alert-seat-haptic-motor-failure</x:v>
       </x:c>
-      <x:c r="C294" s="9" t="str">
+      <x:c r="C295" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | 3.6L V6 LFX/LGX, 3.6L V6 Twin-Turbo LF3</x:v>
       </x:c>
-      <x:c r="D294" s="9" t="str">
+      <x:c r="D295" s="9" t="str">
         <x:v>Safety Alert Seat Haptic Motor Failure</x:v>
       </x:c>
-      <x:c r="E294" s="9" t="str">
+      <x:c r="E295" s="9" t="str">
         <x:v>Confirm the dead side by triggering lane-departure to each side; if only one bolster pulses, the opposite motor/wire has failed. Replace the affected seat haptic vibration motor (left or right bumper-alert motor) and repair the broken wire at the motor entry. If the seat hardware checks out, scan the BCM for driver-assist codes and update software, since a glitch can mimic the failure. As a stopgap, owners can switch Alert Type to 'beeps' in the menu to restore audible warnings.</x:v>
       </x:c>
-      <x:c r="F294" s="9" t="str">
+      <x:c r="F295" s="9" t="str">
         <x:v>Confirm the dead side by triggering lane-departure to each side; if only one bolster pulses, the opposite motor/wire has failed. Replace the affected seat haptic vibration motor (left or right bumper-alert motor) and repair the broken wire at the motor entry. If the seat hardware checks out, scan the BCM for driver-assist codes and update software, since a glitch can mimic the failure. As a stopgap, owners can switch Alert Type to 'beeps' in the menu to restore audible warnings.</x:v>
       </x:c>
-      <x:c r="G294" s="9" t="str">
+      <x:c r="G295" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H294" s="9" t="str">
+      <x:c r="H295" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Safety Alert Seat Haptic Motor Failure</x:v>
       </x:c>
-      <x:c r="I294" s="9" t="str">
+      <x:c r="I295" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J294" s="9" t="str">
+      <x:c r="J295" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K294" s="9" t="str">
+      <x:c r="K295" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L294" s="9" t="str"/>
-      <x:c r="M294" s="9" t="str">
+      <x:c r="L295" s="9" t="str"/>
+      <x:c r="M295" s="9" t="str">
         <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
       </x:c>
-      <x:c r="N294" s="41" t="str">
+      <x:c r="N295" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="295" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A295" s="40" t="str"/>
-      <x:c r="B295" s="9" t="str"/>
-      <x:c r="C295" s="9" t="str"/>
-      <x:c r="D295" s="9" t="str"/>
-      <x:c r="E295" s="9" t="str"/>
-      <x:c r="F295" s="9" t="str"/>
-      <x:c r="G295" s="9" t="str"/>
-      <x:c r="H295" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I295" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J295" s="9" t="str">
+    <x:row r="296" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A296" s="40" t="str"/>
+      <x:c r="B296" s="9" t="str"/>
+      <x:c r="C296" s="9" t="str"/>
+      <x:c r="D296" s="9" t="str"/>
+      <x:c r="E296" s="9" t="str"/>
+      <x:c r="F296" s="9" t="str"/>
+      <x:c r="G296" s="9" t="str"/>
+      <x:c r="H296" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I296" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J296" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K295" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L295" s="9" t="str"/>
-      <x:c r="M295" s="9" t="str"/>
-      <x:c r="N295" s="41" t="str"/>
-    </x:row>
-    <x:row r="296" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A296" s="40" t="n">
+      <x:c r="K296" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L296" s="9" t="str"/>
+      <x:c r="M296" s="9" t="str"/>
+      <x:c r="N296" s="41" t="str"/>
+    </x:row>
+    <x:row r="297" ht="580.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A297" s="40" t="n">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="B296" s="9" t="str">
+      <x:c r="B297" s="9" t="str">
         <x:v>cadillac-xts-service-power-steering-message</x:v>
       </x:c>
-      <x:c r="C296" s="9" t="str">
+      <x:c r="C297" s="9" t="str">
         <x:v>2014-2016 | Cadillac | XTS</x:v>
       </x:c>
-      <x:c r="D296" s="9" t="str">
+      <x:c r="D297" s="9" t="str">
         <x:v>Cold-Start Service Power Steering Message May Require Power, Ground and Software Checks</x:v>
       </x:c>
-      <x:c r="E296" s="9" t="str">
+      <x:c r="E297" s="9" t="str">
         <x:v>Have a qualified technician verify RPO NJ2 and the exact DTC subtypes, inspect the G111 ground and XTS 80A F72UA fuse connections, fully charge and test the battery, then update the power-steering control module under current GM programming procedures. Do not replace the steering gear, module or battery solely from this card.</x:v>
       </x:c>
-      <x:c r="F296" s="9" t="str">
+      <x:c r="F297" s="9" t="str">
         <x:v>Have a qualified technician verify RPO NJ2 and the exact DTC subtypes, inspect the G111 ground and XTS 80A F72UA fuse connections, fully charge and test the battery, then update the power-steering control module under current GM programming procedures. Do not replace the steering gear, module or battery solely from this card.</x:v>
       </x:c>
-      <x:c r="G296" s="9" t="str">
+      <x:c r="G297" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H296" s="9" t="str">
+      <x:c r="H297" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Cold-Start Service Power Steering Message May Require Power, Ground and Software Checks</x:v>
       </x:c>
-      <x:c r="I296" s="9" t="str">
+      <x:c r="I297" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J296" s="9" t="str">
+      <x:c r="J297" s="9" t="str">
         <x:v>2014-2016 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K296" s="9" t="str">
+      <x:c r="K297" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L296" s="9" t="str"/>
-      <x:c r="M296" s="9" t="str">
+      <x:c r="L297" s="9" t="str"/>
+      <x:c r="M297" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N296" s="41" t="str">
+      <x:c r="N297" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="297" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A297" s="40" t="str"/>
-      <x:c r="B297" s="9" t="str"/>
-      <x:c r="C297" s="9" t="str"/>
-      <x:c r="D297" s="9" t="str"/>
-      <x:c r="E297" s="9" t="str"/>
-      <x:c r="F297" s="9" t="str"/>
-      <x:c r="G297" s="9" t="str"/>
-      <x:c r="H297" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I297" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J297" s="9" t="str">
+    <x:row r="298" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A298" s="40" t="str"/>
+      <x:c r="B298" s="9" t="str"/>
+      <x:c r="C298" s="9" t="str"/>
+      <x:c r="D298" s="9" t="str"/>
+      <x:c r="E298" s="9" t="str"/>
+      <x:c r="F298" s="9" t="str"/>
+      <x:c r="G298" s="9" t="str"/>
+      <x:c r="H298" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I298" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J298" s="9" t="str">
         <x:v>2014-2016 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K297" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L297" s="9" t="str"/>
-      <x:c r="M297" s="9" t="str"/>
-      <x:c r="N297" s="41" t="str"/>
-    </x:row>
-    <x:row r="298" ht="739.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A298" s="40" t="n">
+      <x:c r="K298" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L298" s="9" t="str"/>
+      <x:c r="M298" s="9" t="str"/>
+      <x:c r="N298" s="41" t="str"/>
+    </x:row>
+    <x:row r="299" ht="739.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A299" s="40" t="n">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B298" s="9" t="str">
+      <x:c r="B299" s="9" t="str">
         <x:v>cadillac-xts-sunroof-drain-leak-headliner-water-damage</x:v>
       </x:c>
-      <x:c r="C298" s="9" t="str">
+      <x:c r="C299" s="9" t="str">
         <x:v>2013-2018 | Cadillac | XTS | 3.6L V6 LFX/LGX, 3.6L V6 Twin-Turbo LF3</x:v>
       </x:c>
-      <x:c r="D298" s="9" t="str">
+      <x:c r="D299" s="9" t="str">
         <x:v>Sunroof Drain Leak / Headliner Water Damage</x:v>
       </x:c>
-      <x:c r="E298" s="9" t="str">
+      <x:c r="E299" s="9" t="str">
         <x:v>Flush all four sunroof drain tubes with low-pressure compressed air or a flexible trimmer line (avoid stiff wire that can pop the hose off at the bottom). Verify water exits at the rocker/A-pillar and rear quarter outlets. Replace cracked/age-hardened sunroof perimeter gaskets and reseat the drain hose grommets; in stubborn cases seal the leaking drain-tube connection. Dry and replace stained headliner/insulation and check for wet carpet over body control modules.</x:v>
       </x:c>
-      <x:c r="F298" s="9" t="str">
+      <x:c r="F299" s="9" t="str">
         <x:v>Flush all four sunroof drain tubes with low-pressure compressed air or a flexible trimmer line (avoid stiff wire that can pop the hose off at the bottom). Verify water exits at the rocker/A-pillar and rear quarter outlets. Replace cracked/age-hardened sunroof perimeter gaskets and reseat the drain hose grommets; in stubborn cases seal the leaking drain-tube connection. Dry and replace stained headliner/insulation and check for wet carpet over body control modules.</x:v>
       </x:c>
-      <x:c r="G298" s="9" t="str">
+      <x:c r="G299" s="9" t="str">
         <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
       </x:c>
-      <x:c r="H298" s="9" t="str">
+      <x:c r="H299" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Sunroof Drain Leak / Headliner Water Damage</x:v>
       </x:c>
-      <x:c r="I298" s="9" t="str">
+      <x:c r="I299" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J298" s="9" t="str">
+      <x:c r="J299" s="9" t="str">
         <x:v>2013-2018 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K298" s="9" t="str">
+      <x:c r="K299" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L298" s="9" t="str"/>
-      <x:c r="M298" s="9" t="str">
+      <x:c r="L299" s="9" t="str"/>
+      <x:c r="M299" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N298" s="41" t="str">
+      <x:c r="N299" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="299" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A299" s="40" t="str"/>
-      <x:c r="B299" s="9" t="str"/>
-      <x:c r="C299" s="9" t="str"/>
-      <x:c r="D299" s="9" t="str"/>
-      <x:c r="E299" s="9" t="str"/>
-      <x:c r="F299" s="9" t="str"/>
-      <x:c r="G299" s="9" t="str"/>
-      <x:c r="H299" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I299" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J299" s="9" t="str">
+    <x:row r="300" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A300" s="40" t="str"/>
+      <x:c r="B300" s="9" t="str"/>
+      <x:c r="C300" s="9" t="str"/>
+      <x:c r="D300" s="9" t="str"/>
+      <x:c r="E300" s="9" t="str"/>
+      <x:c r="F300" s="9" t="str"/>
+      <x:c r="G300" s="9" t="str"/>
+      <x:c r="H300" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I300" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J300" s="9" t="str">
         <x:v>2013-2018 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K299" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L299" s="9" t="str"/>
-      <x:c r="M299" s="9" t="str"/>
-      <x:c r="N299" s="41" t="str"/>
-    </x:row>
-    <x:row r="300" ht="607.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A300" s="40" t="n">
+      <x:c r="K300" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L300" s="9" t="str"/>
+      <x:c r="M300" s="9" t="str"/>
+      <x:c r="N300" s="41" t="str"/>
+    </x:row>
+    <x:row r="301" ht="607.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A301" s="40" t="n">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="B300" s="9" t="str">
+      <x:c r="B301" s="9" t="str">
         <x:v>cadillac-xts-timing-chain-2013</x:v>
       </x:c>
-      <x:c r="C300" s="9" t="str">
+      <x:c r="C301" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | 3.6L V6 (RPO LFX), 3.6L Twin-Turbo V6 (RPO LF3)</x:v>
       </x:c>
-      <x:c r="D300" s="9" t="str">
+      <x:c r="D301" s="9" t="str">
         <x:v>Multiple Cam/Crank Correlation DTCs Require Chain, Tensioner and Reluctor Diagnosis</x:v>
       </x:c>
-      <x:c r="E300" s="9" t="str">
+      <x:c r="E301" s="9" t="str">
         <x:v>Have a qualified technician confirm that at least two listed correlation DTCs are present, then follow current SI diagnosis for chains and tensioners. If the cause remains unresolved, inspect the crankshaft reluctor as directed by PIP3423P. Do not order the former generic timing kit or water pump from this card; the exact ShowMeTheParts lookup returned no timing-chain candidate.</x:v>
       </x:c>
-      <x:c r="F300" s="9" t="str">
+      <x:c r="F301" s="9" t="str">
         <x:v>Have a qualified technician confirm that at least two listed correlation DTCs are present, then follow current SI diagnosis for chains and tensioners. If the cause remains unresolved, inspect the crankshaft reluctor as directed by PIP3423P. Do not order the former generic timing kit or water pump from this card; the exact ShowMeTheParts lookup returned no timing-chain candidate.</x:v>
       </x:c>
-      <x:c r="G300" s="9" t="str">
+      <x:c r="G301" s="9" t="str">
         <x:v>DIAGNOSIS SERVICE — PRODUCT HOLD</x:v>
       </x:c>
-      <x:c r="H300" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I300" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J300" s="9" t="str">
+      <x:c r="H301" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I301" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J301" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS instruction-specific diagnosis</x:v>
       </x:c>
-      <x:c r="K300" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L300" s="9" t="str"/>
-      <x:c r="M300" s="9" t="str">
-        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
-      </x:c>
-      <x:c r="N300" s="41" t="str">
-        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="301" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A301" s="40" t="n">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="B301" s="9" t="str">
-        <x:v>cadillac-xts-torque-converter-transmission-shudder</x:v>
-      </x:c>
-      <x:c r="C301" s="9" t="str">
-        <x:v>2014-2019 | Cadillac | XTS</x:v>
-      </x:c>
-      <x:c r="D301" s="9" t="str">
-        <x:v>Launch or 2-3/3-2 Shift Shudder Must Be Separated from TCC Shudder</x:v>
-      </x:c>
-      <x:c r="E301" s="9" t="str">
-        <x:v>Have a qualified transmission technician verify the transmission RPO, reproduce the exact event and monitor TCC slip. Do not replace the TEHCM for this symptom. If diagnosis confirms the bulletin valve-body condition, follow current SI for both upper and lower valve-body replacement. Do not use a universal fluid or additive; the exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
-      </x:c>
-      <x:c r="F301" s="9" t="str">
-        <x:v>Have a qualified transmission technician verify the transmission RPO, reproduce the exact event and monitor TCC slip. Do not replace the TEHCM for this symptom. If diagnosis confirms the bulletin valve-body condition, follow current SI for both upper and lower valve-body replacement. Do not use a universal fluid or additive; the exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
-      </x:c>
-      <x:c r="G301" s="9" t="str">
-        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
-      </x:c>
-      <x:c r="H301" s="9" t="str">
-        <x:v>GM Genuine Parts catalog — Launch or 2-3/3-2 Shift Shudder Must Be Separated from TCC Shudder</x:v>
-      </x:c>
-      <x:c r="I301" s="9" t="str">
-        <x:v>https://parts.gmparts.com/</x:v>
-      </x:c>
-      <x:c r="J301" s="9" t="str">
-        <x:v>2014-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
-      </x:c>
       <x:c r="K301" s="9" t="str">
-        <x:v>manufacturer VIN-select parts catalog</x:v>
+        <x:v>manufacturer-capable service</x:v>
       </x:c>
       <x:c r="L301" s="9" t="str"/>
       <x:c r="M301" s="9" t="str">
+        <x:v>The How to Fix explicitly withholds a product or requires diagnosis before component selection.</x:v>
+      </x:c>
+      <x:c r="N301" s="41" t="str">
+        <x:v>Do not turn the symptom, DTC or title into a product recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A302" s="40" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B302" s="9" t="str">
+        <x:v>cadillac-xts-torque-converter-transmission-shudder</x:v>
+      </x:c>
+      <x:c r="C302" s="9" t="str">
+        <x:v>2014-2019 | Cadillac | XTS</x:v>
+      </x:c>
+      <x:c r="D302" s="9" t="str">
+        <x:v>Launch or 2-3/3-2 Shift Shudder Must Be Separated from TCC Shudder</x:v>
+      </x:c>
+      <x:c r="E302" s="9" t="str">
+        <x:v>Have a qualified transmission technician verify the transmission RPO, reproduce the exact event and monitor TCC slip. Do not replace the TEHCM for this symptom. If diagnosis confirms the bulletin valve-body condition, follow current SI for both upper and lower valve-body replacement. Do not use a universal fluid or additive; the exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
+      </x:c>
+      <x:c r="F302" s="9" t="str">
+        <x:v>Have a qualified transmission technician verify the transmission RPO, reproduce the exact event and monitor TCC slip. Do not replace the TEHCM for this symptom. If diagnosis confirms the bulletin valve-body condition, follow current SI for both upper and lower valve-body replacement. Do not use a universal fluid or additive; the exact ShowMeTheParts lookup returned no transmission-fluid candidate.</x:v>
+      </x:c>
+      <x:c r="G302" s="9" t="str">
+        <x:v>VIN/RPO / EXACT-COMPONENT GATE</x:v>
+      </x:c>
+      <x:c r="H302" s="9" t="str">
+        <x:v>GM Genuine Parts catalog — Launch or 2-3/3-2 Shift Shudder Must Be Separated from TCC Shudder</x:v>
+      </x:c>
+      <x:c r="I302" s="9" t="str">
+        <x:v>https://parts.gmparts.com/</x:v>
+      </x:c>
+      <x:c r="J302" s="9" t="str">
+        <x:v>2014-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
+      </x:c>
+      <x:c r="K302" s="9" t="str">
+        <x:v>manufacturer VIN-select parts catalog</x:v>
+      </x:c>
+      <x:c r="L302" s="9" t="str"/>
+      <x:c r="M302" s="9" t="str">
         <x:v>The repair names a physical component, but exact VIN/RPO/position and failed branch must be confirmed before purchase.</x:v>
       </x:c>
-      <x:c r="N301" s="41" t="str">
+      <x:c r="N302" s="41" t="str">
         <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
       </x:c>
     </x:row>
-    <x:row r="302" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A302" s="40" t="str"/>
-      <x:c r="B302" s="9" t="str"/>
-      <x:c r="C302" s="9" t="str"/>
-      <x:c r="D302" s="9" t="str"/>
-      <x:c r="E302" s="9" t="str"/>
-      <x:c r="F302" s="9" t="str"/>
-      <x:c r="G302" s="9" t="str"/>
-      <x:c r="H302" s="9" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I302" s="9" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J302" s="9" t="str">
+    <x:row r="303" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A303" s="40" t="str"/>
+      <x:c r="B303" s="9" t="str"/>
+      <x:c r="C303" s="9" t="str"/>
+      <x:c r="D303" s="9" t="str"/>
+      <x:c r="E303" s="9" t="str"/>
+      <x:c r="F303" s="9" t="str"/>
+      <x:c r="G303" s="9" t="str"/>
+      <x:c r="H303" s="9" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I303" s="9" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J303" s="9" t="str">
         <x:v>2014-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K302" s="9" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L302" s="9" t="str"/>
-      <x:c r="M302" s="9" t="str"/>
-      <x:c r="N302" s="41" t="str"/>
-    </x:row>
-    <x:row r="303" ht="805.2000122070312" hidden="0" customHeight="1">
-      <x:c r="A303" s="40" t="n">
+      <x:c r="K303" s="9" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L303" s="9" t="str"/>
+      <x:c r="M303" s="9" t="str"/>
+      <x:c r="N303" s="41" t="str"/>
+    </x:row>
+    <x:row r="304" ht="805.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A304" s="40" t="n">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="B303" s="9" t="str">
+      <x:c r="B304" s="9" t="str">
         <x:v>cadillac-xts-water-pump-weep-hole-coolant-leak</x:v>
       </x:c>
-      <x:c r="C303" s="9" t="str">
+      <x:c r="C304" s="9" t="str">
         <x:v>2013-2019 | Cadillac | XTS | 3.6L V6 LFX/LGX</x:v>
       </x:c>
-      <x:c r="D303" s="9" t="str">
+      <x:c r="D304" s="9" t="str">
         <x:v>Water Pump Weep-Hole Coolant Leak (3.6L V6)</x:v>
       </x:c>
-      <x:c r="E303" s="9" t="str">
+      <x:c r="E304" s="9" t="str">
         <x:v>Confirm the source: clean the area and look for fresh coolant tracking from the weep hole below the water pump pulley (versus hose clamps or the radiator). Replace the water pump with a new OEM/ACDelco unit and gasket, refill with DEX-COOL, and pressure-test. Do NOT use stop-leak — it can clog the heater core and radiator. ACDelco Gold water pump PN 19325605 (aftermarket ACDelco 252-962 cross-reference); inspect the thermostat and upper/lower hoses while the system is open.</x:v>
       </x:c>
-      <x:c r="F303" s="9" t="str">
+      <x:c r="F304" s="9" t="str">
         <x:v>Confirm the source: clean the area and look for fresh coolant tracking from the weep hole below the water pump pulley (versus hose clamps or the radiator). Replace the water pump with a new OEM/ACDelco unit and gasket, refill with DEX-COOL, and pressure-test. Do NOT use stop-leak — it can clog the heater core and radiator. ACDelco Gold water pump PN 19325605 (aftermarket ACDelco 252-962 cross-reference); inspect the thermostat and upper/lower hoses while the system is open.</x:v>
       </x:c>
-      <x:c r="G303" s="9" t="str">
+      <x:c r="G304" s="9" t="str">
         <x:v>EXPLICIT SCANNER/DIAGNOSTIC TOOL APPROVAL — PROFESSIONAL DIAGNOSIS / EXACT-PART GATE</x:v>
       </x:c>
-      <x:c r="H303" s="9" t="str">
+      <x:c r="H304" s="9" t="str">
+        <x:v>eBay — Engine Water Pump WPGM-611V</x:v>
+      </x:c>
+      <x:c r="I304" s="9" t="str">
+        <x:v>https://www.ebay.com/itm/137201131319?_skw=Aisin+WPGM-611V+Engine+Water+Pump&amp;hash=item1ff1d31f37%3Ag%3AwbcAAeSwarpp01Vu&amp;mkevt=1&amp;mkcid=1&amp;mkrid=711-53200-19255-0&amp;campid=5339164204&amp;customid=&amp;toolid=10049</x:v>
+      </x:c>
+      <x:c r="J304" s="9" t="str">
+        <x:v>2013-2019 Cadillac XTS; only for the diagnosed Engine Water Pump branch, with exact engine/trim/position fitment rechecked before purchase</x:v>
+      </x:c>
+      <x:c r="K304" s="9" t="str">
+        <x:v>stored verified product link; exact conditional branch</x:v>
+      </x:c>
+      <x:c r="L304" s="9" t="str">
+        <x:v>Existing product page title/part number and stored ShowMeTheParts fitment evidence reviewed against the full How to Fix.</x:v>
+      </x:c>
+      <x:c r="M304" s="9" t="str">
+        <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known. Existing exact-part commerce link retained for that conditional branch.</x:v>
+      </x:c>
+      <x:c r="N304" s="41" t="str">
+        <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A305" s="40" t="str"/>
+      <x:c r="B305" s="9" t="str"/>
+      <x:c r="C305" s="9" t="str"/>
+      <x:c r="D305" s="9" t="str"/>
+      <x:c r="E305" s="9" t="str"/>
+      <x:c r="F305" s="9" t="str"/>
+      <x:c r="G305" s="9" t="str"/>
+      <x:c r="H305" s="9" t="str">
         <x:v>GM Genuine Parts catalog — Water Pump Weep-Hole Coolant Leak</x:v>
       </x:c>
-      <x:c r="I303" s="9" t="str">
+      <x:c r="I305" s="9" t="str">
         <x:v>https://parts.gmparts.com/</x:v>
       </x:c>
-      <x:c r="J303" s="9" t="str">
+      <x:c r="J305" s="9" t="str">
         <x:v>2013-2019 Cadillac XTS; select exact VIN, engine, trim, position and current supersession</x:v>
       </x:c>
-      <x:c r="K303" s="9" t="str">
+      <x:c r="K305" s="9" t="str">
         <x:v>manufacturer VIN-select parts catalog</x:v>
       </x:c>
-      <x:c r="L303" s="9" t="str"/>
-      <x:c r="M303" s="9" t="str">
-        <x:v>The How to Fix explicitly requires testing or scan-capable diagnosis before the failed branch and exact part are known.</x:v>
-      </x:c>
-      <x:c r="N303" s="41" t="str">
-        <x:v>The official catalog is a fitment gate, not approval of every listed part; select the exact VIN and confirmed component.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="304" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A304" s="42" t="str"/>
-      <x:c r="B304" s="43" t="str"/>
-      <x:c r="C304" s="43" t="str"/>
-      <x:c r="D304" s="43" t="str"/>
-      <x:c r="E304" s="43" t="str"/>
-      <x:c r="F304" s="43" t="str"/>
-      <x:c r="G304" s="43" t="str"/>
-      <x:c r="H304" s="43" t="str">
-        <x:v>Cadillac certified-service locator</x:v>
-      </x:c>
-      <x:c r="I304" s="43" t="str">
-        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
-      </x:c>
-      <x:c r="J304" s="43" t="str">
+      <x:c r="L305" s="9" t="str"/>
+      <x:c r="M305" s="9" t="str"/>
+      <x:c r="N305" s="41" t="str"/>
+    </x:row>
+    <x:row r="306" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A306" s="42" t="str"/>
+      <x:c r="B306" s="43" t="str"/>
+      <x:c r="C306" s="43" t="str"/>
+      <x:c r="D306" s="43" t="str"/>
+      <x:c r="E306" s="43" t="str"/>
+      <x:c r="F306" s="43" t="str"/>
+      <x:c r="G306" s="43" t="str"/>
+      <x:c r="H306" s="43" t="str">
+        <x:v>Cadillac certified-service locator</x:v>
+      </x:c>
+      <x:c r="I306" s="43" t="str">
+        <x:v>https://www.cadillac.com/certified-service/dealer-locator</x:v>
+      </x:c>
+      <x:c r="J306" s="43" t="str">
         <x:v>2013-2019 Cadillac XTS diagnosis, VIN/RPO confirmation and repair</x:v>
       </x:c>
-      <x:c r="K304" s="43" t="str">
-        <x:v>manufacturer-capable service</x:v>
-      </x:c>
-      <x:c r="L304" s="43" t="str"/>
-      <x:c r="M304" s="43" t="str"/>
-      <x:c r="N304" s="44" t="str"/>
+      <x:c r="K306" s="43" t="str">
+        <x:v>manufacturer-capable service</x:v>
+      </x:c>
+      <x:c r="L306" s="43" t="str"/>
+      <x:c r="M306" s="43" t="str"/>
+      <x:c r="N306" s="44" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
